--- a/database/event/2557/event_2557_evp_summary.xlsx
+++ b/database/event/2557/event_2557_evp_summary.xlsx
@@ -492,219 +492,219 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0458</v>
+        <v>6.7214</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0892</v>
+        <v>2.3226</v>
       </c>
       <c r="D2" t="n">
-        <v>2.021</v>
+        <v>2.2339</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0458</v>
+        <v>6.7214</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3241</v>
+        <v>2.8931</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7217</v>
+        <v>3.8283</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8362</v>
+        <v>2.8931</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9199</v>
+        <v>2.3449</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7217</v>
+        <v>3.8283</v>
       </c>
       <c r="K2" t="n">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="L2" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6416</v>
+        <v>6.1732</v>
       </c>
       <c r="N2" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0172</v>
+        <v>6.3413</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0793</v>
+        <v>2.1913</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0095</v>
+        <v>2.0825</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0172</v>
+        <v>6.3413</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1889</v>
+        <v>4.1527</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8283</v>
+        <v>2.1885</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1889</v>
+        <v>4.2085</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7741</v>
+        <v>4.2439</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8283</v>
+        <v>2.1885</v>
       </c>
       <c r="K3" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="L3" t="n">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6024</v>
+        <v>6.432399999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>280</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1362</v>
+        <v>6.3034</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7749</v>
+        <v>2.1782</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6535</v>
+        <v>2.0674</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1362</v>
+        <v>6.3034</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8816000000000001</v>
+        <v>4.5817</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2546</v>
+        <v>1.7217</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8816000000000001</v>
+        <v>5.8729</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7146</v>
+        <v>4.7601</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2546</v>
+        <v>1.7217</v>
       </c>
       <c r="K4" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="L4" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9692</v>
+        <v>6.481800000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6068</v>
+        <v>5.8987</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5919</v>
+        <v>2.0384</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4397</v>
+        <v>1.9061</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6068</v>
+        <v>5.8987</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3657</v>
+        <v>4.081</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2411</v>
+        <v>1.8177</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3657</v>
+        <v>4.096</v>
       </c>
       <c r="I5" t="n">
-        <v>1.107</v>
+        <v>4.1304</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2411</v>
+        <v>1.8177</v>
       </c>
       <c r="K5" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="L5" t="n">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3481</v>
+        <v>5.9481</v>
       </c>
       <c r="N5" t="n">
-        <v>280</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4709</v>
+        <v>5.3544</v>
       </c>
       <c r="C6" t="n">
-        <v>1.545</v>
+        <v>1.8503</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3848</v>
+        <v>1.6893</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4709</v>
+        <v>5.3544</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6532</v>
+        <v>3.9721</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8177</v>
+        <v>1.3823</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6532</v>
+        <v>3.9721</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6656</v>
+        <v>4.0055</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8177</v>
+        <v>1.3823</v>
       </c>
       <c r="K6" t="n">
         <v>113</v>
@@ -713,7 +713,7 @@
         <v>103</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4833</v>
+        <v>5.387799999999999</v>
       </c>
       <c r="N6" t="n">
         <v>216</v>
@@ -722,173 +722,173 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2957</v>
+        <v>5.1365</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4844</v>
+        <v>1.775</v>
       </c>
       <c r="D7" t="n">
-        <v>1.314</v>
+        <v>1.6025</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2957</v>
+        <v>5.1365</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3989</v>
+        <v>0.8819</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8968</v>
+        <v>4.2546</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3989</v>
+        <v>0.8819</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3989</v>
+        <v>0.7148</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8968</v>
+        <v>4.2546</v>
       </c>
       <c r="K7" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L7" t="n">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2957</v>
+        <v>4.9694</v>
       </c>
       <c r="N7" t="n">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7443</v>
+        <v>5.0839</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2939</v>
+        <v>1.7568</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0913</v>
+        <v>1.5815</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7443</v>
+        <v>5.0839</v>
       </c>
       <c r="F8" t="n">
-        <v>3.717</v>
+        <v>1.8428</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0273</v>
+        <v>3.2411</v>
       </c>
       <c r="H8" t="n">
-        <v>3.717</v>
+        <v>1.8428</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0128</v>
+        <v>1.4936</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0273</v>
+        <v>3.2411</v>
       </c>
       <c r="K8" t="n">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="L8" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0401</v>
+        <v>4.7347</v>
       </c>
       <c r="N8" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6618</v>
+        <v>5.0108</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2654</v>
+        <v>1.7315</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0579</v>
+        <v>1.5524</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6618</v>
+        <v>5.0108</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4732</v>
+        <v>2.114</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1885</v>
+        <v>2.8968</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4732</v>
+        <v>2.114</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4801</v>
+        <v>2.114</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1885</v>
+        <v>2.8968</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="L9" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6686</v>
+        <v>5.0108</v>
       </c>
       <c r="N9" t="n">
-        <v>216</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.614</v>
+        <v>4.9339</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2489</v>
+        <v>1.705</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0386</v>
+        <v>1.5218</v>
       </c>
       <c r="E10" t="n">
-        <v>3.614</v>
+        <v>4.9339</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2581</v>
+        <v>4.7972</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6441</v>
+        <v>0.1367</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3737</v>
+        <v>5.219</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4145</v>
+        <v>5.3072</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6441</v>
+        <v>0.1367</v>
       </c>
       <c r="K10" t="n">
         <v>140</v>
@@ -897,7 +897,7 @@
         <v>76</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7704</v>
+        <v>5.4439</v>
       </c>
       <c r="N10" t="n">
         <v>216</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3981</v>
+        <v>4.6982</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1742</v>
+        <v>1.6235</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9514</v>
+        <v>1.4279</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3981</v>
+        <v>4.6982</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6988</v>
+        <v>5.3423</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6993</v>
+        <v>-0.6441</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6988</v>
+        <v>6.0736</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6988</v>
+        <v>6.1763</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6993</v>
+        <v>-0.6441</v>
       </c>
       <c r="K11" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="L11" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3981</v>
+        <v>5.5322</v>
       </c>
       <c r="N11" t="n">
-        <v>257</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.1245</v>
+        <v>4.0626</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0797</v>
+        <v>1.4039</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8409</v>
+        <v>1.1746</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1245</v>
+        <v>4.0626</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9878</v>
+        <v>4.0353</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1367</v>
+        <v>0.0273</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9878</v>
+        <v>4.0353</v>
       </c>
       <c r="I12" t="n">
-        <v>3.0157</v>
+        <v>3.2707</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1367</v>
+        <v>0.0273</v>
       </c>
       <c r="K12" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L12" t="n">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1524</v>
+        <v>3.298</v>
       </c>
       <c r="N12" t="n">
-        <v>216</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1095</v>
+        <v>4.0121</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0745</v>
+        <v>1.3864</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8348</v>
+        <v>1.1545</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1095</v>
+        <v>4.0121</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7893</v>
+        <v>2.6919</v>
       </c>
       <c r="G13" t="n">
         <v>1.3202</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7893</v>
+        <v>2.6919</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7976</v>
+        <v>2.7146</v>
       </c>
       <c r="J13" t="n">
         <v>1.3202</v>
@@ -1035,7 +1035,7 @@
         <v>103</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1178</v>
+        <v>4.0348</v>
       </c>
       <c r="N13" t="n">
         <v>216</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.059</v>
+        <v>3.9995</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0571</v>
+        <v>1.3821</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8144</v>
+        <v>1.1495</v>
       </c>
       <c r="E14" t="n">
-        <v>3.059</v>
+        <v>3.9995</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6767</v>
+        <v>2.3002</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3823</v>
+        <v>1.6993</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6767</v>
+        <v>2.3002</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6845</v>
+        <v>2.3002</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3823</v>
+        <v>1.6993</v>
       </c>
       <c r="K14" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="L14" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0668</v>
+        <v>3.9995</v>
       </c>
       <c r="N14" t="n">
-        <v>216</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6958</v>
+        <v>3.4822</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9316</v>
+        <v>1.2033</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6677</v>
+        <v>0.9434</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6958</v>
+        <v>3.4822</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3094</v>
+        <v>3.4822</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3864</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3094</v>
+        <v>3.4822</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3201</v>
+        <v>3.4822</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3864</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="L15" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7065</v>
+        <v>3.4822</v>
       </c>
       <c r="N15" t="n">
-        <v>199</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6117</v>
+        <v>3.0546</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9025</v>
+        <v>1.0555</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6337</v>
+        <v>0.773</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6117</v>
+        <v>3.0546</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6117</v>
+        <v>2.6682</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.3864</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6117</v>
+        <v>2.6682</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6117</v>
+        <v>2.6907</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.3864</v>
       </c>
       <c r="K16" t="n">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6117</v>
+        <v>3.0771</v>
       </c>
       <c r="N16" t="n">
-        <v>128</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4826</v>
+        <v>2.9155</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8579</v>
+        <v>1.0075</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5816</v>
+        <v>0.7176</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4826</v>
+        <v>2.9155</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0154</v>
+        <v>0.4175</v>
       </c>
       <c r="G17" t="n">
         <v>2.498</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0154</v>
+        <v>0.4175</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0154</v>
+        <v>0.4175</v>
       </c>
       <c r="J17" t="n">
         <v>2.498</v>
@@ -1219,7 +1219,7 @@
         <v>133</v>
       </c>
       <c r="M17" t="n">
-        <v>2.4826</v>
+        <v>2.9155</v>
       </c>
       <c r="N17" t="n">
         <v>257</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0205</v>
+        <v>2.1657</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6982</v>
+        <v>0.7484</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3949</v>
+        <v>0.4189</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0205</v>
+        <v>2.1657</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8303</v>
+        <v>2.1657</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1902</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8303</v>
+        <v>2.1657</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8388</v>
+        <v>2.1657</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1902</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="L18" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.029</v>
+        <v>2.1657</v>
       </c>
       <c r="N18" t="n">
-        <v>199</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7781</v>
+        <v>2.0625</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.7127</v>
       </c>
       <c r="D19" t="n">
-        <v>0.297</v>
+        <v>0.3778</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7781</v>
+        <v>2.0625</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6601</v>
+        <v>1.8723</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4382</v>
+        <v>0.1902</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6601</v>
+        <v>1.8723</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.535</v>
+        <v>1.8881</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4382</v>
+        <v>0.1902</v>
       </c>
       <c r="K19" t="n">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="L19" t="n">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9032</v>
+        <v>2.0783</v>
       </c>
       <c r="N19" t="n">
-        <v>280</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4192</v>
+        <v>2.007</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4904</v>
+        <v>0.6935</v>
       </c>
       <c r="D20" t="n">
-        <v>0.152</v>
+        <v>0.3557</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4192</v>
+        <v>2.007</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4192</v>
+        <v>2.007</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4192</v>
+        <v>2.007</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4192</v>
+        <v>2.007</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4192</v>
+        <v>2.007</v>
       </c>
       <c r="N20" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1412</v>
+        <v>2.0048</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3944</v>
+        <v>0.6928</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0397</v>
+        <v>0.3548</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1412</v>
+        <v>2.0048</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1412</v>
+        <v>-0.4334</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.4382</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1412</v>
+        <v>-0.4334</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1412</v>
+        <v>-0.3513</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.4382</v>
       </c>
       <c r="K21" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1412</v>
+        <v>2.0869</v>
       </c>
       <c r="N21" t="n">
-        <v>138</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1239</v>
+        <v>1.9909</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3884</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0327</v>
+        <v>0.3493</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1239</v>
+        <v>1.9909</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1239</v>
+        <v>2.9909</v>
       </c>
       <c r="G22" t="n">
         <v>-1</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1239</v>
+        <v>2.9909</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1437</v>
+        <v>3.0415</v>
       </c>
       <c r="J22" t="n">
         <v>-1</v>
@@ -1449,7 +1449,7 @@
         <v>76</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1437</v>
+        <v>2.0415</v>
       </c>
       <c r="N22" t="n">
         <v>216</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0132</v>
+        <v>1.6994</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3501</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0121</v>
+        <v>0.2331</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0132</v>
+        <v>1.6994</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0132</v>
+        <v>1.6994</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0132</v>
+        <v>1.6994</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0132</v>
+        <v>1.6994</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0132</v>
+        <v>1.6994</v>
       </c>
       <c r="N23" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7356</v>
+        <v>1.52</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2542</v>
+        <v>0.5253</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1242</v>
+        <v>0.1617</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7356</v>
+        <v>1.52</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7356</v>
+        <v>1.52</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7356</v>
+        <v>1.52</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7356</v>
+        <v>1.52</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7356</v>
+        <v>1.52</v>
       </c>
       <c r="N24" t="n">
         <v>128</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6914</v>
+        <v>1.3514</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2389</v>
+        <v>0.467</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1421</v>
+        <v>0.0945</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6914</v>
+        <v>1.3514</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6914</v>
+        <v>1.3514</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6914</v>
+        <v>1.3514</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6914</v>
+        <v>1.3514</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6914</v>
+        <v>1.3514</v>
       </c>
       <c r="N25" t="n">
         <v>138</v>
@@ -1596,308 +1596,308 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6142</v>
+        <v>1.3391</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2122</v>
+        <v>0.4627</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1732</v>
+        <v>0.0896</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6142</v>
+        <v>1.3391</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2998</v>
+        <v>2.0915</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6856</v>
+        <v>-0.7524</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2998</v>
+        <v>2.0915</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0535</v>
+        <v>2.1269</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6856</v>
+        <v>-0.7524</v>
       </c>
       <c r="K26" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L26" t="n">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3679000000000001</v>
+        <v>1.3745</v>
       </c>
       <c r="N26" t="n">
-        <v>300</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5089</v>
+        <v>1.2359</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1759</v>
+        <v>0.4271</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2158</v>
+        <v>0.0485</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5089</v>
+        <v>1.2359</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2613</v>
+        <v>1.2359</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.7524</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2613</v>
+        <v>1.2359</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2731</v>
+        <v>1.2359</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.7524</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L27" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5206999999999999</v>
+        <v>1.2359</v>
       </c>
       <c r="N27" t="n">
-        <v>216</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4913</v>
+        <v>1.1439</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1698</v>
+        <v>0.3953</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2229</v>
+        <v>0.0118</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4913</v>
+        <v>1.1439</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4913</v>
+        <v>1.1439</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4913</v>
+        <v>1.1439</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4913</v>
+        <v>1.1439</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4913</v>
+        <v>1.1439</v>
       </c>
       <c r="N28" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4432</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1532</v>
+        <v>0.3008</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2423</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4432</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4432</v>
+        <v>0.9735</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.103</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4432</v>
+        <v>0.9735</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4432</v>
+        <v>0.9899</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.103</v>
       </c>
       <c r="K29" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4432</v>
+        <v>0.8869</v>
       </c>
       <c r="N29" t="n">
-        <v>114</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2968</v>
+        <v>0.832</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1026</v>
+        <v>0.2875</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3015</v>
+        <v>-0.1124</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2968</v>
+        <v>0.832</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2968</v>
+        <v>0.8033</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.0287</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2968</v>
+        <v>0.8033</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2968</v>
+        <v>0.8033</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.0287</v>
       </c>
       <c r="K30" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2968</v>
+        <v>0.832</v>
       </c>
       <c r="N30" t="n">
-        <v>138</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2915</v>
+        <v>0.8118</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1007</v>
+        <v>0.2805</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3036</v>
+        <v>-0.1205</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2915</v>
+        <v>0.8118</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2628</v>
+        <v>0.8118</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0287</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2628</v>
+        <v>0.8118</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2628</v>
+        <v>0.8118</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0287</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="L31" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2915</v>
+        <v>0.8118</v>
       </c>
       <c r="N31" t="n">
-        <v>257</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2852</v>
+        <v>0.7205</v>
       </c>
       <c r="C32" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.249</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3061</v>
+        <v>-0.1569</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2852</v>
+        <v>0.7205</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2852</v>
+        <v>0.7205</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2852</v>
+        <v>0.7205</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2852</v>
+        <v>0.7205</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2852</v>
+        <v>0.7205</v>
       </c>
       <c r="N32" t="n">
         <v>138</v>
@@ -1918,308 +1918,308 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.215</v>
+        <v>0.7037</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0743</v>
+        <v>0.2432</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3345</v>
+        <v>-0.1636</v>
       </c>
       <c r="E33" t="n">
-        <v>0.215</v>
+        <v>0.7037</v>
       </c>
       <c r="F33" t="n">
-        <v>0.215</v>
+        <v>1.3893</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.6856</v>
       </c>
       <c r="H33" t="n">
-        <v>0.215</v>
+        <v>1.3893</v>
       </c>
       <c r="I33" t="n">
-        <v>0.215</v>
+        <v>1.1261</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.6856</v>
       </c>
       <c r="K33" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M33" t="n">
-        <v>0.215</v>
+        <v>0.4405000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>138</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.211</v>
+        <v>0.5976</v>
       </c>
       <c r="C34" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2065</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3361</v>
+        <v>-0.2058</v>
       </c>
       <c r="E34" t="n">
-        <v>0.211</v>
+        <v>0.5976</v>
       </c>
       <c r="F34" t="n">
-        <v>0.211</v>
+        <v>0.5976</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.211</v>
+        <v>0.5976</v>
       </c>
       <c r="I34" t="n">
-        <v>0.211</v>
+        <v>0.5976</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.211</v>
+        <v>0.5976</v>
       </c>
       <c r="N34" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1377</v>
+        <v>0.5494</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0476</v>
+        <v>0.1899</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3657</v>
+        <v>-0.225</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1377</v>
+        <v>0.5494</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3114</v>
+        <v>1.5494</v>
       </c>
       <c r="G35" t="n">
-        <v>1.4491</v>
+        <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3114</v>
+        <v>1.5494</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0629</v>
+        <v>1.5625</v>
       </c>
       <c r="J35" t="n">
-        <v>1.4491</v>
+        <v>-1</v>
       </c>
       <c r="K35" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="L35" t="n">
-        <v>156</v>
+        <v>47</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3862000000000001</v>
+        <v>0.5625</v>
       </c>
       <c r="N35" t="n">
-        <v>300</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.135</v>
+        <v>0.5029</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0467</v>
+        <v>0.1738</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3668</v>
+        <v>-0.2436</v>
       </c>
       <c r="E36" t="n">
-        <v>0.135</v>
+        <v>0.5029</v>
       </c>
       <c r="F36" t="n">
-        <v>0.135</v>
+        <v>0.0912</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.4117</v>
       </c>
       <c r="H36" t="n">
-        <v>0.135</v>
+        <v>0.0912</v>
       </c>
       <c r="I36" t="n">
-        <v>0.135</v>
+        <v>0.0912</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.4117</v>
       </c>
       <c r="K36" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="M36" t="n">
-        <v>0.135</v>
+        <v>0.5029</v>
       </c>
       <c r="N36" t="n">
-        <v>138</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.0097</v>
+        <v>0.486</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0034</v>
+        <v>0.1679</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4253</v>
+        <v>-0.2503</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.0097</v>
+        <v>0.486</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.486</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6493</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.486</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.486</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6493</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="L37" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.006700000000000039</v>
+        <v>0.486</v>
       </c>
       <c r="N37" t="n">
-        <v>199</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ptr</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.0106</v>
+        <v>0.4432</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0037</v>
+        <v>0.1532</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4256</v>
+        <v>-0.2673</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.0106</v>
+        <v>0.4432</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0106</v>
+        <v>0.4432</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0106</v>
+        <v>0.4432</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0106</v>
+        <v>0.4432</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0106</v>
+        <v>0.4432</v>
       </c>
       <c r="N38" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.0397</v>
+        <v>0.3675</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.0137</v>
+        <v>0.127</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4374</v>
+        <v>-0.2975</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0397</v>
+        <v>0.3675</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.0397</v>
+        <v>0.3675</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.0397</v>
+        <v>0.3675</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0397</v>
+        <v>0.3675</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.0397</v>
+        <v>0.3675</v>
       </c>
       <c r="N39" t="n">
         <v>116</v>
@@ -2240,127 +2240,127 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.0444</v>
+        <v>0.3208</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.0153</v>
+        <v>0.1109</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4393</v>
+        <v>-0.3161</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.0444</v>
+        <v>0.3208</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0586</v>
+        <v>0.3208</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.103</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0586</v>
+        <v>0.3208</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0592</v>
+        <v>0.3208</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.103</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L40" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.04379999999999999</v>
+        <v>0.3208</v>
       </c>
       <c r="N40" t="n">
-        <v>216</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.0531</v>
+        <v>0.211</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0183</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4428</v>
+        <v>-0.3598</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0531</v>
+        <v>0.211</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0531</v>
+        <v>0.211</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0531</v>
+        <v>0.211</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0531</v>
+        <v>0.211</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0531</v>
+        <v>0.211</v>
       </c>
       <c r="N41" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.1509</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0261</v>
+        <v>0.0521</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4518</v>
+        <v>-0.3838</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.1509</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.6081</v>
+        <v>-1.2982</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5327</v>
+        <v>1.4491</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.6081</v>
+        <v>-1.2982</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.4929</v>
+        <v>-1.0522</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5327</v>
+        <v>1.4491</v>
       </c>
       <c r="K42" t="n">
         <v>144</v>
@@ -2369,7 +2369,7 @@
         <v>156</v>
       </c>
       <c r="M42" t="n">
-        <v>0.03979999999999995</v>
+        <v>0.3969</v>
       </c>
       <c r="N42" t="n">
         <v>300</v>
@@ -2378,354 +2378,354 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.0902</v>
+        <v>0.1021</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0312</v>
+        <v>0.0353</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4578</v>
+        <v>-0.4032</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.0902</v>
+        <v>0.1021</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.5019</v>
+        <v>0.7514</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4117</v>
+        <v>-0.6493</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.5019</v>
+        <v>0.7514</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5019</v>
+        <v>0.7577</v>
       </c>
       <c r="J43" t="n">
-        <v>0.4117</v>
+        <v>-0.6493</v>
       </c>
       <c r="K43" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="L43" t="n">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.0902</v>
+        <v>0.1084000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>257</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.111</v>
+        <v>0.0581</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0384</v>
+        <v>0.0201</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4662</v>
+        <v>-0.4208</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.111</v>
+        <v>0.0581</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.111</v>
+        <v>0.0581</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.111</v>
+        <v>0.0581</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.111</v>
+        <v>0.0581</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.111</v>
+        <v>0.0581</v>
       </c>
       <c r="N44" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1152</v>
+        <v>0.0467</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.0398</v>
+        <v>0.0161</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4679</v>
+        <v>-0.4253</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.1152</v>
+        <v>0.0467</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.1152</v>
+        <v>0.0467</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.1152</v>
+        <v>0.0467</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1152</v>
+        <v>0.0467</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.1152</v>
+        <v>0.0467</v>
       </c>
       <c r="N45" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1261</v>
+        <v>0.0299</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0436</v>
+        <v>0.0103</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4723</v>
+        <v>-0.432</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.1261</v>
+        <v>0.0299</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1261</v>
+        <v>0.0299</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.1261</v>
+        <v>0.0299</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1261</v>
+        <v>0.0299</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.1261</v>
+        <v>0.0299</v>
       </c>
       <c r="N46" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>ptr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.1622</v>
+        <v>-0.0106</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.056</v>
+        <v>-0.0037</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4869</v>
+        <v>-0.4481</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1622</v>
+        <v>-0.0106</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1622</v>
+        <v>-0.0106</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.1622</v>
+        <v>-0.0106</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1622</v>
+        <v>-0.0106</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.1622</v>
+        <v>-0.0106</v>
       </c>
       <c r="N47" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1763</v>
+        <v>-0.0708</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0609</v>
+        <v>-0.0245</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4926</v>
+        <v>-0.4721</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.1763</v>
+        <v>-0.0708</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8237</v>
+        <v>-0.0708</v>
       </c>
       <c r="G48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8237</v>
+        <v>-0.0708</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8275</v>
+        <v>-0.0708</v>
       </c>
       <c r="J48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="L48" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1725</v>
+        <v>-0.0708</v>
       </c>
       <c r="N48" t="n">
-        <v>199</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.246</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0261</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.4739</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.246</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.246</v>
+        <v>-0.6081</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.5327</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.246</v>
+        <v>-0.6081</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.246</v>
+        <v>-0.4929</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.5327</v>
       </c>
       <c r="K49" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.246</v>
+        <v>0.03979999999999995</v>
       </c>
       <c r="N49" t="n">
-        <v>116</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.383</v>
+        <v>-0.1593</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1323</v>
+        <v>-0.055</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.5074</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.383</v>
+        <v>-0.1593</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.383</v>
+        <v>-0.1593</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.383</v>
+        <v>-0.1593</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.383</v>
+        <v>-0.1593</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.383</v>
+        <v>-0.1593</v>
       </c>
       <c r="N50" t="n">
         <v>116</v>
@@ -2746,93 +2746,93 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.5584</v>
+        <v>-0.383</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.193</v>
+        <v>-0.1323</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6469</v>
+        <v>-0.5965</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.5584</v>
+        <v>-0.383</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.5584</v>
+        <v>-0.383</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5584</v>
+        <v>-0.383</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5584</v>
+        <v>-0.383</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.5584</v>
+        <v>-0.383</v>
       </c>
       <c r="N51" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.5619</v>
+        <v>-0.5584</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1942</v>
+        <v>-0.193</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6484</v>
+        <v>-0.6664</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5619</v>
+        <v>-0.5584</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.5619</v>
+        <v>-0.5584</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5619</v>
+        <v>-0.5584</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.5619</v>
+        <v>-0.5584</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.5619</v>
+        <v>-0.5584</v>
       </c>
       <c r="N52" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.6051</v>
+        <v>-0.6048</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2091</v>
+        <v>-0.209</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.6849</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.6051</v>
+        <v>-0.6048</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.4844</v>
+        <v>-1.4841</v>
       </c>
       <c r="G53" t="n">
         <v>0.8793</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.4844</v>
+        <v>-1.4841</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.2032</v>
+        <v>-1.2029</v>
       </c>
       <c r="J53" t="n">
         <v>0.8793</v>
@@ -2875,7 +2875,7 @@
         <v>155</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3239000000000001</v>
+        <v>-0.3236000000000001</v>
       </c>
       <c r="N53" t="n">
         <v>280</v>
@@ -2884,139 +2884,139 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.7863</v>
+        <v>-0.6932</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2717</v>
+        <v>-0.2395</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.739</v>
+        <v>-0.7201</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.7863</v>
+        <v>-0.6932</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.7863</v>
+        <v>-0.6932</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.7863</v>
+        <v>-0.6932</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.7863</v>
+        <v>-0.6932</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.7863</v>
+        <v>-0.6932</v>
       </c>
       <c r="N54" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.8441</v>
+        <v>-0.7863</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2917</v>
+        <v>-0.2717</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7624</v>
+        <v>-0.7572</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.8441</v>
+        <v>-0.7863</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.8441</v>
+        <v>-0.7863</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.8441</v>
+        <v>-0.7863</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8441</v>
+        <v>-0.7863</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.8441</v>
+        <v>-0.7863</v>
       </c>
       <c r="N55" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.969</v>
+        <v>-0.8441</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3348</v>
+        <v>-0.2917</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.8128</v>
+        <v>-0.7802</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.969</v>
+        <v>-0.8441</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.969</v>
+        <v>-0.8441</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.969</v>
+        <v>-0.8441</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.969</v>
+        <v>-0.8441</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.969</v>
+        <v>-0.8441</v>
       </c>
       <c r="N56" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57">
@@ -3032,7 +3032,7 @@
         <v>-0.4416</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9376</v>
+        <v>-0.953</v>
       </c>
       <c r="E57" t="n">
         <v>-1.2778</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.6265</v>
+        <v>-1.6217</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.5621</v>
+        <v>-0.5604</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.0784</v>
+        <v>-1.09</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.6265</v>
+        <v>-1.6217</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.3008</v>
+        <v>-1.296</v>
       </c>
       <c r="G58" t="n">
         <v>-0.3257</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.3008</v>
+        <v>-1.296</v>
       </c>
       <c r="I58" t="n">
         <v>-1.3069</v>
@@ -3124,7 +3124,7 @@
         <v>-0.5813</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.1009</v>
+        <v>-1.1141</v>
       </c>
       <c r="E59" t="n">
         <v>-1.6822</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.7273</v>
+        <v>-1.7245</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.5969</v>
+        <v>-0.5959</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.1192</v>
+        <v>-1.131</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.7273</v>
+        <v>-1.7245</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.7458</v>
+        <v>-0.743</v>
       </c>
       <c r="G60" t="n">
         <v>-0.9815</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.7458</v>
+        <v>-0.743</v>
       </c>
       <c r="I60" t="n">
         <v>-0.7493</v>
@@ -3216,7 +3216,7 @@
         <v>-0.6226</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.1492</v>
+        <v>-1.1617</v>
       </c>
       <c r="E61" t="n">
         <v>-1.8017</v>

--- a/database/event/2557/event_2557_evp_summary.xlsx
+++ b/database/event/2557/event_2557_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7214</v>
+        <v>6.2766</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3226</v>
+        <v>2.1689</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2339</v>
+        <v>2.1956</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7214</v>
+        <v>6.2766</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8931</v>
+        <v>2.8006</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8283</v>
+        <v>3.476</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8931</v>
+        <v>4.3814</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3449</v>
+        <v>2.2781</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8283</v>
+        <v>3.476</v>
       </c>
       <c r="K2" t="n">
         <v>125</v>
@@ -529,7 +529,7 @@
         <v>155</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1732</v>
+        <v>5.754099999999999</v>
       </c>
       <c r="N2" t="n">
         <v>280</v>
@@ -538,173 +538,173 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3413</v>
+        <v>5.8631</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1913</v>
+        <v>2.0261</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0825</v>
+        <v>2.0089</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3413</v>
+        <v>5.8631</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1527</v>
+        <v>1.7192</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1885</v>
+        <v>4.1439</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2085</v>
+        <v>1.7192</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2439</v>
+        <v>0.8939</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1885</v>
+        <v>4.1439</v>
       </c>
       <c r="K3" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="L3" t="n">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>6.432399999999999</v>
+        <v>5.037800000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>216</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3034</v>
+        <v>5.5081</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1782</v>
+        <v>1.9034</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0674</v>
+        <v>1.8486</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3034</v>
+        <v>5.5081</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5817</v>
+        <v>2.4824</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7217</v>
+        <v>3.0257</v>
       </c>
       <c r="H4" t="n">
-        <v>5.8729</v>
+        <v>3.2601</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7601</v>
+        <v>1.6951</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7217</v>
+        <v>3.0257</v>
       </c>
       <c r="K4" t="n">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="L4" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M4" t="n">
-        <v>6.481800000000001</v>
+        <v>4.720800000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8987</v>
+        <v>5.4093</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0384</v>
+        <v>1.8692</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9061</v>
+        <v>1.804</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8987</v>
+        <v>5.4093</v>
       </c>
       <c r="F5" t="n">
-        <v>4.081</v>
+        <v>4.0185</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8177</v>
+        <v>1.3908</v>
       </c>
       <c r="H5" t="n">
-        <v>4.096</v>
+        <v>8.6723</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1304</v>
+        <v>4.5092</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8177</v>
+        <v>1.3908</v>
       </c>
       <c r="K5" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="L5" t="n">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="M5" t="n">
-        <v>5.9481</v>
+        <v>5.9</v>
       </c>
       <c r="N5" t="n">
-        <v>216</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3544</v>
+        <v>5.2627</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8503</v>
+        <v>1.8186</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6893</v>
+        <v>1.7378</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3544</v>
+        <v>5.2627</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9721</v>
+        <v>3.5033</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3823</v>
+        <v>1.7594</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9721</v>
+        <v>4.3329</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0055</v>
+        <v>4.511</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3823</v>
+        <v>1.7594</v>
       </c>
       <c r="K6" t="n">
         <v>113</v>
@@ -713,7 +713,7 @@
         <v>103</v>
       </c>
       <c r="M6" t="n">
-        <v>5.387799999999999</v>
+        <v>6.2704</v>
       </c>
       <c r="N6" t="n">
         <v>216</v>
@@ -722,182 +722,182 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.1365</v>
+        <v>4.967</v>
       </c>
       <c r="C7" t="n">
-        <v>1.775</v>
+        <v>1.7164</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6025</v>
+        <v>1.6043</v>
       </c>
       <c r="E7" t="n">
-        <v>5.1365</v>
+        <v>4.967</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8819</v>
+        <v>3.4605</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2546</v>
+        <v>1.5065</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8819</v>
+        <v>4.2388</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7148</v>
+        <v>4.4131</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2546</v>
+        <v>1.5065</v>
       </c>
       <c r="K7" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="L7" t="n">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="M7" t="n">
-        <v>4.9694</v>
+        <v>5.9196</v>
       </c>
       <c r="N7" t="n">
-        <v>280</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.0839</v>
+        <v>4.7788</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7568</v>
+        <v>1.6514</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5815</v>
+        <v>1.5194</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0839</v>
+        <v>4.7788</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8428</v>
+        <v>2.3315</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2411</v>
+        <v>2.4473</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8428</v>
+        <v>2.3315</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4936</v>
+        <v>2.3315</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2411</v>
+        <v>2.4473</v>
       </c>
       <c r="K8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L8" t="n">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7347</v>
+        <v>4.7788</v>
       </c>
       <c r="N8" t="n">
-        <v>280</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.0108</v>
+        <v>4.5478</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7315</v>
+        <v>1.5715</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5524</v>
+        <v>1.4151</v>
       </c>
       <c r="E9" t="n">
-        <v>5.0108</v>
+        <v>4.5478</v>
       </c>
       <c r="F9" t="n">
-        <v>2.114</v>
+        <v>3.2447</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8968</v>
+        <v>1.3031</v>
       </c>
       <c r="H9" t="n">
-        <v>2.114</v>
+        <v>3.7651</v>
       </c>
       <c r="I9" t="n">
-        <v>2.114</v>
+        <v>3.9199</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8968</v>
+        <v>1.3031</v>
       </c>
       <c r="K9" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="L9" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="M9" t="n">
-        <v>5.0108</v>
+        <v>5.223</v>
       </c>
       <c r="N9" t="n">
-        <v>257</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.9339</v>
+        <v>3.9106</v>
       </c>
       <c r="C10" t="n">
-        <v>1.705</v>
+        <v>1.3513</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5218</v>
+        <v>1.1274</v>
       </c>
       <c r="E10" t="n">
-        <v>4.9339</v>
+        <v>3.9106</v>
       </c>
       <c r="F10" t="n">
-        <v>4.7972</v>
+        <v>2.8559</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1367</v>
+        <v>1.0547</v>
       </c>
       <c r="H10" t="n">
-        <v>5.219</v>
+        <v>2.9113</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3072</v>
+        <v>3.031</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1367</v>
+        <v>1.0547</v>
       </c>
       <c r="K10" t="n">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="L10" t="n">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="M10" t="n">
-        <v>5.4439</v>
+        <v>4.0857</v>
       </c>
       <c r="N10" t="n">
         <v>216</v>
@@ -906,136 +906,136 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.6982</v>
+        <v>3.8787</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6235</v>
+        <v>1.3403</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4279</v>
+        <v>1.113</v>
       </c>
       <c r="E11" t="n">
-        <v>4.6982</v>
+        <v>3.8787</v>
       </c>
       <c r="F11" t="n">
-        <v>5.3423</v>
+        <v>2.4495</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6441</v>
+        <v>1.4292</v>
       </c>
       <c r="H11" t="n">
-        <v>6.0736</v>
+        <v>2.4495</v>
       </c>
       <c r="I11" t="n">
-        <v>6.1763</v>
+        <v>2.4495</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6441</v>
+        <v>1.4292</v>
       </c>
       <c r="K11" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L11" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="M11" t="n">
-        <v>5.5322</v>
+        <v>3.8787</v>
       </c>
       <c r="N11" t="n">
-        <v>216</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.0626</v>
+        <v>3.6926</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4039</v>
+        <v>1.276</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1746</v>
+        <v>1.029</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0626</v>
+        <v>3.6926</v>
       </c>
       <c r="F12" t="n">
-        <v>4.0353</v>
+        <v>4.1404</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0273</v>
+        <v>-0.4478</v>
       </c>
       <c r="H12" t="n">
-        <v>4.0353</v>
+        <v>5.7316</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2707</v>
+        <v>6.2128</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0273</v>
+        <v>-0.4478</v>
       </c>
       <c r="K12" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L12" t="n">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="M12" t="n">
-        <v>3.298</v>
+        <v>5.765</v>
       </c>
       <c r="N12" t="n">
-        <v>300</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.0121</v>
+        <v>3.6785</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3864</v>
+        <v>1.2711</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1545</v>
+        <v>1.0226</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0121</v>
+        <v>3.6785</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6919</v>
+        <v>3.6082</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3202</v>
+        <v>0.0703</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6919</v>
+        <v>4.5632</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7146</v>
+        <v>4.9462</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3202</v>
+        <v>0.0703</v>
       </c>
       <c r="K13" t="n">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="L13" t="n">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="M13" t="n">
-        <v>4.0348</v>
+        <v>5.0165</v>
       </c>
       <c r="N13" t="n">
         <v>216</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.9995</v>
+        <v>3.4845</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3821</v>
+        <v>1.2041</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1495</v>
+        <v>0.9351</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9995</v>
+        <v>3.4845</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3002</v>
+        <v>3.3873</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6993</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3002</v>
+        <v>6.4483</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3002</v>
+        <v>3.3528</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6993</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="L14" t="n">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9995</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>257</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.4822</v>
+        <v>3.1352</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2033</v>
+        <v>1.0834</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9434</v>
+        <v>0.7774</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4822</v>
+        <v>3.1352</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4822</v>
+        <v>3.1352</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4822</v>
+        <v>3.5245</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4822</v>
+        <v>3.5245</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4822</v>
+        <v>3.5245</v>
       </c>
       <c r="N15" t="n">
         <v>128</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0546</v>
+        <v>3.0073</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0555</v>
+        <v>1.0392</v>
       </c>
       <c r="D16" t="n">
-        <v>0.773</v>
+        <v>0.7196</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0546</v>
+        <v>3.0073</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6682</v>
+        <v>2.6533</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3864</v>
+        <v>0.354</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6682</v>
+        <v>2.6533</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6907</v>
+        <v>2.7624</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3864</v>
+        <v>0.354</v>
       </c>
       <c r="K16" t="n">
         <v>152</v>
@@ -1173,7 +1173,7 @@
         <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0771</v>
+        <v>3.1164</v>
       </c>
       <c r="N16" t="n">
         <v>199</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9155</v>
+        <v>2.881</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0075</v>
+        <v>0.9956</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7176</v>
+        <v>0.6626</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9155</v>
+        <v>2.881</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4175</v>
+        <v>0.8289</v>
       </c>
       <c r="G17" t="n">
-        <v>2.498</v>
+        <v>2.0521</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4175</v>
+        <v>0.8289</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4175</v>
+        <v>0.8289</v>
       </c>
       <c r="J17" t="n">
-        <v>2.498</v>
+        <v>2.0521</v>
       </c>
       <c r="K17" t="n">
         <v>124</v>
@@ -1219,7 +1219,7 @@
         <v>133</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9155</v>
+        <v>2.881</v>
       </c>
       <c r="N17" t="n">
         <v>257</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1657</v>
+        <v>2.584</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7484</v>
+        <v>0.8929</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4189</v>
+        <v>0.5285</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1657</v>
+        <v>2.584</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1657</v>
+        <v>2.584</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1657</v>
+        <v>2.584</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1657</v>
+        <v>2.584</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1657</v>
+        <v>2.584</v>
       </c>
       <c r="N18" t="n">
         <v>128</v>
@@ -1274,415 +1274,415 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0625</v>
+        <v>2.4878</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7127</v>
+        <v>0.8597</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3778</v>
+        <v>0.4851</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0625</v>
+        <v>2.4878</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8723</v>
+        <v>-0.2735</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1902</v>
+        <v>2.7613</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8723</v>
+        <v>-0.2735</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8881</v>
+        <v>-0.1422</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1902</v>
+        <v>2.7613</v>
       </c>
       <c r="K19" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="L19" t="n">
-        <v>47</v>
+        <v>155</v>
       </c>
       <c r="M19" t="n">
-        <v>2.0783</v>
+        <v>2.6191</v>
       </c>
       <c r="N19" t="n">
-        <v>199</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.007</v>
+        <v>2.1491</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6935</v>
+        <v>0.7426</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3557</v>
+        <v>0.3322</v>
       </c>
       <c r="E20" t="n">
-        <v>2.007</v>
+        <v>2.1491</v>
       </c>
       <c r="F20" t="n">
-        <v>2.007</v>
+        <v>1.965</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1841</v>
       </c>
       <c r="H20" t="n">
-        <v>2.007</v>
+        <v>1.965</v>
       </c>
       <c r="I20" t="n">
-        <v>2.007</v>
+        <v>2.0458</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1841</v>
       </c>
       <c r="K20" t="n">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M20" t="n">
-        <v>2.007</v>
+        <v>2.2299</v>
       </c>
       <c r="N20" t="n">
-        <v>114</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0048</v>
+        <v>2.0403</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6928</v>
+        <v>0.705</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3548</v>
+        <v>0.2831</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0048</v>
+        <v>2.0403</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4334</v>
+        <v>2.0403</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4382</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4334</v>
+        <v>2.0403</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3513</v>
+        <v>2.0403</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4382</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="L21" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0869</v>
+        <v>2.0403</v>
       </c>
       <c r="N21" t="n">
-        <v>280</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9909</v>
+        <v>1.9273</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.666</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3493</v>
+        <v>0.2321</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9909</v>
+        <v>1.9273</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9909</v>
+        <v>1.9273</v>
       </c>
       <c r="G22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9909</v>
+        <v>1.9273</v>
       </c>
       <c r="I22" t="n">
-        <v>3.0415</v>
+        <v>1.9273</v>
       </c>
       <c r="J22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L22" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0415</v>
+        <v>1.9273</v>
       </c>
       <c r="N22" t="n">
-        <v>216</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6994</v>
+        <v>1.9095</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2331</v>
+        <v>0.224</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6994</v>
+        <v>1.9095</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6994</v>
+        <v>2.9095</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6994</v>
+        <v>3.0289</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6994</v>
+        <v>3.2832</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K23" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6994</v>
+        <v>2.2832</v>
       </c>
       <c r="N23" t="n">
-        <v>138</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.52</v>
+        <v>1.7846</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5253</v>
+        <v>0.6167</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1617</v>
+        <v>0.1676</v>
       </c>
       <c r="E24" t="n">
-        <v>1.52</v>
+        <v>1.7846</v>
       </c>
       <c r="F24" t="n">
-        <v>1.52</v>
+        <v>1.7846</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.52</v>
+        <v>1.7846</v>
       </c>
       <c r="I24" t="n">
-        <v>1.52</v>
+        <v>1.7846</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.52</v>
+        <v>1.7846</v>
       </c>
       <c r="N24" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3514</v>
+        <v>1.6963</v>
       </c>
       <c r="C25" t="n">
-        <v>0.467</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0945</v>
+        <v>0.1278</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3514</v>
+        <v>1.6963</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3514</v>
+        <v>2.2067</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.5104</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3514</v>
+        <v>2.2067</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3514</v>
+        <v>2.3919</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.5104</v>
       </c>
       <c r="K25" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3514</v>
+        <v>1.8815</v>
       </c>
       <c r="N25" t="n">
-        <v>138</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3391</v>
+        <v>1.6552</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4627</v>
+        <v>0.572</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0896</v>
+        <v>0.1092</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3391</v>
+        <v>1.6552</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0915</v>
+        <v>2.2665</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7524</v>
+        <v>-0.6113</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0915</v>
+        <v>2.4993</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1269</v>
+        <v>1.2995</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7524</v>
+        <v>-0.6113</v>
       </c>
       <c r="K26" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L26" t="n">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3745</v>
+        <v>0.6882000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>216</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2359</v>
+        <v>1.6449</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4271</v>
+        <v>0.5684</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0485</v>
+        <v>0.1046</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2359</v>
+        <v>1.6449</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2359</v>
+        <v>1.6449</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2359</v>
+        <v>1.6449</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2359</v>
+        <v>1.6449</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2359</v>
+        <v>1.6449</v>
       </c>
       <c r="N27" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1439</v>
+        <v>1.5275</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3953</v>
+        <v>0.5278</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0118</v>
+        <v>0.0516</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1439</v>
+        <v>1.5275</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1439</v>
+        <v>1.5275</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1439</v>
+        <v>1.5275</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1439</v>
+        <v>1.5275</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1439</v>
+        <v>1.5275</v>
       </c>
       <c r="N28" t="n">
         <v>138</v>
@@ -1734,231 +1734,231 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8705000000000001</v>
+        <v>1.4976</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3008</v>
+        <v>0.5175</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.0381</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8705000000000001</v>
+        <v>1.4976</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9735</v>
+        <v>1.4976</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.103</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9735</v>
+        <v>1.4976</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9899</v>
+        <v>1.4976</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.103</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L29" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8869</v>
+        <v>1.4976</v>
       </c>
       <c r="N29" t="n">
-        <v>216</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.832</v>
+        <v>1.3558</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2875</v>
+        <v>0.4685</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1124</v>
+        <v>-0.0259</v>
       </c>
       <c r="E30" t="n">
-        <v>0.832</v>
+        <v>1.3558</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8033</v>
+        <v>1.3558</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0287</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8033</v>
+        <v>1.3558</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8033</v>
+        <v>1.3558</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0287</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="L30" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.832</v>
+        <v>1.3558</v>
       </c>
       <c r="N30" t="n">
-        <v>257</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8118</v>
+        <v>1.3359</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2805</v>
+        <v>0.4616</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1205</v>
+        <v>-0.0349</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8118</v>
+        <v>1.3359</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8118</v>
+        <v>0.8942</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.4417</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8118</v>
+        <v>0.8942</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8118</v>
+        <v>0.8942</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.4417</v>
       </c>
       <c r="K31" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8118</v>
+        <v>1.3359</v>
       </c>
       <c r="N31" t="n">
-        <v>114</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7205</v>
+        <v>1.3303</v>
       </c>
       <c r="C32" t="n">
-        <v>0.249</v>
+        <v>0.4597</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1569</v>
+        <v>-0.0375</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7205</v>
+        <v>1.3303</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7205</v>
+        <v>1.3886</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.0583</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7205</v>
+        <v>1.3886</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7205</v>
+        <v>1.5052</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.0583</v>
       </c>
       <c r="K32" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7205</v>
+        <v>1.4469</v>
       </c>
       <c r="N32" t="n">
-        <v>138</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7037</v>
+        <v>1.2142</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2432</v>
+        <v>0.4196</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1636</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7037</v>
+        <v>1.2142</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3893</v>
+        <v>1.2142</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.6856</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3893</v>
+        <v>1.2142</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1261</v>
+        <v>1.2142</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6856</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="L33" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4405000000000001</v>
+        <v>1.2142</v>
       </c>
       <c r="N33" t="n">
-        <v>300</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5976</v>
+        <v>1.1775</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2065</v>
+        <v>0.4069</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2058</v>
+        <v>-0.1064</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5976</v>
+        <v>1.1775</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5976</v>
+        <v>1.1775</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5976</v>
+        <v>1.1775</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5976</v>
+        <v>1.1775</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5976</v>
+        <v>1.1775</v>
       </c>
       <c r="N34" t="n">
         <v>138</v>
@@ -2010,139 +2010,139 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5494</v>
+        <v>0.9901</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1899</v>
+        <v>0.3421</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.225</v>
+        <v>-0.191</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5494</v>
+        <v>0.9901</v>
       </c>
       <c r="F35" t="n">
-        <v>1.5494</v>
+        <v>0.4762</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>0.5139</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5494</v>
+        <v>0.4762</v>
       </c>
       <c r="I35" t="n">
-        <v>1.5625</v>
+        <v>0.4762</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>0.5139</v>
       </c>
       <c r="K35" t="n">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="L35" t="n">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5625</v>
+        <v>0.9901</v>
       </c>
       <c r="N35" t="n">
-        <v>199</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5029</v>
+        <v>0.8424</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1738</v>
+        <v>0.2911</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2436</v>
+        <v>-0.2577</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5029</v>
+        <v>0.8424</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0912</v>
+        <v>0.8424</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4117</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0912</v>
+        <v>0.8424</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0912</v>
+        <v>0.8424</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4117</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="L36" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5029</v>
+        <v>0.8424</v>
       </c>
       <c r="N36" t="n">
-        <v>257</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.486</v>
+        <v>0.731</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1679</v>
+        <v>0.2526</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2503</v>
+        <v>-0.308</v>
       </c>
       <c r="E37" t="n">
-        <v>0.486</v>
+        <v>0.731</v>
       </c>
       <c r="F37" t="n">
-        <v>0.486</v>
+        <v>0.731</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.486</v>
+        <v>0.731</v>
       </c>
       <c r="I37" t="n">
-        <v>0.486</v>
+        <v>0.731</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.486</v>
+        <v>0.731</v>
       </c>
       <c r="N37" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4432</v>
+        <v>0.6837</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1532</v>
+        <v>0.2363</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2673</v>
+        <v>-0.3294</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4432</v>
+        <v>0.6837</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4432</v>
+        <v>0.6837</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4432</v>
+        <v>0.6837</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4432</v>
+        <v>0.6837</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4432</v>
+        <v>0.6837</v>
       </c>
       <c r="N38" t="n">
         <v>114</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3675</v>
+        <v>0.6776</v>
       </c>
       <c r="C39" t="n">
-        <v>0.127</v>
+        <v>0.2342</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2975</v>
+        <v>-0.3321</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3675</v>
+        <v>0.6776</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3675</v>
+        <v>0.6776</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3675</v>
+        <v>0.6776</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3675</v>
+        <v>0.6776</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3675</v>
+        <v>0.6776</v>
       </c>
       <c r="N39" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3208</v>
+        <v>0.644</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1109</v>
+        <v>0.2225</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3161</v>
+        <v>-0.3473</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3208</v>
+        <v>0.644</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3208</v>
+        <v>0.644</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3208</v>
+        <v>0.644</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3208</v>
+        <v>0.644</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3208</v>
+        <v>0.644</v>
       </c>
       <c r="N40" t="n">
         <v>138</v>
@@ -2286,139 +2286,139 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.211</v>
+        <v>0.6133</v>
       </c>
       <c r="C41" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2119</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3598</v>
+        <v>-0.3611</v>
       </c>
       <c r="E41" t="n">
-        <v>0.211</v>
+        <v>0.6133</v>
       </c>
       <c r="F41" t="n">
-        <v>0.211</v>
+        <v>0.6133</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.211</v>
+        <v>0.6133</v>
       </c>
       <c r="I41" t="n">
-        <v>0.211</v>
+        <v>0.6133</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.211</v>
+        <v>0.6133</v>
       </c>
       <c r="N41" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1509</v>
+        <v>0.5753</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0521</v>
+        <v>0.1988</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3838</v>
+        <v>-0.3783</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1509</v>
+        <v>0.5753</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.2982</v>
+        <v>1.5753</v>
       </c>
       <c r="G42" t="n">
-        <v>1.4491</v>
+        <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.2982</v>
+        <v>1.5753</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.0522</v>
+        <v>1.6401</v>
       </c>
       <c r="J42" t="n">
-        <v>1.4491</v>
+        <v>-1</v>
       </c>
       <c r="K42" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="L42" t="n">
-        <v>156</v>
+        <v>47</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3969</v>
+        <v>0.6400999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>300</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1021</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0353</v>
+        <v>0.1858</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4032</v>
+        <v>-0.3952</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1021</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7514</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.6493</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7514</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7577</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6493</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="L43" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1084000000000001</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>199</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44">
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0581</v>
+        <v>0.4845</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0201</v>
+        <v>0.1674</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4208</v>
+        <v>-0.4193</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0581</v>
+        <v>0.4845</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0581</v>
+        <v>0.4845</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0581</v>
+        <v>0.4845</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0581</v>
+        <v>0.4845</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0581</v>
+        <v>0.4845</v>
       </c>
       <c r="N44" t="n">
         <v>114</v>
@@ -2470,93 +2470,93 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0467</v>
+        <v>0.4054</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0161</v>
+        <v>0.1401</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4253</v>
+        <v>-0.455</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0467</v>
+        <v>0.4054</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0467</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.459</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0467</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0467</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.459</v>
       </c>
       <c r="K45" t="n">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0467</v>
+        <v>0.441</v>
       </c>
       <c r="N45" t="n">
-        <v>128</v>
+        <v>199</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0299</v>
+        <v>0.3351</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0103</v>
+        <v>0.1158</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.432</v>
+        <v>-0.4867</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0299</v>
+        <v>0.3351</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0299</v>
+        <v>0.3351</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0299</v>
+        <v>0.3351</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0299</v>
+        <v>0.3351</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0299</v>
+        <v>0.3351</v>
       </c>
       <c r="N46" t="n">
-        <v>138</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0106</v>
+        <v>0.3349</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0037</v>
+        <v>0.1157</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4481</v>
+        <v>-0.4868</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0106</v>
+        <v>0.3349</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0106</v>
+        <v>0.3349</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0106</v>
+        <v>0.3349</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0106</v>
+        <v>0.3349</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0106</v>
+        <v>0.3349</v>
       </c>
       <c r="N47" t="n">
         <v>134</v>
@@ -2608,139 +2608,139 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0708</v>
+        <v>0.3159</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0245</v>
+        <v>0.1092</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4721</v>
+        <v>-0.4954</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0708</v>
+        <v>0.3159</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0708</v>
+        <v>-0.2968</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.6127</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0708</v>
+        <v>-0.2968</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0708</v>
+        <v>-0.1543</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.6127</v>
       </c>
       <c r="K48" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0708</v>
+        <v>0.4584</v>
       </c>
       <c r="N48" t="n">
-        <v>138</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.3101</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0261</v>
+        <v>0.1072</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4739</v>
+        <v>-0.498</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.3101</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.6081</v>
+        <v>0.3101</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5327</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.6081</v>
+        <v>0.3101</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4929</v>
+        <v>0.3101</v>
       </c>
       <c r="J49" t="n">
-        <v>0.5327</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L49" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.03979999999999995</v>
+        <v>0.3101</v>
       </c>
       <c r="N49" t="n">
-        <v>300</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1593</v>
+        <v>0.1453</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.055</v>
+        <v>0.0502</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5074</v>
+        <v>-0.5724</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1593</v>
+        <v>0.1453</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1593</v>
+        <v>-1.2278</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1.3731</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1593</v>
+        <v>-1.2278</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1593</v>
+        <v>-0.6384</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1.3731</v>
       </c>
       <c r="K50" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1593</v>
+        <v>0.7347</v>
       </c>
       <c r="N50" t="n">
-        <v>116</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.383</v>
+        <v>0.0366</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1323</v>
+        <v>0.0126</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5965</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.383</v>
+        <v>0.0366</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.383</v>
+        <v>0.0366</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.383</v>
+        <v>0.0366</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.383</v>
+        <v>0.0366</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.383</v>
+        <v>0.0366</v>
       </c>
       <c r="N51" t="n">
         <v>116</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.5584</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.193</v>
+        <v>-0.0237</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6664</v>
+        <v>-0.669</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5584</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.5584</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5584</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.5584</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.5584</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="N52" t="n">
         <v>134</v>
@@ -2838,47 +2838,47 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.6048</v>
+        <v>-0.073</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.209</v>
+        <v>-0.0252</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6849</v>
+        <v>-0.671</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.6048</v>
+        <v>-0.073</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.4841</v>
+        <v>-0.073</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8793</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.4841</v>
+        <v>-0.073</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.2029</v>
+        <v>-0.073</v>
       </c>
       <c r="J53" t="n">
-        <v>0.8793</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="L53" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3236000000000001</v>
+        <v>-0.073</v>
       </c>
       <c r="N53" t="n">
-        <v>280</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.6932</v>
+        <v>-0.1158</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2395</v>
+        <v>-0.04</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.7201</v>
+        <v>-0.6903</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.6932</v>
+        <v>-0.1158</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.6932</v>
+        <v>-0.1158</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.6932</v>
+        <v>-0.1158</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.6932</v>
+        <v>-0.1158</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.6932</v>
+        <v>-0.1158</v>
       </c>
       <c r="N54" t="n">
         <v>116</v>
@@ -2930,277 +2930,277 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.7863</v>
+        <v>-0.1327</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2717</v>
+        <v>-0.0459</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7572</v>
+        <v>-0.6979</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.7863</v>
+        <v>-0.1327</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.7863</v>
+        <v>-1.1366</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1.0039</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.7863</v>
+        <v>-1.1366</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.7863</v>
+        <v>-0.591</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1.0039</v>
       </c>
       <c r="K55" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.7863</v>
+        <v>0.4129</v>
       </c>
       <c r="N55" t="n">
-        <v>134</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.8441</v>
+        <v>-0.2558</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2917</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7802</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.8441</v>
+        <v>-0.2558</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.8441</v>
+        <v>-0.2558</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.8441</v>
+        <v>-0.2558</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8441</v>
+        <v>-0.2558</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.8441</v>
+        <v>-0.2558</v>
       </c>
       <c r="N56" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jasonR</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.2778</v>
+        <v>-0.737</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.4416</v>
+        <v>-0.2547</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.953</v>
+        <v>-0.9707</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.2778</v>
+        <v>-0.737</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.2778</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-0.1448</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.2778</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.2778</v>
+        <v>-0.6166</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-0.1448</v>
       </c>
       <c r="K57" t="n">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.2778</v>
+        <v>-0.7614000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>138</v>
+        <v>216</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>jasonR</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.6217</v>
+        <v>-0.7601</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.5604</v>
+        <v>-0.2627</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.09</v>
+        <v>-0.9812</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.6217</v>
+        <v>-0.7601</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.296</v>
+        <v>-0.7601</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.3257</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.296</v>
+        <v>-0.7601</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.3069</v>
+        <v>-0.7601</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.3257</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="L58" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.6326</v>
+        <v>-0.7601</v>
       </c>
       <c r="N58" t="n">
-        <v>216</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LILMAN</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.6822</v>
+        <v>-1.099</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.5813</v>
+        <v>-0.3798</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.1141</v>
+        <v>-1.1342</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.6822</v>
+        <v>-1.099</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.6822</v>
+        <v>-0.4171</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-0.6819</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.6822</v>
+        <v>-0.4171</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.6822</v>
+        <v>-0.4343</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>-0.6819</v>
       </c>
       <c r="K59" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.6822</v>
+        <v>-1.1162</v>
       </c>
       <c r="N59" t="n">
-        <v>134</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>LILMAN</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.7245</v>
+        <v>-1.1535</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.5959</v>
+        <v>-0.3986</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.131</v>
+        <v>-1.1588</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.7245</v>
+        <v>-1.1535</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.743</v>
+        <v>-1.1535</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.9815</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.743</v>
+        <v>-1.1535</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7493</v>
+        <v>-1.1535</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.9815</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="L60" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.7308</v>
+        <v>-1.1535</v>
       </c>
       <c r="N60" t="n">
-        <v>199</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61">
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.8017</v>
+        <v>-1.2064</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.6226</v>
+        <v>-0.4169</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.1617</v>
+        <v>-1.1826</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.8017</v>
+        <v>-1.2064</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.8017</v>
+        <v>-1.2064</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.8017</v>
+        <v>-1.2064</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.8017</v>
+        <v>-1.2064</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-1.8017</v>
+        <v>-1.2064</v>
       </c>
       <c r="N61" t="n">
         <v>134</v>
@@ -3349,10 +3349,10 @@
         <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5407</v>
+        <v>1.3497</v>
       </c>
       <c r="J2" t="n">
-        <v>44.6803</v>
+        <v>39.1413</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4226</v>
+        <v>0.4667</v>
       </c>
       <c r="J3" t="n">
-        <v>12.2554</v>
+        <v>13.5343</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2179</v>
+        <v>0.2792</v>
       </c>
       <c r="J4" t="n">
-        <v>6.3191</v>
+        <v>8.0968</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1149</v>
+        <v>-0.043</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.3321</v>
+        <v>-1.247</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.98</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2156</v>
+        <v>-0.1391</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.2524</v>
+        <v>-4.0339</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.11</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2749</v>
+        <v>0.2909</v>
       </c>
       <c r="J7" t="n">
-        <v>7.9721</v>
+        <v>8.4361</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.04</v>
+        <v>-0.0431</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.16</v>
+        <v>-1.2499</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.92</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1509</v>
+        <v>-0.1041</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.3761</v>
+        <v>-3.0189</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2323</v>
+        <v>-0.1472</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.7367</v>
+        <v>-4.2688</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4768</v>
+        <v>-0.3076</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.8272</v>
+        <v>-8.920400000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.53</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1889</v>
+        <v>1.1411</v>
       </c>
       <c r="J12" t="n">
-        <v>24.9669</v>
+        <v>23.9631</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.45</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0201</v>
+        <v>1.0431</v>
       </c>
       <c r="J13" t="n">
-        <v>21.4221</v>
+        <v>21.9051</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.39</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8686</v>
+        <v>0.9487</v>
       </c>
       <c r="J14" t="n">
-        <v>18.2406</v>
+        <v>19.9227</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>1.37</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8168</v>
+        <v>0.9097</v>
       </c>
       <c r="J15" t="n">
-        <v>17.1528</v>
+        <v>19.1037</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>1.23</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4899</v>
+        <v>0.5944</v>
       </c>
       <c r="J16" t="n">
-        <v>10.2879</v>
+        <v>12.4824</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0039</v>
+        <v>-0.0321</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0819</v>
+        <v>-0.6741</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>0.79</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2705</v>
+        <v>-0.2159</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.6805</v>
+        <v>-4.5339</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>0.71</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4196</v>
+        <v>-0.2913</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.8116</v>
+        <v>-6.1173</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>0.63</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5441</v>
+        <v>-0.3657</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.4261</v>
+        <v>-7.6797</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6409</v>
+        <v>-0.4312</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.4589</v>
+        <v>-9.055199999999999</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.41</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6737</v>
+        <v>0.6325</v>
       </c>
       <c r="J22" t="n">
-        <v>20.211</v>
+        <v>18.975</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.13</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2945</v>
+        <v>0.2448</v>
       </c>
       <c r="J23" t="n">
-        <v>8.835000000000001</v>
+        <v>7.344</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0645</v>
+        <v>0.0352</v>
       </c>
       <c r="J24" t="n">
-        <v>1.935</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.68</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5376</v>
+        <v>-0.3498</v>
       </c>
       <c r="J25" t="n">
-        <v>-16.128</v>
+        <v>-10.494</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.54</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7113</v>
+        <v>-0.479</v>
       </c>
       <c r="J26" t="n">
-        <v>-21.339</v>
+        <v>-14.37</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7059</v>
+        <v>0.6262</v>
       </c>
       <c r="J27" t="n">
-        <v>21.177</v>
+        <v>18.786</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.34</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5118</v>
+        <v>0.4469</v>
       </c>
       <c r="J28" t="n">
-        <v>15.354</v>
+        <v>13.407</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2217</v>
+        <v>0.221</v>
       </c>
       <c r="J29" t="n">
-        <v>6.651</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.156</v>
+        <v>0.1676</v>
       </c>
       <c r="J30" t="n">
-        <v>4.68</v>
+        <v>5.028</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3619</v>
+        <v>-0.2182</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.857</v>
+        <v>-6.546</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.58</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2238</v>
+        <v>1.1836</v>
       </c>
       <c r="J32" t="n">
-        <v>23.2522</v>
+        <v>22.4884</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.57</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2027</v>
+        <v>1.1721</v>
       </c>
       <c r="J33" t="n">
-        <v>22.8513</v>
+        <v>22.2699</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1112</v>
+        <v>1.1265</v>
       </c>
       <c r="J34" t="n">
-        <v>21.1128</v>
+        <v>21.4035</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>1.53</v>
       </c>
       <c r="I35" t="n">
-        <v>1.1112</v>
+        <v>1.1265</v>
       </c>
       <c r="J35" t="n">
-        <v>21.1128</v>
+        <v>21.4035</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>1.42</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8602</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>16.3438</v>
+        <v>18.7036</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>0.85</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1162</v>
+        <v>-0.1203</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.2078</v>
+        <v>-2.2857</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2118</v>
+        <v>-0.1887</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.0242</v>
+        <v>-3.5853</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>0.63</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4682</v>
+        <v>-0.35</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.895799999999999</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.5</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6857</v>
+        <v>-0.4684</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.0283</v>
+        <v>-8.8996</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.32</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9197</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.4743</v>
+        <v>-12.1524</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.82</v>
       </c>
       <c r="I42" t="n">
-        <v>1.7176</v>
+        <v>1.2097</v>
       </c>
       <c r="J42" t="n">
-        <v>36.0696</v>
+        <v>25.4037</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.35</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7689</v>
+        <v>0.6483</v>
       </c>
       <c r="J43" t="n">
-        <v>16.1469</v>
+        <v>13.6143</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.5833</v>
       </c>
       <c r="J44" t="n">
-        <v>13.7067</v>
+        <v>12.2493</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6065</v>
+        <v>0.5565</v>
       </c>
       <c r="J45" t="n">
-        <v>12.7365</v>
+        <v>11.6865</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>1.22</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4663</v>
+        <v>0.4732</v>
       </c>
       <c r="J46" t="n">
-        <v>9.792299999999999</v>
+        <v>9.937200000000001</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>0.97</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0421</v>
+        <v>-0.0055</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8841</v>
+        <v>-0.1155</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>0.92</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0551</v>
+        <v>-0.0727</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.1571</v>
+        <v>-1.5267</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.66</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5026</v>
+        <v>-0.3385</v>
       </c>
       <c r="J49" t="n">
-        <v>-10.5546</v>
+        <v>-7.1085</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.57</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6293</v>
+        <v>-0.4228</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.2153</v>
+        <v>-8.8788</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6559</v>
+        <v>-0.4415</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.7739</v>
+        <v>-9.2715</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9018</v>
+        <v>0.6602</v>
       </c>
       <c r="J52" t="n">
-        <v>32.4648</v>
+        <v>23.7672</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.27</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7638</v>
+        <v>0.5767</v>
       </c>
       <c r="J53" t="n">
-        <v>27.4968</v>
+        <v>20.7612</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.14</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4208</v>
+        <v>0.387</v>
       </c>
       <c r="J54" t="n">
-        <v>15.1488</v>
+        <v>13.932</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1519</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.4684</v>
+        <v>-3.042</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.9</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4521</v>
+        <v>-0.3843</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.2756</v>
+        <v>-13.8348</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.32</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5309</v>
+        <v>0.5112</v>
       </c>
       <c r="J57" t="n">
-        <v>19.1124</v>
+        <v>18.4032</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.14</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2764</v>
+        <v>0.3134</v>
       </c>
       <c r="J58" t="n">
-        <v>9.9504</v>
+        <v>11.2824</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.09</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1914</v>
+        <v>0.2161</v>
       </c>
       <c r="J59" t="n">
-        <v>6.8904</v>
+        <v>7.7796</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1103</v>
+        <v>0.1319</v>
       </c>
       <c r="J60" t="n">
-        <v>3.9708</v>
+        <v>4.7484</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6158</v>
+        <v>-0.4064</v>
       </c>
       <c r="J61" t="n">
-        <v>-22.1688</v>
+        <v>-14.6304</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.37</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9909</v>
+        <v>0.7153</v>
       </c>
       <c r="J62" t="n">
-        <v>27.7452</v>
+        <v>20.0284</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.15</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4532</v>
+        <v>0.4024</v>
       </c>
       <c r="J63" t="n">
-        <v>12.6896</v>
+        <v>11.2672</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4532</v>
+        <v>0.4024</v>
       </c>
       <c r="J64" t="n">
-        <v>12.6896</v>
+        <v>11.2672</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1936</v>
+        <v>-0.1251</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.4208</v>
+        <v>-3.5028</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.97</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2317</v>
+        <v>-0.1623</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.4876</v>
+        <v>-4.5444</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.2</v>
       </c>
       <c r="I67" t="n">
-        <v>0.376</v>
+        <v>0.3917</v>
       </c>
       <c r="J67" t="n">
-        <v>10.528</v>
+        <v>10.9676</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.19</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3614</v>
+        <v>0.3809</v>
       </c>
       <c r="J68" t="n">
-        <v>10.1192</v>
+        <v>10.6652</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.08</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1836</v>
+        <v>0.2001</v>
       </c>
       <c r="J69" t="n">
-        <v>5.1408</v>
+        <v>5.6028</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.91</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2175</v>
+        <v>-0.1255</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.09</v>
+        <v>-3.514</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4848</v>
+        <v>-0.3101</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.5744</v>
+        <v>-8.6828</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.53</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3067</v>
+        <v>0.9196</v>
       </c>
       <c r="J72" t="n">
-        <v>36.5876</v>
+        <v>25.7488</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5738</v>
+        <v>0.4727</v>
       </c>
       <c r="J73" t="n">
-        <v>16.0664</v>
+        <v>13.2356</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.12</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3249</v>
+        <v>0.3543</v>
       </c>
       <c r="J74" t="n">
-        <v>9.097200000000001</v>
+        <v>9.920400000000001</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1034</v>
+        <v>-0.0359</v>
       </c>
       <c r="J75" t="n">
-        <v>-2.8952</v>
+        <v>-1.0052</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.9</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4604</v>
+        <v>-0.3907</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.8912</v>
+        <v>-10.9396</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.31</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5414</v>
+        <v>0.5168</v>
       </c>
       <c r="J77" t="n">
-        <v>15.1592</v>
+        <v>14.4704</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2864</v>
+        <v>0.3125</v>
       </c>
       <c r="J78" t="n">
-        <v>8.0192</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2539</v>
+        <v>-0.1534</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.1092</v>
+        <v>-4.2952</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.82</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3483</v>
+        <v>-0.216</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.7524</v>
+        <v>-6.048</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4622</v>
+        <v>-0.2952</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.9416</v>
+        <v>-8.265599999999999</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.34</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5494</v>
+        <v>0.4146</v>
       </c>
       <c r="J82" t="n">
-        <v>16.482</v>
+        <v>12.438</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.32</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5238</v>
+        <v>0.4005</v>
       </c>
       <c r="J83" t="n">
-        <v>15.714</v>
+        <v>12.015</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.04</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0704</v>
+        <v>0.076</v>
       </c>
       <c r="J84" t="n">
-        <v>2.112</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I85" t="n">
-        <v>0.025</v>
+        <v>0.0405</v>
       </c>
       <c r="J85" t="n">
-        <v>0.75</v>
+        <v>1.215</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.62</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6309</v>
+        <v>-0.4177</v>
       </c>
       <c r="J86" t="n">
-        <v>-18.927</v>
+        <v>-12.531</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.25</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4214</v>
+        <v>0.3627</v>
       </c>
       <c r="J87" t="n">
-        <v>12.642</v>
+        <v>10.881</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>1.23</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3934</v>
+        <v>0.3466</v>
       </c>
       <c r="J88" t="n">
-        <v>11.802</v>
+        <v>10.398</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2034</v>
+        <v>0.1894</v>
       </c>
       <c r="J89" t="n">
-        <v>6.102</v>
+        <v>5.682</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1189</v>
+        <v>0.1292</v>
       </c>
       <c r="J90" t="n">
-        <v>3.567</v>
+        <v>3.876</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3749</v>
+        <v>-0.2295</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.247</v>
+        <v>-6.885</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0732</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.8954</v>
+        <v>-1.9032</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>0.93</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0922</v>
+        <v>-0.0854</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.3972</v>
+        <v>-2.2204</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>0.89</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.167</v>
+        <v>-0.1309</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.342</v>
+        <v>-3.4034</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>0.79</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3549</v>
+        <v>-0.2313</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.227399999999999</v>
+        <v>-6.0138</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.73</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4452</v>
+        <v>-0.2896</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.5752</v>
+        <v>-7.5296</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.54</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2753</v>
+        <v>0.9056</v>
       </c>
       <c r="J97" t="n">
-        <v>33.1578</v>
+        <v>23.5456</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8766</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>22.7916</v>
+        <v>17.2328</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>1.2</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4803</v>
+        <v>0.4619</v>
       </c>
       <c r="J99" t="n">
-        <v>12.4878</v>
+        <v>12.0094</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2951</v>
+        <v>0.3567</v>
       </c>
       <c r="J100" t="n">
-        <v>7.6726</v>
+        <v>9.2742</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>1.05</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0625</v>
+        <v>0.1391</v>
       </c>
       <c r="J101" t="n">
-        <v>1.625</v>
+        <v>3.6166</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>0.73</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.3142</v>
+        <v>-0.257</v>
       </c>
       <c r="J102" t="n">
-        <v>-6.284</v>
+        <v>-5.14</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>0.73</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3142</v>
+        <v>-0.257</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.284</v>
+        <v>-5.14</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3776</v>
+        <v>-0.2968</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.552</v>
+        <v>-5.936</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.59</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5602</v>
+        <v>-0.3875</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.204</v>
+        <v>-7.75</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.43</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7849</v>
+        <v>-0.5375</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.698</v>
+        <v>-10.75</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.83</v>
       </c>
       <c r="I107" t="n">
-        <v>1.6952</v>
+        <v>1.1981</v>
       </c>
       <c r="J107" t="n">
-        <v>33.904</v>
+        <v>23.962</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.61</v>
       </c>
       <c r="I108" t="n">
-        <v>1.295</v>
+        <v>0.9468</v>
       </c>
       <c r="J108" t="n">
-        <v>25.9</v>
+        <v>18.936</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>1.46</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9558</v>
+        <v>0.7731</v>
       </c>
       <c r="J109" t="n">
-        <v>19.116</v>
+        <v>15.462</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>1.44</v>
       </c>
       <c r="I110" t="n">
-        <v>0.9121</v>
+        <v>0.749</v>
       </c>
       <c r="J110" t="n">
-        <v>18.242</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>1.19</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3612</v>
+        <v>0.416</v>
       </c>
       <c r="J111" t="n">
-        <v>7.224</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.57</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3188</v>
+        <v>0.9358</v>
       </c>
       <c r="J112" t="n">
-        <v>30.3324</v>
+        <v>21.5234</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.43</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0353</v>
+        <v>0.7607</v>
       </c>
       <c r="J113" t="n">
-        <v>23.8119</v>
+        <v>17.4961</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.38</v>
       </c>
       <c r="I114" t="n">
-        <v>0.9263</v>
+        <v>0.6969</v>
       </c>
       <c r="J114" t="n">
-        <v>21.3049</v>
+        <v>16.0287</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>1.21</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4883</v>
+        <v>0.4724</v>
       </c>
       <c r="J115" t="n">
-        <v>11.2309</v>
+        <v>10.8652</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6536</v>
+        <v>-0.5899</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.0328</v>
+        <v>-13.5677</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.01</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1423</v>
+        <v>0.1113</v>
       </c>
       <c r="J117" t="n">
-        <v>3.2729</v>
+        <v>2.5599</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>0.92</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0716</v>
+        <v>-0.0814</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.6468</v>
+        <v>-1.8722</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2606</v>
+        <v>-0.2026</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.9938</v>
+        <v>-4.6598</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.62</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5725</v>
+        <v>-0.3816</v>
       </c>
       <c r="J120" t="n">
-        <v>-13.1675</v>
+        <v>-8.7768</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.49</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.741</v>
+        <v>-0.5026</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.043</v>
+        <v>-11.5598</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.49</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1532</v>
+        <v>0.8338</v>
       </c>
       <c r="J122" t="n">
-        <v>27.6768</v>
+        <v>20.0112</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.48</v>
       </c>
       <c r="I123" t="n">
-        <v>1.1327</v>
+        <v>0.8213</v>
       </c>
       <c r="J123" t="n">
-        <v>27.1848</v>
+        <v>19.7112</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.34</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.6437</v>
       </c>
       <c r="J124" t="n">
-        <v>19.8024</v>
+        <v>15.4488</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>1.26</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6065</v>
+        <v>0.5402</v>
       </c>
       <c r="J125" t="n">
-        <v>14.556</v>
+        <v>12.9648</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4185</v>
+        <v>-0.3378</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.044</v>
+        <v>-8.107200000000001</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2618</v>
+        <v>0.2655</v>
       </c>
       <c r="J127" t="n">
-        <v>6.2832</v>
+        <v>6.372</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2441</v>
+        <v>0.2427</v>
       </c>
       <c r="J128" t="n">
-        <v>5.8584</v>
+        <v>5.8248</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.84</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2405</v>
+        <v>-0.1793</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.772</v>
+        <v>-4.3032</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3887</v>
+        <v>-0.2564</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.328799999999999</v>
+        <v>-6.1536</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.37</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8917</v>
+        <v>-0.6186</v>
       </c>
       <c r="J131" t="n">
-        <v>-21.4008</v>
+        <v>-14.8464</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.5</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2607</v>
+        <v>1.1621</v>
       </c>
       <c r="J132" t="n">
-        <v>32.7782</v>
+        <v>30.2146</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9252</v>
+        <v>0.9113</v>
       </c>
       <c r="J133" t="n">
-        <v>24.0552</v>
+        <v>23.6938</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7411</v>
+        <v>0.7226</v>
       </c>
       <c r="J134" t="n">
-        <v>19.2686</v>
+        <v>18.7876</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.87</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5333</v>
+        <v>-0.4688</v>
       </c>
       <c r="J135" t="n">
-        <v>-13.8658</v>
+        <v>-12.1888</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.65</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.0466</v>
+        <v>-1.0275</v>
       </c>
       <c r="J136" t="n">
-        <v>-27.2116</v>
+        <v>-26.715</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.37</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6024</v>
+        <v>0.729</v>
       </c>
       <c r="J137" t="n">
-        <v>15.6624</v>
+        <v>18.954</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.28</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4872</v>
+        <v>0.575</v>
       </c>
       <c r="J138" t="n">
-        <v>12.6672</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.96</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1226</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.1876</v>
+        <v>-1.6952</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4164</v>
+        <v>-0.2612</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.8264</v>
+        <v>-6.7912</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5108</v>
+        <v>-0.329</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.2808</v>
+        <v>-8.554</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>2.06</v>
       </c>
       <c r="I142" t="n">
-        <v>2.0486</v>
+        <v>1.7663</v>
       </c>
       <c r="J142" t="n">
-        <v>49.1664</v>
+        <v>42.3912</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.47</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0798</v>
+        <v>1.0725</v>
       </c>
       <c r="J143" t="n">
-        <v>25.9152</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.36</v>
       </c>
       <c r="I144" t="n">
-        <v>0.8168</v>
+        <v>0.893</v>
       </c>
       <c r="J144" t="n">
-        <v>19.6032</v>
+        <v>21.432</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0746</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="J145" t="n">
-        <v>-1.7904</v>
+        <v>0.2088</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.49</v>
+        <v>-0.4119</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.76</v>
+        <v>-9.8856</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.12</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3443</v>
+        <v>0.3734</v>
       </c>
       <c r="J147" t="n">
-        <v>8.263199999999999</v>
+        <v>8.961600000000001</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1602</v>
+        <v>0.1341</v>
       </c>
       <c r="J148" t="n">
-        <v>3.8448</v>
+        <v>3.2184</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.6</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.604</v>
+        <v>-0.4027</v>
       </c>
       <c r="J149" t="n">
-        <v>-14.496</v>
+        <v>-9.6648</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.6</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.604</v>
+        <v>-0.4027</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.496</v>
+        <v>-9.6648</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.59</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6172</v>
+        <v>-0.412</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.8128</v>
+        <v>-9.888</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5381</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="J152" t="n">
-        <v>13.9906</v>
+        <v>16.7076</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3158</v>
+        <v>0.3573</v>
       </c>
       <c r="J153" t="n">
-        <v>8.210800000000001</v>
+        <v>9.2898</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1638</v>
+        <v>-0.0906</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.2588</v>
+        <v>-2.3556</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2181</v>
+        <v>-0.1257</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.6706</v>
+        <v>-3.2682</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4032</v>
+        <v>-0.2518</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.4832</v>
+        <v>-6.5468</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.31</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8378</v>
+        <v>0.8288</v>
       </c>
       <c r="J157" t="n">
-        <v>21.7828</v>
+        <v>21.5488</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.29</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7915</v>
+        <v>0.7821</v>
       </c>
       <c r="J158" t="n">
-        <v>20.579</v>
+        <v>20.3346</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3177</v>
+        <v>0.3665</v>
       </c>
       <c r="J159" t="n">
-        <v>8.260199999999999</v>
+        <v>9.529</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1015</v>
+        <v>0.1622</v>
       </c>
       <c r="J160" t="n">
-        <v>2.639</v>
+        <v>4.2172</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0319</v>
+        <v>0.0945</v>
       </c>
       <c r="J161" t="n">
-        <v>0.8294</v>
+        <v>2.457</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9966</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>27.9048</v>
+        <v>27.5352</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6743</v>
+        <v>0.6653</v>
       </c>
       <c r="J163" t="n">
-        <v>18.8804</v>
+        <v>18.6284</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3522</v>
+        <v>0.3942</v>
       </c>
       <c r="J164" t="n">
-        <v>9.861599999999999</v>
+        <v>11.0376</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0704</v>
+        <v>0.1307</v>
       </c>
       <c r="J165" t="n">
-        <v>1.9712</v>
+        <v>3.6596</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.98</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2063</v>
+        <v>-0.1329</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.7764</v>
+        <v>-3.7212</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="J167" t="n">
-        <v>16.5256</v>
+        <v>19.88</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.431</v>
+        <v>0.4949</v>
       </c>
       <c r="J168" t="n">
-        <v>12.068</v>
+        <v>13.8572</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>0.8</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3699</v>
+        <v>-0.2326</v>
       </c>
       <c r="J169" t="n">
-        <v>-10.3572</v>
+        <v>-6.5128</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.73</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4693</v>
+        <v>-0.3012</v>
       </c>
       <c r="J170" t="n">
-        <v>-13.1404</v>
+        <v>-8.4336</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.64</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5875</v>
+        <v>-0.3864</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.45</v>
+        <v>-10.8192</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.21</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6612</v>
+        <v>0.625</v>
       </c>
       <c r="J172" t="n">
-        <v>19.836</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3901</v>
+        <v>0.3608</v>
       </c>
       <c r="J173" t="n">
-        <v>11.703</v>
+        <v>10.824</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.03</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0969</v>
+        <v>0.1205</v>
       </c>
       <c r="J174" t="n">
-        <v>2.907</v>
+        <v>3.615</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I175" t="n">
-        <v>0.01</v>
+        <v>0.0437</v>
       </c>
       <c r="J175" t="n">
-        <v>0.3</v>
+        <v>1.311</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.9</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4224</v>
+        <v>-0.3638</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.672</v>
+        <v>-10.914</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.3</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5089</v>
+        <v>0.6048</v>
       </c>
       <c r="J177" t="n">
-        <v>15.267</v>
+        <v>18.144</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.22</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4004</v>
+        <v>0.4645</v>
       </c>
       <c r="J178" t="n">
-        <v>12.012</v>
+        <v>13.935</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.04</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0954</v>
+        <v>0.1108</v>
       </c>
       <c r="J179" t="n">
-        <v>2.862</v>
+        <v>3.324</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.87</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2867</v>
+        <v>-0.1707</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.601000000000001</v>
+        <v>-5.121</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.74</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4737</v>
+        <v>-0.3018</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.211</v>
+        <v>-9.054</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.67</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5867</v>
+        <v>1.3808</v>
       </c>
       <c r="J182" t="n">
-        <v>44.4276</v>
+        <v>38.6624</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.28</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7885</v>
+        <v>0.7705</v>
       </c>
       <c r="J183" t="n">
-        <v>22.078</v>
+        <v>21.574</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.05</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1205</v>
+        <v>0.171</v>
       </c>
       <c r="J184" t="n">
-        <v>3.374</v>
+        <v>4.788</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.87</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5333</v>
+        <v>-0.4688</v>
       </c>
       <c r="J185" t="n">
-        <v>-14.9324</v>
+        <v>-13.1264</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.75</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.827</v>
+        <v>-0.7834</v>
       </c>
       <c r="J186" t="n">
-        <v>-23.156</v>
+        <v>-21.9352</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4093</v>
+        <v>0.4726</v>
       </c>
       <c r="J187" t="n">
-        <v>11.4604</v>
+        <v>13.2328</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2905</v>
+        <v>0.3235</v>
       </c>
       <c r="J188" t="n">
-        <v>8.134</v>
+        <v>9.058</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.03</v>
       </c>
       <c r="I189" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0905</v>
       </c>
       <c r="J189" t="n">
-        <v>2.464</v>
+        <v>2.534</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.85</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3111</v>
+        <v>-0.1889</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.710800000000001</v>
+        <v>-5.2892</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.8</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3854</v>
+        <v>-0.2399</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.7912</v>
+        <v>-6.7172</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>0.86</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0955</v>
+        <v>-0.1052</v>
       </c>
       <c r="J192" t="n">
-        <v>-2.0055</v>
+        <v>-2.2092</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>0.65</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.4271</v>
+        <v>-0.3303</v>
       </c>
       <c r="J193" t="n">
-        <v>-8.969099999999999</v>
+        <v>-6.9363</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.55</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.6093</v>
+        <v>-0.4201</v>
       </c>
       <c r="J194" t="n">
-        <v>-12.7953</v>
+        <v>-8.822100000000001</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.52</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6539</v>
+        <v>-0.4481</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.7319</v>
+        <v>-9.4101</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.47</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.4952</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.2103</v>
+        <v>-10.3992</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>2.23</v>
       </c>
       <c r="I197" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J197" t="n">
-        <v>43.2453</v>
+        <v>38.5098</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.81</v>
       </c>
       <c r="I198" t="n">
-        <v>1.6436</v>
+        <v>1.4396</v>
       </c>
       <c r="J198" t="n">
-        <v>34.5156</v>
+        <v>30.2316</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.38</v>
       </c>
       <c r="I199" t="n">
-        <v>0.7621</v>
+        <v>0.9008</v>
       </c>
       <c r="J199" t="n">
-        <v>16.0041</v>
+        <v>18.9168</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>1.21</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3931</v>
+        <v>0.5112</v>
       </c>
       <c r="J200" t="n">
-        <v>8.255100000000001</v>
+        <v>10.7352</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>1.19</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3468</v>
+        <v>0.4617</v>
       </c>
       <c r="J201" t="n">
-        <v>7.2828</v>
+        <v>9.6957</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>2.22</v>
       </c>
       <c r="I202" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J202" t="n">
-        <v>8.2372</v>
+        <v>7.3352</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>2.08</v>
       </c>
       <c r="I203" t="n">
-        <v>1.9866</v>
+        <v>1.7043</v>
       </c>
       <c r="J203" t="n">
-        <v>7.9464</v>
+        <v>6.8172</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.95</v>
       </c>
       <c r="I204" t="n">
-        <v>1.8178</v>
+        <v>1.5668</v>
       </c>
       <c r="J204" t="n">
-        <v>7.2712</v>
+        <v>6.2672</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.53</v>
       </c>
       <c r="I205" t="n">
-        <v>1.006</v>
+        <v>1.1069</v>
       </c>
       <c r="J205" t="n">
-        <v>4.024</v>
+        <v>4.4276</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4674</v>
+        <v>-0.3872</v>
       </c>
       <c r="J206" t="n">
-        <v>-1.8696</v>
+        <v>-1.5488</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>0.74</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.2816</v>
+        <v>-0.2383</v>
       </c>
       <c r="J207" t="n">
-        <v>-1.1264</v>
+        <v>-0.9532</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.71</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.328</v>
+        <v>-0.2696</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.312</v>
+        <v>-1.0784</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.58</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.5574</v>
+        <v>-0.3917</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.2296</v>
+        <v>-1.5668</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.5</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.6801</v>
+        <v>-0.4657</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.7204</v>
+        <v>-1.8628</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.49</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6943</v>
+        <v>-0.4751</v>
       </c>
       <c r="J211" t="n">
-        <v>-2.7772</v>
+        <v>-1.9004</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6973</v>
+        <v>0.8716</v>
       </c>
       <c r="J212" t="n">
-        <v>3.4865</v>
+        <v>4.358</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.07</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2541</v>
+        <v>0.2543</v>
       </c>
       <c r="J213" t="n">
-        <v>1.2705</v>
+        <v>1.2715</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3437</v>
+        <v>-0.2343</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.7185</v>
+        <v>-1.1715</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.64</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5541</v>
+        <v>-0.3672</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.7705</v>
+        <v>-1.836</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.13</v>
       </c>
       <c r="I216" t="n">
-        <v>-1.1519</v>
+        <v>-0.8315</v>
       </c>
       <c r="J216" t="n">
-        <v>-5.7595</v>
+        <v>-4.1575</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>2.36</v>
       </c>
       <c r="I217" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J217" t="n">
-        <v>10.2965</v>
+        <v>9.169</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.73</v>
       </c>
       <c r="I218" t="n">
-        <v>1.5668</v>
+        <v>1.3771</v>
       </c>
       <c r="J218" t="n">
-        <v>7.834</v>
+        <v>6.8855</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.28</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6031</v>
+        <v>0.7101</v>
       </c>
       <c r="J219" t="n">
-        <v>3.0155</v>
+        <v>3.5505</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>1.03</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0477</v>
+        <v>0.0376</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.2385</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.61</v>
       </c>
       <c r="I221" t="n">
-        <v>-1.172</v>
+        <v>-1.1732</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.86</v>
+        <v>-5.866</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.4</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9822</v>
+        <v>0.9895</v>
       </c>
       <c r="J222" t="n">
-        <v>15.7152</v>
+        <v>15.832</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.35</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8709</v>
+        <v>0.8895</v>
       </c>
       <c r="J223" t="n">
-        <v>13.9344</v>
+        <v>14.232</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6714</v>
+        <v>0.7115</v>
       </c>
       <c r="J224" t="n">
-        <v>10.7424</v>
+        <v>11.384</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5793</v>
+        <v>0.6442</v>
       </c>
       <c r="J225" t="n">
-        <v>9.268800000000001</v>
+        <v>10.3072</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>1.06</v>
       </c>
       <c r="I226" t="n">
-        <v>0.0905</v>
+        <v>0.1686</v>
       </c>
       <c r="J226" t="n">
-        <v>1.448</v>
+        <v>2.6976</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.06</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2178</v>
+        <v>0.2106</v>
       </c>
       <c r="J227" t="n">
-        <v>3.4848</v>
+        <v>3.3696</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.04</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1791</v>
+        <v>0.1621</v>
       </c>
       <c r="J228" t="n">
-        <v>2.8656</v>
+        <v>2.5936</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.82</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2994</v>
+        <v>-0.2003</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.7904</v>
+        <v>-3.2048</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4981</v>
+        <v>-0.3262</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.9696</v>
+        <v>-5.2192</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6052</v>
+        <v>-0.4015</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.683199999999999</v>
+        <v>-6.424</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.06</v>
       </c>
       <c r="I232" t="n">
-        <v>0.19</v>
+        <v>0.1847</v>
       </c>
       <c r="J232" t="n">
-        <v>5.13</v>
+        <v>4.9869</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>0.92</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.144</v>
+        <v>-0.1038</v>
       </c>
       <c r="J233" t="n">
-        <v>-3.888</v>
+        <v>-2.8026</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.88</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2295</v>
+        <v>-0.1466</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.1965</v>
+        <v>-3.9582</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.86</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2645</v>
+        <v>-0.1676</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.1415</v>
+        <v>-4.5252</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2813</v>
+        <v>-0.1779</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.5951</v>
+        <v>-4.8033</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.71</v>
       </c>
       <c r="I237" t="n">
-        <v>1.615</v>
+        <v>1.4005</v>
       </c>
       <c r="J237" t="n">
-        <v>43.605</v>
+        <v>37.8135</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.35</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8988</v>
+        <v>0.903</v>
       </c>
       <c r="J238" t="n">
-        <v>24.2676</v>
+        <v>24.381</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.04</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0444</v>
+        <v>0.1158</v>
       </c>
       <c r="J239" t="n">
-        <v>1.1988</v>
+        <v>3.1266</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>1.02</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0281</v>
+        <v>0.0439</v>
       </c>
       <c r="J240" t="n">
-        <v>-0.7587</v>
+        <v>1.1853</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.95</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.333</v>
+        <v>-0.254</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.991</v>
+        <v>-6.858</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.08</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3118</v>
+        <v>0.3325</v>
       </c>
       <c r="J242" t="n">
-        <v>5.9242</v>
+        <v>6.3175</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>0.79</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2608</v>
+        <v>-0.2126</v>
       </c>
       <c r="J243" t="n">
-        <v>-4.9552</v>
+        <v>-4.0394</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.76</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3097</v>
+        <v>-0.2427</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.8843</v>
+        <v>-4.6113</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.5</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.7146</v>
+        <v>-0.4844</v>
       </c>
       <c r="J245" t="n">
-        <v>-13.5774</v>
+        <v>-9.2036</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.42</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.8152</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="J246" t="n">
-        <v>-15.4888</v>
+        <v>-10.621</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>2.43</v>
       </c>
       <c r="I247" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J247" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>1.3796</v>
+        <v>1.2745</v>
       </c>
       <c r="J248" t="n">
-        <v>26.2124</v>
+        <v>24.2155</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.28</v>
       </c>
       <c r="I249" t="n">
-        <v>0.5576</v>
+        <v>0.6835</v>
       </c>
       <c r="J249" t="n">
-        <v>10.5944</v>
+        <v>12.9865</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.26</v>
       </c>
       <c r="I250" t="n">
-        <v>0.5135</v>
+        <v>0.637</v>
       </c>
       <c r="J250" t="n">
-        <v>9.756500000000001</v>
+        <v>12.103</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>1.04</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.043</v>
+        <v>0.046</v>
       </c>
       <c r="J251" t="n">
-        <v>-0.8169999999999999</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.67</v>
       </c>
       <c r="I252" t="n">
-        <v>1.46</v>
+        <v>1.3082</v>
       </c>
       <c r="J252" t="n">
-        <v>35.04</v>
+        <v>31.3968</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.66</v>
       </c>
       <c r="I253" t="n">
-        <v>1.4414</v>
+        <v>1.2964</v>
       </c>
       <c r="J253" t="n">
-        <v>34.5936</v>
+        <v>31.1136</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>1.38</v>
       </c>
       <c r="I254" t="n">
-        <v>0.8418</v>
+        <v>0.9298</v>
       </c>
       <c r="J254" t="n">
-        <v>20.2032</v>
+        <v>22.3152</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>1.28</v>
       </c>
       <c r="I255" t="n">
-        <v>0.6065</v>
+        <v>0.7117</v>
       </c>
       <c r="J255" t="n">
-        <v>14.556</v>
+        <v>17.0808</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.98</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2784</v>
+        <v>-0.1896</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.6816</v>
+        <v>-4.5504</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>0.95</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0026</v>
+        <v>-0.036</v>
       </c>
       <c r="J257" t="n">
-        <v>-0.0624</v>
+        <v>-0.864</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>0.74</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.3733</v>
+        <v>-0.2656</v>
       </c>
       <c r="J258" t="n">
-        <v>-8.959199999999999</v>
+        <v>-6.3744</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>0.72</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4115</v>
+        <v>-0.2838</v>
       </c>
       <c r="J259" t="n">
-        <v>-9.875999999999999</v>
+        <v>-6.8112</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.7</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4447</v>
+        <v>-0.3023</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.6728</v>
+        <v>-7.2552</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.6</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5911</v>
+        <v>-0.396</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.1864</v>
+        <v>-9.504</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.57</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3002</v>
+        <v>1.2014</v>
       </c>
       <c r="J262" t="n">
-        <v>28.6044</v>
+        <v>26.4308</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.46</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0783</v>
+        <v>1.0657</v>
       </c>
       <c r="J263" t="n">
-        <v>23.7226</v>
+        <v>23.4454</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.42</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9926</v>
+        <v>1.0101</v>
       </c>
       <c r="J264" t="n">
-        <v>21.8372</v>
+        <v>22.2222</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.28</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6405</v>
+        <v>0.7248</v>
       </c>
       <c r="J265" t="n">
-        <v>14.091</v>
+        <v>15.9456</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.9</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5088</v>
+        <v>-0.4329</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.1936</v>
+        <v>-9.5238</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1</v>
       </c>
       <c r="I267" t="n">
-        <v>0.1149</v>
+        <v>0.079</v>
       </c>
       <c r="J267" t="n">
-        <v>2.5278</v>
+        <v>1.738</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>0.88</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1344</v>
+        <v>-0.1249</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.9568</v>
+        <v>-2.7478</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.76</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3399</v>
+        <v>-0.2487</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.4778</v>
+        <v>-5.4714</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.74</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3842</v>
+        <v>-0.2667</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.452400000000001</v>
+        <v>-5.8674</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.39</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.859</v>
+        <v>-0.5926</v>
       </c>
       <c r="J271" t="n">
-        <v>-18.898</v>
+        <v>-13.0372</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.96</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8868</v>
+        <v>1.6009</v>
       </c>
       <c r="J272" t="n">
-        <v>33.9624</v>
+        <v>28.8162</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.85</v>
       </c>
       <c r="I273" t="n">
-        <v>1.7038</v>
+        <v>1.48</v>
       </c>
       <c r="J273" t="n">
-        <v>30.6684</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.8</v>
       </c>
       <c r="I274" t="n">
-        <v>1.6153</v>
+        <v>1.4245</v>
       </c>
       <c r="J274" t="n">
-        <v>29.0754</v>
+        <v>25.641</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>1.42</v>
       </c>
       <c r="I275" t="n">
-        <v>0.8363</v>
+        <v>0.9749</v>
       </c>
       <c r="J275" t="n">
-        <v>15.0534</v>
+        <v>17.5482</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.92</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5029</v>
+        <v>-0.4243</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.052199999999999</v>
+        <v>-7.6374</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>0.83</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1707</v>
+        <v>-0.1574</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.0726</v>
+        <v>-2.8332</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>0.78</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2501</v>
+        <v>-0.2117</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.5018</v>
+        <v>-3.8106</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>0.63</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.5111</v>
+        <v>-0.3551</v>
       </c>
       <c r="J279" t="n">
-        <v>-9.1998</v>
+        <v>-6.3918</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>0.59</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5737</v>
+        <v>-0.3918</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.3266</v>
+        <v>-7.0524</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.47</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7401</v>
+        <v>-0.5042</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.3218</v>
+        <v>-9.0756</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>0.9</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.1249</v>
+        <v>-0.1127</v>
       </c>
       <c r="J282" t="n">
-        <v>-3.2474</v>
+        <v>-2.9302</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>0.86</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1952</v>
+        <v>-0.1567</v>
       </c>
       <c r="J283" t="n">
-        <v>-5.0752</v>
+        <v>-4.0742</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>0.84</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2304</v>
+        <v>-0.1774</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.9904</v>
+        <v>-4.6124</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.83</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2484</v>
+        <v>-0.1875</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.4584</v>
+        <v>-4.875</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.61</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5965</v>
+        <v>-0.3965</v>
       </c>
       <c r="J286" t="n">
-        <v>-15.509</v>
+        <v>-10.309</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.93</v>
       </c>
       <c r="I287" t="n">
-        <v>1.9176</v>
+        <v>1.6168</v>
       </c>
       <c r="J287" t="n">
-        <v>49.8576</v>
+        <v>42.0368</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1403</v>
+        <v>1.1086</v>
       </c>
       <c r="J288" t="n">
-        <v>29.6478</v>
+        <v>28.8236</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1.17</v>
       </c>
       <c r="I289" t="n">
-        <v>0.3542</v>
+        <v>0.4516</v>
       </c>
       <c r="J289" t="n">
-        <v>9.209199999999999</v>
+        <v>11.7416</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>1.13</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2526</v>
+        <v>0.3466</v>
       </c>
       <c r="J290" t="n">
-        <v>6.5676</v>
+        <v>9.0116</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>1.11</v>
       </c>
       <c r="I291" t="n">
-        <v>0.1997</v>
+        <v>0.2918</v>
       </c>
       <c r="J291" t="n">
-        <v>5.1922</v>
+        <v>7.5868</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.5</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1648</v>
+        <v>1.1168</v>
       </c>
       <c r="J292" t="n">
-        <v>25.6256</v>
+        <v>24.5696</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.4</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9529</v>
+        <v>0.9782</v>
       </c>
       <c r="J293" t="n">
-        <v>20.9638</v>
+        <v>21.5204</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.29</v>
       </c>
       <c r="I294" t="n">
-        <v>0.6708</v>
+        <v>0.7487</v>
       </c>
       <c r="J294" t="n">
-        <v>14.7576</v>
+        <v>16.4714</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>1.22</v>
       </c>
       <c r="I295" t="n">
-        <v>0.4974</v>
+        <v>0.5864</v>
       </c>
       <c r="J295" t="n">
-        <v>10.9428</v>
+        <v>12.9008</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>1.18</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3981</v>
+        <v>0.4879</v>
       </c>
       <c r="J296" t="n">
-        <v>8.7582</v>
+        <v>10.7338</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1267</v>
+        <v>0.0935</v>
       </c>
       <c r="J297" t="n">
-        <v>2.7874</v>
+        <v>2.057</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>0.92</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0523</v>
+        <v>-0.0711</v>
       </c>
       <c r="J298" t="n">
-        <v>-1.1506</v>
+        <v>-1.5642</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>0.68</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.4692</v>
+        <v>-0.319</v>
       </c>
       <c r="J299" t="n">
-        <v>-10.3224</v>
+        <v>-7.018</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.54</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.6674</v>
+        <v>-0.4499</v>
       </c>
       <c r="J300" t="n">
-        <v>-14.6828</v>
+        <v>-9.8978</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.5</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7191</v>
+        <v>-0.4872</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.8202</v>
+        <v>-10.7184</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.08</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2224</v>
+        <v>0.226</v>
       </c>
       <c r="J302" t="n">
-        <v>6.4496</v>
+        <v>6.554</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.01</v>
       </c>
       <c r="I303" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0533</v>
       </c>
       <c r="J303" t="n">
-        <v>2.2533</v>
+        <v>1.5457</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>0.91</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1777</v>
+        <v>-0.1153</v>
       </c>
       <c r="J304" t="n">
-        <v>-5.1533</v>
+        <v>-3.3437</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.84</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3014</v>
+        <v>-0.1894</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.740600000000001</v>
+        <v>-5.4926</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.78</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3931</v>
+        <v>-0.2497</v>
       </c>
       <c r="J306" t="n">
-        <v>-11.3999</v>
+        <v>-7.2413</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.62</v>
       </c>
       <c r="I307" t="n">
-        <v>1.4552</v>
+        <v>1.2932</v>
       </c>
       <c r="J307" t="n">
-        <v>42.2008</v>
+        <v>37.5028</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.19</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4924</v>
+        <v>0.5366</v>
       </c>
       <c r="J308" t="n">
-        <v>14.2796</v>
+        <v>15.5614</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>1.15</v>
       </c>
       <c r="I309" t="n">
-        <v>0.3779</v>
+        <v>0.4371</v>
       </c>
       <c r="J309" t="n">
-        <v>10.9591</v>
+        <v>12.6759</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>1.14</v>
       </c>
       <c r="I310" t="n">
-        <v>0.3499</v>
+        <v>0.4111</v>
       </c>
       <c r="J310" t="n">
-        <v>10.1471</v>
+        <v>11.9219</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.9</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4762</v>
+        <v>-0.4035</v>
       </c>
       <c r="J311" t="n">
-        <v>-13.8098</v>
+        <v>-11.7015</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.42</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0848</v>
+        <v>1.0495</v>
       </c>
       <c r="J312" t="n">
-        <v>31.4592</v>
+        <v>30.4355</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.727</v>
+        <v>0.7149</v>
       </c>
       <c r="J313" t="n">
-        <v>21.083</v>
+        <v>20.7321</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>1.22</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6187</v>
       </c>
       <c r="J314" t="n">
-        <v>18.1975</v>
+        <v>17.9423</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.93</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3727</v>
+        <v>-0.3005</v>
       </c>
       <c r="J315" t="n">
-        <v>-10.8083</v>
+        <v>-8.714499999999999</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.91</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4315</v>
+        <v>-0.3609</v>
       </c>
       <c r="J316" t="n">
-        <v>-12.5135</v>
+        <v>-10.4661</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.26</v>
       </c>
       <c r="I317" t="n">
-        <v>0.496</v>
+        <v>0.5805</v>
       </c>
       <c r="J317" t="n">
-        <v>14.384</v>
+        <v>16.8345</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.11</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2757</v>
+        <v>0.2916</v>
       </c>
       <c r="J318" t="n">
-        <v>7.9953</v>
+        <v>8.4564</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>0.96</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0612</v>
+        <v>-0.0563</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.7748</v>
+        <v>-1.6327</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.8</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3616</v>
+        <v>-0.2291</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.4864</v>
+        <v>-6.6439</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.46</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.8001</v>
+        <v>-0.5473</v>
       </c>
       <c r="J321" t="n">
-        <v>-23.2029</v>
+        <v>-15.8717</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.67</v>
       </c>
       <c r="I322" t="n">
-        <v>1.4366</v>
+        <v>1.2986</v>
       </c>
       <c r="J322" t="n">
-        <v>30.1686</v>
+        <v>27.2706</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.64</v>
       </c>
       <c r="I323" t="n">
-        <v>1.3799</v>
+        <v>1.2636</v>
       </c>
       <c r="J323" t="n">
-        <v>28.9779</v>
+        <v>26.5356</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.58</v>
       </c>
       <c r="I324" t="n">
-        <v>1.2632</v>
+        <v>1.1931</v>
       </c>
       <c r="J324" t="n">
-        <v>26.5272</v>
+        <v>25.0551</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>1.36</v>
       </c>
       <c r="I325" t="n">
-        <v>0.7639</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="J325" t="n">
-        <v>16.0419</v>
+        <v>18.4695</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.99</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2496</v>
+        <v>-0.1596</v>
       </c>
       <c r="J326" t="n">
-        <v>-5.2416</v>
+        <v>-3.3516</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.12</v>
       </c>
       <c r="I327" t="n">
-        <v>0.3758</v>
+        <v>0.4197</v>
       </c>
       <c r="J327" t="n">
-        <v>7.8918</v>
+        <v>8.813700000000001</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>0.85</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1663</v>
+        <v>-0.1499</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.4923</v>
+        <v>-3.1479</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.66</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.4943</v>
+        <v>-0.3358</v>
       </c>
       <c r="J329" t="n">
-        <v>-10.3803</v>
+        <v>-7.0518</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.48</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.7417</v>
+        <v>-0.504</v>
       </c>
       <c r="J330" t="n">
-        <v>-15.5757</v>
+        <v>-10.584</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.47</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7543</v>
+        <v>-0.5133</v>
       </c>
       <c r="J331" t="n">
-        <v>-15.8403</v>
+        <v>-10.7793</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.0154</v>
+        <v>-0.0455</v>
       </c>
       <c r="J332" t="n">
-        <v>-0.3542</v>
+        <v>-1.0465</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>0.8</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2541</v>
+        <v>-0.2058</v>
       </c>
       <c r="J333" t="n">
-        <v>-5.8443</v>
+        <v>-4.7334</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.73</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.3767</v>
+        <v>-0.2735</v>
       </c>
       <c r="J334" t="n">
-        <v>-8.664099999999999</v>
+        <v>-6.2905</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.73</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3767</v>
+        <v>-0.2735</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.664099999999999</v>
+        <v>-6.2905</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.44</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.7942</v>
+        <v>-0.5429</v>
       </c>
       <c r="J336" t="n">
-        <v>-18.2666</v>
+        <v>-12.4867</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.77</v>
       </c>
       <c r="I337" t="n">
-        <v>1.674</v>
+        <v>1.443</v>
       </c>
       <c r="J337" t="n">
-        <v>38.502</v>
+        <v>33.189</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.51</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1841</v>
+        <v>1.1288</v>
       </c>
       <c r="J338" t="n">
-        <v>27.2343</v>
+        <v>25.9624</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.3</v>
       </c>
       <c r="I339" t="n">
-        <v>0.695</v>
+        <v>0.7705</v>
       </c>
       <c r="J339" t="n">
-        <v>15.985</v>
+        <v>17.7215</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.08</v>
       </c>
       <c r="I340" t="n">
-        <v>0.1313</v>
+        <v>0.2165</v>
       </c>
       <c r="J340" t="n">
-        <v>3.0199</v>
+        <v>4.9795</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3937</v>
+        <v>-0.3112</v>
       </c>
       <c r="J341" t="n">
-        <v>-9.055099999999999</v>
+        <v>-7.1576</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.33</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5555</v>
+        <v>0.6651</v>
       </c>
       <c r="J342" t="n">
-        <v>19.4425</v>
+        <v>23.2785</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.22</v>
       </c>
       <c r="I343" t="n">
-        <v>0.4086</v>
+        <v>0.4719</v>
       </c>
       <c r="J343" t="n">
-        <v>14.301</v>
+        <v>16.5165</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>0.96</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.1187</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="J344" t="n">
-        <v>-4.1545</v>
+        <v>-2.247</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3715</v>
+        <v>-0.2301</v>
       </c>
       <c r="J345" t="n">
-        <v>-13.0025</v>
+        <v>-8.0535</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.73</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4826</v>
+        <v>-0.3087</v>
       </c>
       <c r="J346" t="n">
-        <v>-16.891</v>
+        <v>-10.8045</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.35</v>
       </c>
       <c r="I347" t="n">
-        <v>0.9537</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="J347" t="n">
-        <v>33.3795</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.16</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4913</v>
+        <v>0.4783</v>
       </c>
       <c r="J348" t="n">
-        <v>17.1955</v>
+        <v>16.7405</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>1.15</v>
       </c>
       <c r="I349" t="n">
-        <v>0.4628</v>
+        <v>0.4526</v>
       </c>
       <c r="J349" t="n">
-        <v>16.198</v>
+        <v>15.841</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>1.04</v>
       </c>
       <c r="I350" t="n">
-        <v>0.0926</v>
+        <v>0.141</v>
       </c>
       <c r="J350" t="n">
-        <v>3.241</v>
+        <v>4.935</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.86</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5556</v>
+        <v>-0.4932</v>
       </c>
       <c r="J351" t="n">
-        <v>-19.446</v>
+        <v>-17.262</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.26</v>
       </c>
       <c r="I352" t="n">
-        <v>0.748</v>
+        <v>0.7267</v>
       </c>
       <c r="J352" t="n">
-        <v>25.432</v>
+        <v>24.7078</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.18</v>
       </c>
       <c r="I353" t="n">
-        <v>0.5463</v>
+        <v>0.5292</v>
       </c>
       <c r="J353" t="n">
-        <v>18.5742</v>
+        <v>17.9928</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.14</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4334</v>
+        <v>0.4267</v>
       </c>
       <c r="J354" t="n">
-        <v>14.7356</v>
+        <v>14.5078</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.12</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3702</v>
+        <v>0.3744</v>
       </c>
       <c r="J355" t="n">
-        <v>12.5868</v>
+        <v>12.7296</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.86</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.5556</v>
+        <v>-0.4932</v>
       </c>
       <c r="J356" t="n">
-        <v>-18.8904</v>
+        <v>-16.7688</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.38</v>
       </c>
       <c r="I357" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.7491</v>
       </c>
       <c r="J357" t="n">
-        <v>20.9916</v>
+        <v>25.4694</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2232</v>
+        <v>0.2435</v>
       </c>
       <c r="J358" t="n">
-        <v>7.5888</v>
+        <v>8.279</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.07</v>
       </c>
       <c r="I359" t="n">
-        <v>0.1692</v>
+        <v>0.181</v>
       </c>
       <c r="J359" t="n">
-        <v>5.7528</v>
+        <v>6.154</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.8</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3863</v>
+        <v>-0.2404</v>
       </c>
       <c r="J360" t="n">
-        <v>-13.1342</v>
+        <v>-8.1736</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.71</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5094</v>
+        <v>-0.3281</v>
       </c>
       <c r="J361" t="n">
-        <v>-17.3196</v>
+        <v>-11.1554</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.16</v>
       </c>
       <c r="I362" t="n">
-        <v>0.3497</v>
+        <v>0.3874</v>
       </c>
       <c r="J362" t="n">
-        <v>12.5892</v>
+        <v>13.9464</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.15</v>
       </c>
       <c r="I363" t="n">
-        <v>0.3345</v>
+        <v>0.3679</v>
       </c>
       <c r="J363" t="n">
-        <v>12.042</v>
+        <v>13.2444</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.83</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.3193</v>
+        <v>-0.2003</v>
       </c>
       <c r="J364" t="n">
-        <v>-11.4948</v>
+        <v>-7.2108</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.78</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.3948</v>
+        <v>-0.2505</v>
       </c>
       <c r="J365" t="n">
-        <v>-14.2128</v>
+        <v>-9.018000000000001</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.73</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.4655</v>
+        <v>-0.2992</v>
       </c>
       <c r="J366" t="n">
-        <v>-16.758</v>
+        <v>-10.7712</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.45</v>
       </c>
       <c r="I367" t="n">
-        <v>1.1327</v>
+        <v>1.0827</v>
       </c>
       <c r="J367" t="n">
-        <v>40.7772</v>
+        <v>38.9772</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.31</v>
       </c>
       <c r="I368" t="n">
-        <v>0.8289</v>
+        <v>0.8237</v>
       </c>
       <c r="J368" t="n">
-        <v>29.8404</v>
+        <v>29.6532</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.24</v>
       </c>
       <c r="I369" t="n">
-        <v>0.6603</v>
+        <v>0.6596</v>
       </c>
       <c r="J369" t="n">
-        <v>23.7708</v>
+        <v>23.7456</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.95</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3203</v>
+        <v>-0.2443</v>
       </c>
       <c r="J370" t="n">
-        <v>-11.5308</v>
+        <v>-8.7948</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.93</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3825</v>
+        <v>-0.3078</v>
       </c>
       <c r="J371" t="n">
-        <v>-13.77</v>
+        <v>-11.0808</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.02</v>
       </c>
       <c r="I372" t="n">
-        <v>0.2069</v>
+        <v>0.1949</v>
       </c>
       <c r="J372" t="n">
-        <v>4.138</v>
+        <v>3.898</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>0.75</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.3109</v>
+        <v>-0.2479</v>
       </c>
       <c r="J373" t="n">
-        <v>-6.218</v>
+        <v>-4.958</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>0.66</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.4763</v>
+        <v>-0.3312</v>
       </c>
       <c r="J374" t="n">
-        <v>-9.526</v>
+        <v>-6.624</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.5</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.7076</v>
+        <v>-0.4801</v>
       </c>
       <c r="J375" t="n">
-        <v>-14.152</v>
+        <v>-9.602</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.49</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.7207</v>
+        <v>-0.4895</v>
       </c>
       <c r="J376" t="n">
-        <v>-14.414</v>
+        <v>-9.789999999999999</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.79</v>
       </c>
       <c r="I377" t="n">
-        <v>1.6818</v>
+        <v>1.451</v>
       </c>
       <c r="J377" t="n">
-        <v>33.636</v>
+        <v>29.02</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.44</v>
       </c>
       <c r="I378" t="n">
-        <v>1.0038</v>
+        <v>1.0309</v>
       </c>
       <c r="J378" t="n">
-        <v>20.076</v>
+        <v>20.618</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.41</v>
       </c>
       <c r="I379" t="n">
-        <v>0.9348</v>
+        <v>0.9849</v>
       </c>
       <c r="J379" t="n">
-        <v>18.696</v>
+        <v>19.698</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>1.16</v>
       </c>
       <c r="I380" t="n">
-        <v>0.3239</v>
+        <v>0.4223</v>
       </c>
       <c r="J380" t="n">
-        <v>6.478</v>
+        <v>8.446</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>1.12</v>
       </c>
       <c r="I381" t="n">
-        <v>0.2215</v>
+        <v>0.3159</v>
       </c>
       <c r="J381" t="n">
-        <v>4.43</v>
+        <v>6.318</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.67</v>
       </c>
       <c r="I382" t="n">
-        <v>1.5331</v>
+        <v>1.3461</v>
       </c>
       <c r="J382" t="n">
-        <v>41.3937</v>
+        <v>36.3447</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.26</v>
       </c>
       <c r="I383" t="n">
-        <v>0.6725</v>
+        <v>0.694</v>
       </c>
       <c r="J383" t="n">
-        <v>18.1575</v>
+        <v>18.738</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.22</v>
       </c>
       <c r="I384" t="n">
-        <v>0.5505</v>
+        <v>0.6028</v>
       </c>
       <c r="J384" t="n">
-        <v>14.8635</v>
+        <v>16.2756</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.11</v>
       </c>
       <c r="I385" t="n">
-        <v>0.2497</v>
+        <v>0.323</v>
       </c>
       <c r="J385" t="n">
-        <v>6.7419</v>
+        <v>8.721</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.9</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4854</v>
+        <v>-0.4113</v>
       </c>
       <c r="J386" t="n">
-        <v>-13.1058</v>
+        <v>-11.1051</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.22</v>
       </c>
       <c r="I387" t="n">
-        <v>0.4448</v>
+        <v>0.511</v>
       </c>
       <c r="J387" t="n">
-        <v>12.0096</v>
+        <v>13.797</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1</v>
       </c>
       <c r="I388" t="n">
-        <v>0.0495</v>
+        <v>0.0185</v>
       </c>
       <c r="J388" t="n">
-        <v>1.3365</v>
+        <v>0.4995</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.93</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.1187</v>
+        <v>-0.0919</v>
       </c>
       <c r="J389" t="n">
-        <v>-3.2049</v>
+        <v>-2.4813</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.9</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.1874</v>
+        <v>-0.1248</v>
       </c>
       <c r="J390" t="n">
-        <v>-5.0598</v>
+        <v>-3.3696</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.49</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.764</v>
+        <v>-0.5193</v>
       </c>
       <c r="J391" t="n">
-        <v>-20.628</v>
+        <v>-14.0211</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>0.63</v>
       </c>
       <c r="I392" t="n">
-        <v>-0.4124</v>
+        <v>-0.3326</v>
       </c>
       <c r="J392" t="n">
-        <v>-7.8356</v>
+        <v>-6.3194</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>0.61</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.4439</v>
+        <v>-0.3526</v>
       </c>
       <c r="J393" t="n">
-        <v>-8.434100000000001</v>
+        <v>-6.6994</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>0.57</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3911</v>
       </c>
       <c r="J394" t="n">
-        <v>-9.682399999999999</v>
+        <v>-7.4309</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.51</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.4439</v>
       </c>
       <c r="J395" t="n">
-        <v>-11.9795</v>
+        <v>-8.434100000000001</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.38</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.8227</v>
+        <v>-0.5676</v>
       </c>
       <c r="J396" t="n">
-        <v>-15.6313</v>
+        <v>-10.7844</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>2.06</v>
       </c>
       <c r="I397" t="n">
-        <v>2.0151</v>
+        <v>1.7261</v>
       </c>
       <c r="J397" t="n">
-        <v>38.2869</v>
+        <v>32.7959</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.6</v>
       </c>
       <c r="I398" t="n">
-        <v>1.2711</v>
+        <v>1.208</v>
       </c>
       <c r="J398" t="n">
-        <v>24.1509</v>
+        <v>22.952</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.53</v>
       </c>
       <c r="I399" t="n">
-        <v>1.1219</v>
+        <v>1.1274</v>
       </c>
       <c r="J399" t="n">
-        <v>21.3161</v>
+        <v>21.4206</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>1.27</v>
       </c>
       <c r="I400" t="n">
-        <v>0.5415</v>
+        <v>0.6643</v>
       </c>
       <c r="J400" t="n">
-        <v>10.2885</v>
+        <v>12.6217</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>1.11</v>
       </c>
       <c r="I401" t="n">
-        <v>0.1615</v>
+        <v>0.2613</v>
       </c>
       <c r="J401" t="n">
-        <v>3.0685</v>
+        <v>4.9647</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.55</v>
       </c>
       <c r="I402" t="n">
-        <v>1.3132</v>
+        <v>1.201</v>
       </c>
       <c r="J402" t="n">
-        <v>32.83</v>
+        <v>30.025</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.28</v>
       </c>
       <c r="I403" t="n">
-        <v>0.7342</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J403" t="n">
-        <v>18.355</v>
+        <v>18.585</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.17</v>
       </c>
       <c r="I404" t="n">
-        <v>0.4232</v>
+        <v>0.4846</v>
       </c>
       <c r="J404" t="n">
-        <v>10.58</v>
+        <v>12.115</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>1.13</v>
       </c>
       <c r="I405" t="n">
-        <v>0.3132</v>
+        <v>0.3811</v>
       </c>
       <c r="J405" t="n">
-        <v>7.83</v>
+        <v>9.5275</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.95</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.3337</v>
+        <v>-0.2545</v>
       </c>
       <c r="J406" t="n">
-        <v>-8.342499999999999</v>
+        <v>-6.3625</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.22</v>
       </c>
       <c r="I407" t="n">
-        <v>0.4375</v>
+        <v>0.5023</v>
       </c>
       <c r="J407" t="n">
-        <v>10.9375</v>
+        <v>12.5575</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.05</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1653</v>
+        <v>0.1572</v>
       </c>
       <c r="J408" t="n">
-        <v>4.1325</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.01</v>
       </c>
       <c r="I409" t="n">
-        <v>0.076</v>
+        <v>0.0523</v>
       </c>
       <c r="J409" t="n">
-        <v>1.9</v>
+        <v>1.3075</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.79</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.3795</v>
+        <v>-0.2403</v>
       </c>
       <c r="J410" t="n">
-        <v>-9.487500000000001</v>
+        <v>-6.0075</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.57</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.6714</v>
+        <v>-0.4489</v>
       </c>
       <c r="J411" t="n">
-        <v>-16.785</v>
+        <v>-11.2225</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.8</v>
       </c>
       <c r="I412" t="n">
-        <v>1.6944</v>
+        <v>1.4599</v>
       </c>
       <c r="J412" t="n">
-        <v>35.5824</v>
+        <v>30.6579</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.77</v>
       </c>
       <c r="I413" t="n">
-        <v>1.6412</v>
+        <v>1.425</v>
       </c>
       <c r="J413" t="n">
-        <v>34.4652</v>
+        <v>29.925</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>1.28</v>
       </c>
       <c r="I414" t="n">
-        <v>0.6056</v>
+        <v>0.7113</v>
       </c>
       <c r="J414" t="n">
-        <v>12.7176</v>
+        <v>14.9373</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>1.21</v>
       </c>
       <c r="I415" t="n">
-        <v>0.4418</v>
+        <v>0.5455</v>
       </c>
       <c r="J415" t="n">
-        <v>9.277799999999999</v>
+        <v>11.4555</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.92</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.469</v>
+        <v>-0.3888</v>
       </c>
       <c r="J416" t="n">
-        <v>-9.849</v>
+        <v>-8.1648</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.12</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3646</v>
+        <v>0.4025</v>
       </c>
       <c r="J417" t="n">
-        <v>7.6566</v>
+        <v>8.452500000000001</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>0.88</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.1277</v>
+        <v>-0.1218</v>
       </c>
       <c r="J418" t="n">
-        <v>-2.6817</v>
+        <v>-2.5578</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>0.66</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.5051</v>
+        <v>-0.3395</v>
       </c>
       <c r="J419" t="n">
-        <v>-10.6071</v>
+        <v>-7.1295</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.65</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.5198</v>
+        <v>-0.3488</v>
       </c>
       <c r="J420" t="n">
-        <v>-10.9158</v>
+        <v>-7.3248</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.39</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.8568</v>
+        <v>-0.5908</v>
       </c>
       <c r="J421" t="n">
-        <v>-17.9928</v>
+        <v>-12.4068</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.64</v>
       </c>
       <c r="I422" t="n">
-        <v>1.4295</v>
+        <v>1.2841</v>
       </c>
       <c r="J422" t="n">
-        <v>35.7375</v>
+        <v>32.1025</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.44</v>
       </c>
       <c r="I423" t="n">
-        <v>1.0306</v>
+        <v>1.0378</v>
       </c>
       <c r="J423" t="n">
-        <v>25.765</v>
+        <v>25.945</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.36</v>
       </c>
       <c r="I424" t="n">
-        <v>0.8484</v>
+        <v>0.8963</v>
       </c>
       <c r="J424" t="n">
-        <v>21.21</v>
+        <v>22.4075</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.31</v>
       </c>
       <c r="I425" t="n">
-        <v>0.7088</v>
+        <v>0.79</v>
       </c>
       <c r="J425" t="n">
-        <v>17.72</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.93</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.4272</v>
+        <v>-0.3458</v>
       </c>
       <c r="J426" t="n">
-        <v>-10.68</v>
+        <v>-8.645</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.08</v>
       </c>
       <c r="I427" t="n">
-        <v>0.2751</v>
+        <v>0.2816</v>
       </c>
       <c r="J427" t="n">
-        <v>6.8775</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>0.89</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.135</v>
+        <v>-0.1212</v>
       </c>
       <c r="J428" t="n">
-        <v>-3.375</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.72</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.4369</v>
+        <v>-0.2904</v>
       </c>
       <c r="J429" t="n">
-        <v>-10.9225</v>
+        <v>-7.26</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.67</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.51</v>
+        <v>-0.3378</v>
       </c>
       <c r="J430" t="n">
-        <v>-12.75</v>
+        <v>-8.445</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.6</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.6056</v>
+        <v>-0.4036</v>
       </c>
       <c r="J431" t="n">
-        <v>-15.14</v>
+        <v>-10.09</v>
       </c>
     </row>
     <row r="432">
@@ -20549,10 +20549,10 @@
         <v>0.77</v>
       </c>
       <c r="I432" t="n">
-        <v>-0.225</v>
+        <v>-0.1998</v>
       </c>
       <c r="J432" t="n">
-        <v>-4.5</v>
+        <v>-3.996</v>
       </c>
     </row>
     <row r="433">
@@ -20589,10 +20589,10 @@
         <v>0.75</v>
       </c>
       <c r="I433" t="n">
-        <v>-0.2559</v>
+        <v>-0.2218</v>
       </c>
       <c r="J433" t="n">
-        <v>-5.118</v>
+        <v>-4.436</v>
       </c>
     </row>
     <row r="434">
@@ -20629,10 +20629,10 @@
         <v>0.64</v>
       </c>
       <c r="I434" t="n">
-        <v>-0.4271</v>
+        <v>-0.3348</v>
       </c>
       <c r="J434" t="n">
-        <v>-8.542</v>
+        <v>-6.696</v>
       </c>
     </row>
     <row r="435">
@@ -20669,10 +20669,10 @@
         <v>0.42</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.7839</v>
+        <v>-0.5382</v>
       </c>
       <c r="J435" t="n">
-        <v>-15.678</v>
+        <v>-10.764</v>
       </c>
     </row>
     <row r="436">
@@ -20709,10 +20709,10 @@
         <v>0.35</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.8753</v>
+        <v>-0.6055</v>
       </c>
       <c r="J436" t="n">
-        <v>-17.506</v>
+        <v>-12.11</v>
       </c>
     </row>
     <row r="437">
@@ -20749,10 +20749,10 @@
         <v>1.69</v>
       </c>
       <c r="I437" t="n">
-        <v>1.4584</v>
+        <v>1.316</v>
       </c>
       <c r="J437" t="n">
-        <v>29.168</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="438">
@@ -20789,10 +20789,10 @@
         <v>1.64</v>
       </c>
       <c r="I438" t="n">
-        <v>1.3638</v>
+        <v>1.2582</v>
       </c>
       <c r="J438" t="n">
-        <v>27.276</v>
+        <v>25.164</v>
       </c>
     </row>
     <row r="439">
@@ -20829,10 +20829,10 @@
         <v>1.5</v>
       </c>
       <c r="I439" t="n">
-        <v>1.0743</v>
+        <v>1.0951</v>
       </c>
       <c r="J439" t="n">
-        <v>21.486</v>
+        <v>21.902</v>
       </c>
     </row>
     <row r="440">
@@ -20869,10 +20869,10 @@
         <v>1.32</v>
       </c>
       <c r="I440" t="n">
-        <v>0.6613</v>
+        <v>0.7844</v>
       </c>
       <c r="J440" t="n">
-        <v>13.226</v>
+        <v>15.688</v>
       </c>
     </row>
     <row r="441">
@@ -20909,10 +20909,10 @@
         <v>1.27</v>
       </c>
       <c r="I441" t="n">
-        <v>0.5507</v>
+        <v>0.6703</v>
       </c>
       <c r="J441" t="n">
-        <v>11.014</v>
+        <v>13.406</v>
       </c>
     </row>
     <row r="442">
@@ -20949,10 +20949,10 @@
         <v>1.21</v>
       </c>
       <c r="I442" t="n">
-        <v>0.6419</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="J442" t="n">
-        <v>19.257</v>
+        <v>18.402</v>
       </c>
     </row>
     <row r="443">
@@ -20989,10 +20989,10 @@
         <v>1.15</v>
       </c>
       <c r="I443" t="n">
-        <v>0.4832</v>
+        <v>0.4597</v>
       </c>
       <c r="J443" t="n">
-        <v>14.496</v>
+        <v>13.791</v>
       </c>
     </row>
     <row r="444">
@@ -21029,10 +21029,10 @@
         <v>1.12</v>
       </c>
       <c r="I444" t="n">
-        <v>0.396</v>
+        <v>0.38</v>
       </c>
       <c r="J444" t="n">
-        <v>11.88</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="445">
@@ -21069,10 +21069,10 @@
         <v>1.11</v>
       </c>
       <c r="I445" t="n">
-        <v>0.3651</v>
+        <v>0.3529</v>
       </c>
       <c r="J445" t="n">
-        <v>10.953</v>
+        <v>10.587</v>
       </c>
     </row>
     <row r="446">
@@ -21109,10 +21109,10 @@
         <v>0.83</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.6232</v>
+        <v>-0.5666</v>
       </c>
       <c r="J446" t="n">
-        <v>-18.696</v>
+        <v>-16.998</v>
       </c>
     </row>
     <row r="447">
@@ -21149,10 +21149,10 @@
         <v>1.22</v>
       </c>
       <c r="I447" t="n">
-        <v>0.4107</v>
+        <v>0.4739</v>
       </c>
       <c r="J447" t="n">
-        <v>12.321</v>
+        <v>14.217</v>
       </c>
     </row>
     <row r="448">
@@ -21189,10 +21189,10 @@
         <v>1.09</v>
       </c>
       <c r="I448" t="n">
-        <v>0.209</v>
+        <v>0.2249</v>
       </c>
       <c r="J448" t="n">
-        <v>6.27</v>
+        <v>6.747</v>
       </c>
     </row>
     <row r="449">
@@ -21229,10 +21229,10 @@
         <v>0.98</v>
       </c>
       <c r="I449" t="n">
-        <v>-0.0702</v>
+        <v>-0.0363</v>
       </c>
       <c r="J449" t="n">
-        <v>-2.106</v>
+        <v>-1.089</v>
       </c>
     </row>
     <row r="450">
@@ -21269,10 +21269,10 @@
         <v>0.88</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.2625</v>
+        <v>-0.1566</v>
       </c>
       <c r="J450" t="n">
-        <v>-7.875</v>
+        <v>-4.698</v>
       </c>
     </row>
     <row r="451">
@@ -21309,10 +21309,10 @@
         <v>0.85</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.3101</v>
+        <v>-0.1884</v>
       </c>
       <c r="J451" t="n">
-        <v>-9.303000000000001</v>
+        <v>-5.652</v>
       </c>
     </row>
     <row r="452">
@@ -21349,10 +21349,10 @@
         <v>1.96</v>
       </c>
       <c r="I452" t="n">
-        <v>1.9563</v>
+        <v>1.654</v>
       </c>
       <c r="J452" t="n">
-        <v>44.9949</v>
+        <v>38.042</v>
       </c>
     </row>
     <row r="453">
@@ -21389,10 +21389,10 @@
         <v>1.49</v>
       </c>
       <c r="I453" t="n">
-        <v>1.1247</v>
+        <v>1.0979</v>
       </c>
       <c r="J453" t="n">
-        <v>25.8681</v>
+        <v>25.2517</v>
       </c>
     </row>
     <row r="454">
@@ -21429,10 +21429,10 @@
         <v>1.18</v>
       </c>
       <c r="I454" t="n">
-        <v>0.3826</v>
+        <v>0.4791</v>
       </c>
       <c r="J454" t="n">
-        <v>8.799799999999999</v>
+        <v>11.0193</v>
       </c>
     </row>
     <row r="455">
@@ -21469,10 +21469,10 @@
         <v>1.08</v>
       </c>
       <c r="I455" t="n">
-        <v>0.1196</v>
+        <v>0.2079</v>
       </c>
       <c r="J455" t="n">
-        <v>2.7508</v>
+        <v>4.7817</v>
       </c>
     </row>
     <row r="456">
@@ -21509,10 +21509,10 @@
         <v>1.08</v>
       </c>
       <c r="I456" t="n">
-        <v>0.1196</v>
+        <v>0.2079</v>
       </c>
       <c r="J456" t="n">
-        <v>2.7508</v>
+        <v>4.7817</v>
       </c>
     </row>
     <row r="457">
@@ -21549,10 +21549,10 @@
         <v>1.14</v>
       </c>
       <c r="I457" t="n">
-        <v>0.369</v>
+        <v>0.4067</v>
       </c>
       <c r="J457" t="n">
-        <v>8.487</v>
+        <v>9.354100000000001</v>
       </c>
     </row>
     <row r="458">
@@ -21589,10 +21589,10 @@
         <v>0.86</v>
       </c>
       <c r="I458" t="n">
-        <v>-0.192</v>
+        <v>-0.1558</v>
       </c>
       <c r="J458" t="n">
-        <v>-4.416</v>
+        <v>-3.5834</v>
       </c>
     </row>
     <row r="459">
@@ -21629,10 +21629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I459" t="n">
-        <v>-0.2819</v>
+        <v>-0.2064</v>
       </c>
       <c r="J459" t="n">
-        <v>-6.4837</v>
+        <v>-4.7472</v>
       </c>
     </row>
     <row r="460">
@@ -21669,10 +21669,10 @@
         <v>0.7</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.4704</v>
+        <v>-0.3108</v>
       </c>
       <c r="J460" t="n">
-        <v>-10.8192</v>
+        <v>-7.1484</v>
       </c>
     </row>
     <row r="461">
@@ -21709,10 +21709,10 @@
         <v>0.5</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.7349</v>
+        <v>-0.4977</v>
       </c>
       <c r="J461" t="n">
-        <v>-16.9027</v>
+        <v>-11.4471</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2557/event_2557_evp_summary.xlsx
+++ b/database/event/2557/event_2557_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2766</v>
+        <v>6.3737</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1689</v>
+        <v>2.2025</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1956</v>
+        <v>2.2772</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2766</v>
+        <v>6.3737</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8006</v>
+        <v>2.6979</v>
       </c>
       <c r="G2" t="n">
-        <v>3.476</v>
+        <v>3.6758</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3814</v>
+        <v>4.0071</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2781</v>
+        <v>2.1638</v>
       </c>
       <c r="J2" t="n">
-        <v>3.476</v>
+        <v>3.6758</v>
       </c>
       <c r="K2" t="n">
         <v>125</v>
@@ -529,7 +529,7 @@
         <v>155</v>
       </c>
       <c r="M2" t="n">
-        <v>5.754099999999999</v>
+        <v>5.839600000000001</v>
       </c>
       <c r="N2" t="n">
         <v>280</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8631</v>
+        <v>5.7124</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0261</v>
+        <v>1.974</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0089</v>
+        <v>1.9762</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8631</v>
+        <v>5.7124</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7192</v>
+        <v>1.5397</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1439</v>
+        <v>4.1727</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7192</v>
+        <v>1.5397</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8939</v>
+        <v>0.8314</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1439</v>
+        <v>4.1727</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>5.037800000000001</v>
+        <v>5.0041</v>
       </c>
       <c r="N3" t="n">
         <v>280</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5081</v>
+        <v>5.4724</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9034</v>
+        <v>1.891</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8486</v>
+        <v>1.8669</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5081</v>
+        <v>5.4724</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4824</v>
+        <v>2.3754</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0257</v>
+        <v>3.097</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2601</v>
+        <v>2.9432</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6951</v>
+        <v>1.5893</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0257</v>
+        <v>3.097</v>
       </c>
       <c r="K4" t="n">
         <v>125</v>
@@ -621,7 +621,7 @@
         <v>155</v>
       </c>
       <c r="M4" t="n">
-        <v>4.720800000000001</v>
+        <v>4.6863</v>
       </c>
       <c r="N4" t="n">
         <v>280</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4093</v>
+        <v>5.4195</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8692</v>
+        <v>1.8728</v>
       </c>
       <c r="D5" t="n">
-        <v>1.804</v>
+        <v>1.8429</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4093</v>
+        <v>5.4195</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0185</v>
+        <v>3.943</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3908</v>
+        <v>1.4765</v>
       </c>
       <c r="H5" t="n">
-        <v>8.6723</v>
+        <v>8.1153</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5092</v>
+        <v>4.3822</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3908</v>
+        <v>1.4765</v>
       </c>
       <c r="K5" t="n">
         <v>144</v>
@@ -667,7 +667,7 @@
         <v>156</v>
       </c>
       <c r="M5" t="n">
-        <v>5.9</v>
+        <v>5.8587</v>
       </c>
       <c r="N5" t="n">
         <v>300</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2627</v>
+        <v>5.3034</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8186</v>
+        <v>1.8326</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7378</v>
+        <v>1.79</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2627</v>
+        <v>5.3034</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5033</v>
+        <v>3.3527</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7594</v>
+        <v>1.9507</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3329</v>
+        <v>4.613</v>
       </c>
       <c r="I6" t="n">
-        <v>4.511</v>
+        <v>4.7319</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7594</v>
+        <v>1.9507</v>
       </c>
       <c r="K6" t="n">
         <v>113</v>
@@ -713,7 +713,7 @@
         <v>103</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2704</v>
+        <v>6.682600000000001</v>
       </c>
       <c r="N6" t="n">
         <v>216</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.967</v>
+        <v>4.8775</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7164</v>
+        <v>1.6855</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6043</v>
+        <v>1.5961</v>
       </c>
       <c r="E7" t="n">
-        <v>4.967</v>
+        <v>4.8775</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4605</v>
+        <v>2.1919</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5065</v>
+        <v>2.6856</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2388</v>
+        <v>2.1919</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4131</v>
+        <v>2.1919</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5065</v>
+        <v>2.6856</v>
       </c>
       <c r="K7" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="L7" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="M7" t="n">
-        <v>5.9196</v>
+        <v>4.8775</v>
       </c>
       <c r="N7" t="n">
-        <v>216</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7788</v>
+        <v>4.8731</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6514</v>
+        <v>1.6839</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5194</v>
+        <v>1.5941</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7788</v>
+        <v>4.8731</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3315</v>
+        <v>3.1533</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4473</v>
+        <v>1.7198</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3315</v>
+        <v>4.1767</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3315</v>
+        <v>4.2843</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4473</v>
+        <v>1.7198</v>
       </c>
       <c r="K8" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="L8" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7788</v>
+        <v>6.0041</v>
       </c>
       <c r="N8" t="n">
-        <v>257</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5478</v>
+        <v>4.3816</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5715</v>
+        <v>1.5141</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4151</v>
+        <v>1.3704</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5478</v>
+        <v>4.3816</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2447</v>
+        <v>2.9612</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3031</v>
+        <v>1.4204</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7651</v>
+        <v>3.7561</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9199</v>
+        <v>3.8529</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3031</v>
+        <v>1.4204</v>
       </c>
       <c r="K9" t="n">
         <v>113</v>
@@ -851,7 +851,7 @@
         <v>103</v>
       </c>
       <c r="M9" t="n">
-        <v>5.223</v>
+        <v>5.2733</v>
       </c>
       <c r="N9" t="n">
         <v>216</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9106</v>
+        <v>3.9225</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3513</v>
+        <v>1.3555</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1274</v>
+        <v>1.1614</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9106</v>
+        <v>3.9225</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8559</v>
+        <v>2.3028</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0547</v>
+        <v>1.6197</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9113</v>
+        <v>2.3152</v>
       </c>
       <c r="I10" t="n">
-        <v>3.031</v>
+        <v>2.3152</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0547</v>
+        <v>1.6197</v>
       </c>
       <c r="K10" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="L10" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="M10" t="n">
-        <v>4.0857</v>
+        <v>3.9349</v>
       </c>
       <c r="N10" t="n">
-        <v>216</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8787</v>
+        <v>3.8003</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3403</v>
+        <v>1.3132</v>
       </c>
       <c r="D11" t="n">
-        <v>1.113</v>
+        <v>1.1058</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8787</v>
+        <v>3.8003</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4495</v>
+        <v>2.6028</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4292</v>
+        <v>1.1975</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4495</v>
+        <v>2.9718</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4495</v>
+        <v>3.0484</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4292</v>
+        <v>1.1975</v>
       </c>
       <c r="K11" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="L11" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8787</v>
+        <v>4.2459</v>
       </c>
       <c r="N11" t="n">
-        <v>257</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6926</v>
+        <v>3.5211</v>
       </c>
       <c r="C12" t="n">
-        <v>1.276</v>
+        <v>1.2168</v>
       </c>
       <c r="D12" t="n">
-        <v>1.029</v>
+        <v>0.9787</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6926</v>
+        <v>3.5211</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1404</v>
+        <v>4.0005</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4478</v>
+        <v>-0.4794</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7316</v>
+        <v>6.0308</v>
       </c>
       <c r="I12" t="n">
-        <v>6.2128</v>
+        <v>6.3456</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4478</v>
+        <v>-0.4794</v>
       </c>
       <c r="K12" t="n">
         <v>140</v>
@@ -989,7 +989,7 @@
         <v>76</v>
       </c>
       <c r="M12" t="n">
-        <v>5.765</v>
+        <v>5.8662</v>
       </c>
       <c r="N12" t="n">
         <v>216</v>
@@ -998,231 +998,231 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.6785</v>
+        <v>3.4654</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2711</v>
+        <v>1.1975</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0226</v>
+        <v>0.9533</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6785</v>
+        <v>3.4654</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6082</v>
+        <v>3.3011</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0703</v>
+        <v>0.1643</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5632</v>
+        <v>5.9975</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9462</v>
+        <v>3.2386</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0703</v>
+        <v>0.1643</v>
       </c>
       <c r="K13" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L13" t="n">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="M13" t="n">
-        <v>5.0165</v>
+        <v>3.4029</v>
       </c>
       <c r="N13" t="n">
-        <v>216</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.4845</v>
+        <v>3.4474</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2041</v>
+        <v>1.1913</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9351</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4845</v>
+        <v>3.4474</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3873</v>
+        <v>3.3668</v>
       </c>
       <c r="G14" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0806</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4483</v>
+        <v>4.6439</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3528</v>
+        <v>4.8863</v>
       </c>
       <c r="J14" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0806</v>
       </c>
       <c r="K14" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L14" t="n">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>4.966900000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>300</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1352</v>
+        <v>2.9908</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0834</v>
+        <v>1.0335</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7774</v>
+        <v>0.7373</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1352</v>
+        <v>2.9908</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1352</v>
+        <v>0.7952</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.1956</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5245</v>
+        <v>0.7952</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5245</v>
+        <v>0.7952</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2.1956</v>
       </c>
       <c r="K15" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5245</v>
+        <v>2.9908</v>
       </c>
       <c r="N15" t="n">
-        <v>128</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0073</v>
+        <v>2.8131</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0392</v>
+        <v>0.9721</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7196</v>
+        <v>0.6564</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0073</v>
+        <v>2.8131</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6533</v>
+        <v>2.8131</v>
       </c>
       <c r="G16" t="n">
-        <v>0.354</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6533</v>
+        <v>3.4321</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7624</v>
+        <v>3.4321</v>
       </c>
       <c r="J16" t="n">
-        <v>0.354</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1164</v>
+        <v>3.4321</v>
       </c>
       <c r="N16" t="n">
-        <v>199</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.881</v>
+        <v>2.7334</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9956</v>
+        <v>0.9446</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6626</v>
+        <v>0.6201</v>
       </c>
       <c r="E17" t="n">
-        <v>2.881</v>
+        <v>2.7334</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8289</v>
+        <v>2.4016</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0521</v>
+        <v>0.3318</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8289</v>
+        <v>2.5314</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8289</v>
+        <v>2.5966</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0521</v>
+        <v>0.3318</v>
       </c>
       <c r="K17" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="L17" t="n">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>2.881</v>
+        <v>2.9284</v>
       </c>
       <c r="N17" t="n">
-        <v>257</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.584</v>
+        <v>2.4762</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8929</v>
+        <v>0.8557</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5285</v>
+        <v>0.503</v>
       </c>
       <c r="E18" t="n">
-        <v>2.584</v>
+        <v>2.4762</v>
       </c>
       <c r="F18" t="n">
-        <v>2.584</v>
+        <v>2.4762</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.584</v>
+        <v>2.6947</v>
       </c>
       <c r="I18" t="n">
-        <v>2.584</v>
+        <v>2.6947</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.584</v>
+        <v>2.6947</v>
       </c>
       <c r="N18" t="n">
         <v>128</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4878</v>
+        <v>2.4252</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8597</v>
+        <v>0.8381</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4851</v>
+        <v>0.4798</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4878</v>
+        <v>2.4252</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2735</v>
+        <v>-0.3394</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7613</v>
+        <v>2.7646</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2735</v>
+        <v>-0.3394</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1422</v>
+        <v>-0.1833</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7613</v>
+        <v>2.7646</v>
       </c>
       <c r="K19" t="n">
         <v>125</v>
@@ -1311,7 +1311,7 @@
         <v>155</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6191</v>
+        <v>2.5813</v>
       </c>
       <c r="N19" t="n">
         <v>280</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1491</v>
+        <v>2.1179</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7426</v>
+        <v>0.7319</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3322</v>
+        <v>0.3399</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1491</v>
+        <v>2.1179</v>
       </c>
       <c r="F20" t="n">
-        <v>1.965</v>
+        <v>1.9615</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1841</v>
+        <v>0.1564</v>
       </c>
       <c r="H20" t="n">
-        <v>1.965</v>
+        <v>1.9615</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0458</v>
+        <v>2.012</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1841</v>
+        <v>0.1564</v>
       </c>
       <c r="K20" t="n">
         <v>152</v>
@@ -1357,7 +1357,7 @@
         <v>47</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2299</v>
+        <v>2.1684</v>
       </c>
       <c r="N20" t="n">
         <v>199</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0403</v>
+        <v>1.9988</v>
       </c>
       <c r="C21" t="n">
-        <v>0.705</v>
+        <v>0.6907</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2831</v>
+        <v>0.2857</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0403</v>
+        <v>1.9988</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0403</v>
+        <v>1.9988</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0403</v>
+        <v>1.9988</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0403</v>
+        <v>1.9988</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0403</v>
+        <v>1.9988</v>
       </c>
       <c r="N21" t="n">
         <v>114</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9273</v>
+        <v>1.8711</v>
       </c>
       <c r="C22" t="n">
-        <v>0.666</v>
+        <v>0.6466</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2321</v>
+        <v>0.2276</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9273</v>
+        <v>1.8711</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9273</v>
+        <v>1.8711</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9273</v>
+        <v>1.8711</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9273</v>
+        <v>1.8711</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9273</v>
+        <v>1.8711</v>
       </c>
       <c r="N22" t="n">
         <v>138</v>
@@ -1458,35 +1458,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9095</v>
+        <v>1.7024</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.5883</v>
       </c>
       <c r="D23" t="n">
-        <v>0.224</v>
+        <v>0.1508</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9095</v>
+        <v>1.7024</v>
       </c>
       <c r="F23" t="n">
-        <v>2.9095</v>
+        <v>2.2393</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>-0.5369</v>
       </c>
       <c r="H23" t="n">
-        <v>3.0289</v>
+        <v>2.2393</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2832</v>
+        <v>2.3562</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>-0.5369</v>
       </c>
       <c r="K23" t="n">
         <v>140</v>
@@ -1495,7 +1495,7 @@
         <v>76</v>
       </c>
       <c r="M23" t="n">
-        <v>2.2832</v>
+        <v>1.8193</v>
       </c>
       <c r="N23" t="n">
         <v>216</v>
@@ -1504,81 +1504,81 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7846</v>
+        <v>1.6821</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6167</v>
+        <v>0.5813</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1676</v>
+        <v>0.1415</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7846</v>
+        <v>1.6821</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7846</v>
+        <v>2.6821</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7846</v>
+        <v>3.1454</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7846</v>
+        <v>3.3096</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K24" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7846</v>
+        <v>2.3096</v>
       </c>
       <c r="N24" t="n">
-        <v>138</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6963</v>
+        <v>1.6721</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5778</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1278</v>
+        <v>0.137</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6963</v>
+        <v>1.6721</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2067</v>
+        <v>1.712</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5104</v>
+        <v>-0.0399</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2067</v>
+        <v>1.712</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3919</v>
+        <v>1.8014</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5104</v>
+        <v>-0.0399</v>
       </c>
       <c r="K25" t="n">
         <v>140</v>
@@ -1587,7 +1587,7 @@
         <v>76</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8815</v>
+        <v>1.7615</v>
       </c>
       <c r="N25" t="n">
         <v>216</v>
@@ -1596,170 +1596,170 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6552</v>
+        <v>1.6517</v>
       </c>
       <c r="C26" t="n">
-        <v>0.572</v>
+        <v>0.5708</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1092</v>
+        <v>0.1277</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6552</v>
+        <v>1.6517</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2665</v>
+        <v>1.6517</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6113</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.4993</v>
+        <v>1.6517</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2995</v>
+        <v>1.6517</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6113</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L26" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6882000000000001</v>
+        <v>1.6517</v>
       </c>
       <c r="N26" t="n">
-        <v>300</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6449</v>
+        <v>1.6339</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5684</v>
+        <v>0.5646</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1046</v>
+        <v>0.1196</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6449</v>
+        <v>1.6339</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6449</v>
+        <v>2.184</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.5501</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6449</v>
+        <v>2.3117</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6449</v>
+        <v>1.2483</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.5501</v>
       </c>
       <c r="K27" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6449</v>
+        <v>0.6981999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5275</v>
+        <v>1.6309</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5278</v>
+        <v>0.5636</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0516</v>
+        <v>0.1182</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5275</v>
+        <v>1.6309</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5275</v>
+        <v>1.6309</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5275</v>
+        <v>1.6309</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5275</v>
+        <v>1.6309</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5275</v>
+        <v>1.6309</v>
       </c>
       <c r="N28" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4976</v>
+        <v>1.6076</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5175</v>
+        <v>0.5555</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0381</v>
+        <v>0.1076</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4976</v>
+        <v>1.6076</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4976</v>
+        <v>1.6076</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.4976</v>
+        <v>1.6076</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4976</v>
+        <v>1.6076</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4976</v>
+        <v>1.6076</v>
       </c>
       <c r="N29" t="n">
         <v>138</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3558</v>
+        <v>1.4597</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4685</v>
+        <v>0.5044</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0259</v>
+        <v>0.0403</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3558</v>
+        <v>1.4597</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3558</v>
+        <v>0.9296</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.5301</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3558</v>
+        <v>0.9296</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3558</v>
+        <v>0.9296</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.5301</v>
       </c>
       <c r="K30" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="M30" t="n">
-        <v>1.3558</v>
+        <v>1.4597</v>
       </c>
       <c r="N30" t="n">
-        <v>138</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3359</v>
+        <v>1.4012</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4616</v>
+        <v>0.4842</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0349</v>
+        <v>0.0137</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3359</v>
+        <v>1.4012</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8942</v>
+        <v>1.4012</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4417</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8942</v>
+        <v>1.4012</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8942</v>
+        <v>1.4012</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4417</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="L31" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3359</v>
+        <v>1.4012</v>
       </c>
       <c r="N31" t="n">
-        <v>257</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3303</v>
+        <v>1.2608</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4597</v>
+        <v>0.4357</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0375</v>
+        <v>-0.0503</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3303</v>
+        <v>1.2608</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3886</v>
+        <v>1.2608</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0583</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3886</v>
+        <v>1.2608</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5052</v>
+        <v>1.2608</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.0583</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L32" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.4469</v>
+        <v>1.2608</v>
       </c>
       <c r="N32" t="n">
-        <v>216</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2142</v>
+        <v>1.1178</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4196</v>
+        <v>0.3863</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.1154</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2142</v>
+        <v>1.1178</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2142</v>
+        <v>1.1178</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2142</v>
+        <v>1.1178</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2142</v>
+        <v>1.1178</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2142</v>
+        <v>1.1178</v>
       </c>
       <c r="N33" t="n">
         <v>114</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1775</v>
+        <v>1.0728</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4069</v>
+        <v>0.3707</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1064</v>
+        <v>-0.1358</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1775</v>
+        <v>1.0728</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1775</v>
+        <v>0.456</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.6168</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1775</v>
+        <v>0.456</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1775</v>
+        <v>0.456</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.6168</v>
       </c>
       <c r="K34" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1775</v>
+        <v>1.0728</v>
       </c>
       <c r="N34" t="n">
-        <v>138</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9901</v>
+        <v>0.9939</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3421</v>
+        <v>0.3435</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.191</v>
+        <v>-0.1718</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9901</v>
+        <v>0.9939</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4762</v>
+        <v>0.9939</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5139</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4762</v>
+        <v>0.9939</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4762</v>
+        <v>0.9939</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5139</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="L35" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9901</v>
+        <v>0.9939</v>
       </c>
       <c r="N35" t="n">
-        <v>257</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8424</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2911</v>
+        <v>0.2621</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2577</v>
+        <v>-0.2789</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8424</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8424</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8424</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8424</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8424</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>116</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.731</v>
+        <v>0.7048</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2526</v>
+        <v>0.2436</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.308</v>
+        <v>-0.3034</v>
       </c>
       <c r="E37" t="n">
-        <v>0.731</v>
+        <v>0.7048</v>
       </c>
       <c r="F37" t="n">
-        <v>0.731</v>
+        <v>0.7048</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.731</v>
+        <v>0.7048</v>
       </c>
       <c r="I37" t="n">
-        <v>0.731</v>
+        <v>0.7048</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.731</v>
+        <v>0.7048</v>
       </c>
       <c r="N37" t="n">
         <v>128</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6837</v>
+        <v>0.6552</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2363</v>
+        <v>0.2264</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3294</v>
+        <v>-0.3259</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6837</v>
+        <v>0.6552</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6837</v>
+        <v>0.6552</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6837</v>
+        <v>0.6552</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6837</v>
+        <v>0.6552</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6837</v>
+        <v>0.6552</v>
       </c>
       <c r="N38" t="n">
         <v>114</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6776</v>
+        <v>0.6301</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2342</v>
+        <v>0.2177</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3321</v>
+        <v>-0.3374</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6776</v>
+        <v>0.6301</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6776</v>
+        <v>0.6301</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6776</v>
+        <v>0.6301</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6776</v>
+        <v>0.6301</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6776</v>
+        <v>0.6301</v>
       </c>
       <c r="N39" t="n">
         <v>128</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.644</v>
+        <v>0.6223</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2225</v>
+        <v>0.215</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3473</v>
+        <v>-0.3409</v>
       </c>
       <c r="E40" t="n">
-        <v>0.644</v>
+        <v>0.6223</v>
       </c>
       <c r="F40" t="n">
-        <v>0.644</v>
+        <v>0.6223</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.644</v>
+        <v>0.6223</v>
       </c>
       <c r="I40" t="n">
-        <v>0.644</v>
+        <v>0.6223</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.644</v>
+        <v>0.6223</v>
       </c>
       <c r="N40" t="n">
         <v>138</v>
@@ -2286,277 +2286,277 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6133</v>
+        <v>0.5641</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2119</v>
+        <v>0.1949</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3611</v>
+        <v>-0.3674</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6133</v>
+        <v>0.5641</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6133</v>
+        <v>1.5641</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6133</v>
+        <v>1.5641</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6133</v>
+        <v>1.6044</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K41" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6133</v>
+        <v>0.6044</v>
       </c>
       <c r="N41" t="n">
-        <v>138</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5753</v>
+        <v>0.4823</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1988</v>
+        <v>0.1667</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3783</v>
+        <v>-0.4047</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5753</v>
+        <v>0.4823</v>
       </c>
       <c r="F42" t="n">
-        <v>1.5753</v>
+        <v>0.4823</v>
       </c>
       <c r="G42" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.5753</v>
+        <v>0.4823</v>
       </c>
       <c r="I42" t="n">
-        <v>1.6401</v>
+        <v>0.4823</v>
       </c>
       <c r="J42" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="L42" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6400999999999999</v>
+        <v>0.4823</v>
       </c>
       <c r="N42" t="n">
-        <v>199</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.4782</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1858</v>
+        <v>0.1652</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3952</v>
+        <v>-0.4065</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.4782</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.2724</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.7506</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.2724</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.1471</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.7506</v>
       </c>
       <c r="K43" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.6035</v>
       </c>
       <c r="N43" t="n">
-        <v>116</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4845</v>
+        <v>0.4694</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1674</v>
+        <v>0.1622</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4193</v>
+        <v>-0.4105</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4845</v>
+        <v>0.4694</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4845</v>
+        <v>0.4694</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4845</v>
+        <v>0.4694</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4845</v>
+        <v>0.4694</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4845</v>
+        <v>0.4694</v>
       </c>
       <c r="N44" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4054</v>
+        <v>0.3949</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1401</v>
+        <v>0.1365</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.455</v>
+        <v>-0.4444</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4054</v>
+        <v>0.3949</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.3949</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.459</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.3949</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.3949</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.459</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L45" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.441</v>
+        <v>0.3949</v>
       </c>
       <c r="N45" t="n">
-        <v>199</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3351</v>
+        <v>0.3531</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1158</v>
+        <v>0.122</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4867</v>
+        <v>-0.4635</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3351</v>
+        <v>0.3531</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3351</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.4962</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3351</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3351</v>
+        <v>0.8712</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.4962</v>
       </c>
       <c r="K46" t="n">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3351</v>
+        <v>0.375</v>
       </c>
       <c r="N46" t="n">
-        <v>116</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3349</v>
+        <v>0.2646</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1157</v>
+        <v>0.0914</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4868</v>
+        <v>-0.5038</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3349</v>
+        <v>0.2646</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3349</v>
+        <v>0.2646</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3349</v>
+        <v>0.2646</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3349</v>
+        <v>0.2646</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3349</v>
+        <v>0.2646</v>
       </c>
       <c r="N47" t="n">
         <v>134</v>
@@ -2608,47 +2608,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3159</v>
+        <v>0.2412</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1092</v>
+        <v>0.0833</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4954</v>
+        <v>-0.5144</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3159</v>
+        <v>0.2412</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.2968</v>
+        <v>0.2412</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6127</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.2968</v>
+        <v>0.2412</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1543</v>
+        <v>0.2412</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6127</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="L48" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4584</v>
+        <v>0.2412</v>
       </c>
       <c r="N48" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3101</v>
+        <v>0.2311</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1072</v>
+        <v>0.0799</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.498</v>
+        <v>-0.519</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3101</v>
+        <v>0.2311</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3101</v>
+        <v>0.2311</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3101</v>
+        <v>0.2311</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3101</v>
+        <v>0.2311</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.3101</v>
+        <v>0.2311</v>
       </c>
       <c r="N49" t="n">
         <v>138</v>
@@ -2704,31 +2704,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1453</v>
+        <v>0.2017</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0502</v>
+        <v>0.0697</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5724</v>
+        <v>-0.5324</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1453</v>
+        <v>0.2017</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.2278</v>
+        <v>-1.1795</v>
       </c>
       <c r="G50" t="n">
-        <v>1.3731</v>
+        <v>1.3812</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.2278</v>
+        <v>-1.1795</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6384</v>
+        <v>-0.6369</v>
       </c>
       <c r="J50" t="n">
-        <v>1.3731</v>
+        <v>1.3812</v>
       </c>
       <c r="K50" t="n">
         <v>125</v>
@@ -2737,7 +2737,7 @@
         <v>155</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7347</v>
+        <v>0.7443</v>
       </c>
       <c r="N50" t="n">
         <v>280</v>
@@ -2746,231 +2746,231 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0366</v>
+        <v>-0.0125</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0126</v>
+        <v>-0.0043</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.6299</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0366</v>
+        <v>-0.0125</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0366</v>
+        <v>-1.0961</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1.0836</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0366</v>
+        <v>-1.0961</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0366</v>
+        <v>-0.5919</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1.0836</v>
       </c>
       <c r="K51" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0366</v>
+        <v>0.4916999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>116</v>
+        <v>300</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0237</v>
+        <v>-0.0182</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.669</v>
+        <v>-0.6482</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="N52" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.073</v>
+        <v>-0.1249</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0252</v>
+        <v>-0.0432</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.671</v>
+        <v>-0.6811</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.073</v>
+        <v>-0.1249</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.073</v>
+        <v>-0.1249</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.073</v>
+        <v>-0.1249</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.073</v>
+        <v>-0.1249</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.073</v>
+        <v>-0.1249</v>
       </c>
       <c r="N53" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1158</v>
+        <v>-0.134</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.04</v>
+        <v>-0.0463</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6903</v>
+        <v>-0.6852</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1158</v>
+        <v>-0.134</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1158</v>
+        <v>-0.134</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1158</v>
+        <v>-0.134</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1158</v>
+        <v>-0.134</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1158</v>
+        <v>-0.134</v>
       </c>
       <c r="N54" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1327</v>
+        <v>-0.2069</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0459</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6979</v>
+        <v>-0.7184</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1327</v>
+        <v>-0.2069</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.1366</v>
+        <v>-0.2069</v>
       </c>
       <c r="G55" t="n">
-        <v>1.0039</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.1366</v>
+        <v>-0.2069</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.591</v>
+        <v>-0.2069</v>
       </c>
       <c r="J55" t="n">
-        <v>1.0039</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="L55" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4129</v>
+        <v>-0.2069</v>
       </c>
       <c r="N55" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2558</v>
+        <v>-0.3241</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.112</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2558</v>
+        <v>-0.3241</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2558</v>
+        <v>-0.3241</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2558</v>
+        <v>-0.3241</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2558</v>
+        <v>-0.3241</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2558</v>
+        <v>-0.3241</v>
       </c>
       <c r="N56" t="n">
         <v>134</v>
@@ -3026,31 +3026,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.737</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2547</v>
+        <v>-0.1991</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9707</v>
+        <v>-0.8865</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.737</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.5335</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.1448</v>
+        <v>-0.0426</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.5335</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.6166</v>
+        <v>-0.5472</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.1448</v>
+        <v>-0.0426</v>
       </c>
       <c r="K57" t="n">
         <v>113</v>
@@ -3059,7 +3059,7 @@
         <v>103</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.7614000000000001</v>
+        <v>-0.5898</v>
       </c>
       <c r="N57" t="n">
         <v>216</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.7601</v>
+        <v>-0.7821</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2627</v>
+        <v>-0.2703</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.9812</v>
+        <v>-0.9802</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.7601</v>
+        <v>-0.7821</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.7601</v>
+        <v>-0.7821</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.7601</v>
+        <v>-0.7821</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.7601</v>
+        <v>-0.7821</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.7601</v>
+        <v>-0.7821</v>
       </c>
       <c r="N58" t="n">
         <v>138</v>
@@ -3118,31 +3118,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.099</v>
+        <v>-1.0598</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3798</v>
+        <v>-0.3662</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.1342</v>
+        <v>-1.1066</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.099</v>
+        <v>-1.0598</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.4171</v>
+        <v>-0.3516</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.6819</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.4171</v>
+        <v>-0.3516</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4343</v>
+        <v>-0.3607</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.6819</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="K59" t="n">
         <v>152</v>
@@ -3151,7 +3151,7 @@
         <v>47</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.1162</v>
+        <v>-1.0689</v>
       </c>
       <c r="N59" t="n">
         <v>199</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.1535</v>
+        <v>-1.2329</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3986</v>
+        <v>-0.426</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.1588</v>
+        <v>-1.1854</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.1535</v>
+        <v>-1.2329</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.1535</v>
+        <v>-1.2329</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.1535</v>
+        <v>-1.2329</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1535</v>
+        <v>-1.2329</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.1535</v>
+        <v>-1.2329</v>
       </c>
       <c r="N60" t="n">
         <v>134</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.2064</v>
+        <v>-1.2775</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4169</v>
+        <v>-0.4415</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.1826</v>
+        <v>-1.2057</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.2064</v>
+        <v>-1.2775</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.2064</v>
+        <v>-1.2775</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.2064</v>
+        <v>-1.2775</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.2064</v>
+        <v>-1.2775</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-1.2064</v>
+        <v>-1.2775</v>
       </c>
       <c r="N61" t="n">
         <v>134</v>
@@ -3349,10 +3349,10 @@
         <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3497</v>
+        <v>1.4367</v>
       </c>
       <c r="J2" t="n">
-        <v>39.1413</v>
+        <v>41.6643</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4667</v>
+        <v>0.4596</v>
       </c>
       <c r="J3" t="n">
-        <v>13.5343</v>
+        <v>13.3284</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2792</v>
+        <v>0.2874</v>
       </c>
       <c r="J4" t="n">
-        <v>8.0968</v>
+        <v>8.3346</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.043</v>
+        <v>-0.0297</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.247</v>
+        <v>-0.8613</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.98</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1391</v>
+        <v>-0.131</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.0339</v>
+        <v>-3.799</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.11</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2909</v>
+        <v>0.2896</v>
       </c>
       <c r="J7" t="n">
-        <v>8.4361</v>
+        <v>8.398400000000001</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0431</v>
+        <v>-0.053</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2499</v>
+        <v>-1.537</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.92</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1041</v>
+        <v>-0.1179</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.0189</v>
+        <v>-3.4191</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1472</v>
+        <v>-0.1624</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.2688</v>
+        <v>-4.7096</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3076</v>
+        <v>-0.3216</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.920400000000001</v>
+        <v>-9.3264</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.53</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1411</v>
+        <v>1.1492</v>
       </c>
       <c r="J12" t="n">
-        <v>23.9631</v>
+        <v>24.1332</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.45</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0431</v>
+        <v>1.007</v>
       </c>
       <c r="J13" t="n">
-        <v>21.9051</v>
+        <v>21.147</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.39</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9487</v>
+        <v>0.8993</v>
       </c>
       <c r="J14" t="n">
-        <v>19.9227</v>
+        <v>18.8853</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>1.37</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9097</v>
+        <v>0.8628</v>
       </c>
       <c r="J15" t="n">
-        <v>19.1037</v>
+        <v>18.1188</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>1.23</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5944</v>
+        <v>0.5838</v>
       </c>
       <c r="J16" t="n">
-        <v>12.4824</v>
+        <v>12.2598</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0321</v>
+        <v>-0.0521</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6741</v>
+        <v>-1.0941</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>0.79</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2159</v>
+        <v>-0.2368</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.5339</v>
+        <v>-4.9728</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>0.71</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2913</v>
+        <v>-0.3109</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.1173</v>
+        <v>-6.5289</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>0.63</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3657</v>
+        <v>-0.3826</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.6797</v>
+        <v>-8.034599999999999</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4312</v>
+        <v>-0.4448</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.055199999999999</v>
+        <v>-9.3408</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.41</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6325</v>
+        <v>0.6129</v>
       </c>
       <c r="J22" t="n">
-        <v>18.975</v>
+        <v>18.387</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.13</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2448</v>
+        <v>0.2503</v>
       </c>
       <c r="J23" t="n">
-        <v>7.344</v>
+        <v>7.509</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0352</v>
+        <v>0.0386</v>
       </c>
       <c r="J24" t="n">
-        <v>1.056</v>
+        <v>1.158</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.68</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3498</v>
+        <v>-0.3618</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.494</v>
+        <v>-10.854</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.54</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.479</v>
+        <v>-0.4854</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.37</v>
+        <v>-14.562</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6262</v>
+        <v>0.6271</v>
       </c>
       <c r="J27" t="n">
-        <v>18.786</v>
+        <v>18.813</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.34</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4469</v>
+        <v>0.4585</v>
       </c>
       <c r="J28" t="n">
-        <v>13.407</v>
+        <v>13.755</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.221</v>
+        <v>0.2388</v>
       </c>
       <c r="J29" t="n">
-        <v>6.63</v>
+        <v>7.164</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1676</v>
+        <v>0.1854</v>
       </c>
       <c r="J30" t="n">
-        <v>5.028</v>
+        <v>5.562</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2182</v>
+        <v>-0.2275</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.546</v>
+        <v>-6.825</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.58</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1836</v>
+        <v>1.216</v>
       </c>
       <c r="J32" t="n">
-        <v>22.4884</v>
+        <v>23.104</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.57</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1721</v>
+        <v>1.1992</v>
       </c>
       <c r="J33" t="n">
-        <v>22.2699</v>
+        <v>22.7848</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1265</v>
+        <v>1.1322</v>
       </c>
       <c r="J34" t="n">
-        <v>21.4035</v>
+        <v>21.5118</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>1.53</v>
       </c>
       <c r="I35" t="n">
-        <v>1.1265</v>
+        <v>1.1322</v>
       </c>
       <c r="J35" t="n">
-        <v>21.4035</v>
+        <v>21.5118</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>1.42</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9397</v>
       </c>
       <c r="J36" t="n">
-        <v>18.7036</v>
+        <v>17.8543</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>0.85</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1203</v>
+        <v>-0.1489</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.2857</v>
+        <v>-2.8291</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1887</v>
+        <v>-0.2156</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.5853</v>
+        <v>-4.0964</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>0.63</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.35</v>
+        <v>-0.3706</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.65</v>
+        <v>-7.0414</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.5</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4684</v>
+        <v>-0.4828</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.8996</v>
+        <v>-9.1732</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.32</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.6411</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.1524</v>
+        <v>-12.1809</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.82</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2097</v>
+        <v>1.3286</v>
       </c>
       <c r="J42" t="n">
-        <v>25.4037</v>
+        <v>27.9006</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.35</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6483</v>
+        <v>0.7245</v>
       </c>
       <c r="J43" t="n">
-        <v>13.6143</v>
+        <v>15.2145</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5833</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>12.2493</v>
+        <v>13.7067</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5565</v>
+        <v>0.623</v>
       </c>
       <c r="J45" t="n">
-        <v>11.6865</v>
+        <v>13.083</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>1.22</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4732</v>
+        <v>0.53</v>
       </c>
       <c r="J46" t="n">
-        <v>9.937200000000001</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>0.97</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0055</v>
+        <v>-0.0236</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.1155</v>
+        <v>-0.4956</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>0.92</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0727</v>
+        <v>-0.0935</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.5267</v>
+        <v>-1.9635</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.66</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3385</v>
+        <v>-0.3564</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.1085</v>
+        <v>-7.4844</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.57</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4228</v>
+        <v>-0.4367</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.8788</v>
+        <v>-9.1707</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4415</v>
+        <v>-0.4544</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.2715</v>
+        <v>-9.542400000000001</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6602</v>
+        <v>0.7287</v>
       </c>
       <c r="J52" t="n">
-        <v>23.7672</v>
+        <v>26.2332</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.27</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5767</v>
+        <v>0.637</v>
       </c>
       <c r="J53" t="n">
-        <v>20.7612</v>
+        <v>22.932</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.14</v>
       </c>
       <c r="I54" t="n">
-        <v>0.387</v>
+        <v>0.4178</v>
       </c>
       <c r="J54" t="n">
-        <v>13.932</v>
+        <v>15.0408</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0801</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.042</v>
+        <v>-2.8836</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.9</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3843</v>
+        <v>-0.3667</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.8348</v>
+        <v>-13.2012</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.32</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5112</v>
+        <v>0.57</v>
       </c>
       <c r="J57" t="n">
-        <v>18.4032</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.14</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3134</v>
+        <v>0.3195</v>
       </c>
       <c r="J58" t="n">
-        <v>11.2824</v>
+        <v>11.502</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.09</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2161</v>
+        <v>0.2256</v>
       </c>
       <c r="J59" t="n">
-        <v>7.7796</v>
+        <v>8.121600000000001</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1319</v>
+        <v>0.1426</v>
       </c>
       <c r="J60" t="n">
-        <v>4.7484</v>
+        <v>5.1336</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4064</v>
+        <v>-0.4145</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.6304</v>
+        <v>-14.922</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.37</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7153</v>
+        <v>0.7886</v>
       </c>
       <c r="J62" t="n">
-        <v>20.0284</v>
+        <v>22.0808</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.15</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4024</v>
+        <v>0.439</v>
       </c>
       <c r="J63" t="n">
-        <v>11.2672</v>
+        <v>12.292</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4024</v>
+        <v>0.439</v>
       </c>
       <c r="J64" t="n">
-        <v>11.2672</v>
+        <v>12.292</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1251</v>
+        <v>-0.1212</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.5028</v>
+        <v>-3.3936</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.97</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1623</v>
+        <v>-0.1578</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.5444</v>
+        <v>-4.4184</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.2</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3917</v>
+        <v>0.4271</v>
       </c>
       <c r="J67" t="n">
-        <v>10.9676</v>
+        <v>11.9588</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.19</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3809</v>
+        <v>0.4113</v>
       </c>
       <c r="J68" t="n">
-        <v>10.6652</v>
+        <v>11.5164</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.08</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2001</v>
+        <v>0.209</v>
       </c>
       <c r="J69" t="n">
-        <v>5.6028</v>
+        <v>5.852</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.91</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1255</v>
+        <v>-0.1373</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.514</v>
+        <v>-3.8444</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3101</v>
+        <v>-0.3218</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.6828</v>
+        <v>-9.010400000000001</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.53</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9196</v>
+        <v>1.01</v>
       </c>
       <c r="J72" t="n">
-        <v>25.7488</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4727</v>
+        <v>0.522</v>
       </c>
       <c r="J73" t="n">
-        <v>13.2356</v>
+        <v>14.616</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.12</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3543</v>
+        <v>0.3685</v>
       </c>
       <c r="J74" t="n">
-        <v>9.920400000000001</v>
+        <v>10.318</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0359</v>
+        <v>-0.0247</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.0052</v>
+        <v>-0.6916</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.9</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3907</v>
+        <v>-0.3711</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.9396</v>
+        <v>-10.3908</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.31</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5168</v>
+        <v>0.5729</v>
       </c>
       <c r="J77" t="n">
-        <v>14.4704</v>
+        <v>16.0412</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3125</v>
+        <v>0.3146</v>
       </c>
       <c r="J78" t="n">
-        <v>8.75</v>
+        <v>8.8088</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1534</v>
+        <v>-0.1672</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.2952</v>
+        <v>-4.6816</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.82</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.216</v>
+        <v>-0.2302</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.048</v>
+        <v>-6.4456</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2952</v>
+        <v>-0.3082</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.265599999999999</v>
+        <v>-8.6296</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.34</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4146</v>
+        <v>0.4665</v>
       </c>
       <c r="J82" t="n">
-        <v>12.438</v>
+        <v>13.995</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.32</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4005</v>
+        <v>0.4488</v>
       </c>
       <c r="J83" t="n">
-        <v>12.015</v>
+        <v>13.464</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.04</v>
       </c>
       <c r="I84" t="n">
-        <v>0.076</v>
+        <v>0.0877</v>
       </c>
       <c r="J84" t="n">
-        <v>2.28</v>
+        <v>2.631</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0405</v>
+        <v>0.0497</v>
       </c>
       <c r="J85" t="n">
-        <v>1.215</v>
+        <v>1.491</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.62</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4177</v>
+        <v>-0.425</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.531</v>
+        <v>-12.75</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.25</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3627</v>
+        <v>0.3884</v>
       </c>
       <c r="J87" t="n">
-        <v>10.881</v>
+        <v>11.652</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>1.23</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3466</v>
+        <v>0.3633</v>
       </c>
       <c r="J88" t="n">
-        <v>10.398</v>
+        <v>10.899</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1894</v>
+        <v>0.2022</v>
       </c>
       <c r="J89" t="n">
-        <v>5.682</v>
+        <v>6.066</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1292</v>
+        <v>0.1419</v>
       </c>
       <c r="J90" t="n">
-        <v>3.876</v>
+        <v>4.257</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2295</v>
+        <v>-0.2407</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.885</v>
+        <v>-7.221</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0732</v>
+        <v>-0.0876</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.9032</v>
+        <v>-2.2776</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>0.93</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0854</v>
+        <v>-0.1003</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.2204</v>
+        <v>-2.6078</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>0.89</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1309</v>
+        <v>-0.1473</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.4034</v>
+        <v>-3.8298</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>0.79</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2313</v>
+        <v>-0.2485</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.0138</v>
+        <v>-6.461</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.73</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2896</v>
+        <v>-0.3057</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.5296</v>
+        <v>-7.9482</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.54</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9056</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>23.5456</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.7369</v>
       </c>
       <c r="J98" t="n">
-        <v>17.2328</v>
+        <v>19.1594</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>1.2</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4619</v>
+        <v>0.5129</v>
       </c>
       <c r="J99" t="n">
-        <v>12.0094</v>
+        <v>13.3354</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3567</v>
+        <v>0.3773</v>
       </c>
       <c r="J100" t="n">
-        <v>9.2742</v>
+        <v>9.809799999999999</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>1.05</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1391</v>
+        <v>0.1603</v>
       </c>
       <c r="J101" t="n">
-        <v>3.6166</v>
+        <v>4.1678</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>0.73</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.257</v>
+        <v>-0.2806</v>
       </c>
       <c r="J102" t="n">
-        <v>-5.14</v>
+        <v>-5.612</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>0.73</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.257</v>
+        <v>-0.2806</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.14</v>
+        <v>-5.612</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2968</v>
+        <v>-0.3189</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.936</v>
+        <v>-6.378</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.59</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3875</v>
+        <v>-0.4061</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.75</v>
+        <v>-8.122</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.43</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5375</v>
+        <v>-0.5466</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.75</v>
+        <v>-10.932</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.83</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1981</v>
+        <v>1.3202</v>
       </c>
       <c r="J107" t="n">
-        <v>23.962</v>
+        <v>26.404</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.61</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9468</v>
+        <v>1.0527</v>
       </c>
       <c r="J108" t="n">
-        <v>18.936</v>
+        <v>21.054</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>1.46</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7731</v>
+        <v>0.8641</v>
       </c>
       <c r="J109" t="n">
-        <v>15.462</v>
+        <v>17.282</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>1.44</v>
       </c>
       <c r="I110" t="n">
-        <v>0.749</v>
+        <v>0.8378</v>
       </c>
       <c r="J110" t="n">
-        <v>14.98</v>
+        <v>16.756</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>1.19</v>
       </c>
       <c r="I111" t="n">
-        <v>0.416</v>
+        <v>0.469</v>
       </c>
       <c r="J111" t="n">
-        <v>8.32</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.57</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9358</v>
+        <v>1.0337</v>
       </c>
       <c r="J112" t="n">
-        <v>21.5234</v>
+        <v>23.7751</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.43</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7607</v>
+        <v>0.845</v>
       </c>
       <c r="J113" t="n">
-        <v>17.4961</v>
+        <v>19.435</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.38</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6969</v>
+        <v>0.7754</v>
       </c>
       <c r="J114" t="n">
-        <v>16.0287</v>
+        <v>17.8342</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>1.21</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4724</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="J115" t="n">
-        <v>10.8652</v>
+        <v>12.0911</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5899</v>
+        <v>-0.5455</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.5677</v>
+        <v>-12.5465</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.01</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1113</v>
+        <v>0.097</v>
       </c>
       <c r="J117" t="n">
-        <v>2.5599</v>
+        <v>2.231</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>0.92</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0814</v>
+        <v>-0.1003</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.8722</v>
+        <v>-2.3069</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2026</v>
+        <v>-0.2221</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.6598</v>
+        <v>-5.1083</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.62</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3816</v>
+        <v>-0.3966</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.7768</v>
+        <v>-9.1218</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.49</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5026</v>
+        <v>-0.511</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.5598</v>
+        <v>-11.753</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.49</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8338</v>
+        <v>0.9246</v>
       </c>
       <c r="J122" t="n">
-        <v>20.0112</v>
+        <v>22.1904</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.48</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8213</v>
+        <v>0.9111</v>
       </c>
       <c r="J123" t="n">
-        <v>19.7112</v>
+        <v>21.8664</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.34</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6437</v>
+        <v>0.7174</v>
       </c>
       <c r="J124" t="n">
-        <v>15.4488</v>
+        <v>17.2176</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>1.26</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5402</v>
+        <v>0.6021</v>
       </c>
       <c r="J125" t="n">
-        <v>12.9648</v>
+        <v>14.4504</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3378</v>
+        <v>-0.3139</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.107200000000001</v>
+        <v>-7.5336</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2655</v>
+        <v>0.2567</v>
       </c>
       <c r="J127" t="n">
-        <v>6.372</v>
+        <v>6.1608</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2427</v>
+        <v>0.2348</v>
       </c>
       <c r="J128" t="n">
-        <v>5.8248</v>
+        <v>5.6352</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.84</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1793</v>
+        <v>-0.1972</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.3032</v>
+        <v>-4.7328</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2564</v>
+        <v>-0.2741</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.1536</v>
+        <v>-6.5784</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.37</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6186</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.8464</v>
+        <v>-14.8416</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.5</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1621</v>
+        <v>1.1225</v>
       </c>
       <c r="J132" t="n">
-        <v>30.2146</v>
+        <v>29.185</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9113</v>
+        <v>0.8517</v>
       </c>
       <c r="J133" t="n">
-        <v>23.6938</v>
+        <v>22.1442</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7226</v>
+        <v>0.6862</v>
       </c>
       <c r="J134" t="n">
-        <v>18.7876</v>
+        <v>17.8412</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.87</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4688</v>
+        <v>-0.444</v>
       </c>
       <c r="J135" t="n">
-        <v>-12.1888</v>
+        <v>-11.544</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.65</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.0275</v>
+        <v>-0.9371</v>
       </c>
       <c r="J136" t="n">
-        <v>-26.715</v>
+        <v>-24.3646</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.37</v>
       </c>
       <c r="I137" t="n">
-        <v>0.729</v>
+        <v>0.6998</v>
       </c>
       <c r="J137" t="n">
-        <v>18.954</v>
+        <v>18.1948</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.28</v>
       </c>
       <c r="I138" t="n">
-        <v>0.575</v>
+        <v>0.5603</v>
       </c>
       <c r="J138" t="n">
-        <v>14.95</v>
+        <v>14.5678</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.96</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.074</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.6952</v>
+        <v>-1.924</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2612</v>
+        <v>-0.2739</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.7912</v>
+        <v>-7.1214</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.329</v>
+        <v>-0.3402</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.554</v>
+        <v>-8.8452</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>2.06</v>
       </c>
       <c r="I142" t="n">
-        <v>1.7663</v>
+        <v>1.7703</v>
       </c>
       <c r="J142" t="n">
-        <v>42.3912</v>
+        <v>42.4872</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.47</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0725</v>
+        <v>1.034</v>
       </c>
       <c r="J143" t="n">
-        <v>25.74</v>
+        <v>24.816</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.36</v>
       </c>
       <c r="I144" t="n">
-        <v>0.893</v>
+        <v>0.8469</v>
       </c>
       <c r="J144" t="n">
-        <v>21.432</v>
+        <v>20.3256</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0406</v>
       </c>
       <c r="J145" t="n">
-        <v>0.2088</v>
+        <v>0.9744</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4119</v>
+        <v>-0.3796</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.8856</v>
+        <v>-9.1104</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.12</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3734</v>
+        <v>0.3547</v>
       </c>
       <c r="J147" t="n">
-        <v>8.961600000000001</v>
+        <v>8.5128</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1341</v>
+        <v>0.123</v>
       </c>
       <c r="J148" t="n">
-        <v>3.2184</v>
+        <v>2.952</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.6</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4027</v>
+        <v>-0.4163</v>
       </c>
       <c r="J149" t="n">
-        <v>-9.6648</v>
+        <v>-9.991199999999999</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.6</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4027</v>
+        <v>-0.4163</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.6648</v>
+        <v>-9.991199999999999</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.59</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.412</v>
+        <v>-0.4252</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.888</v>
+        <v>-10.2048</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.6221</v>
       </c>
       <c r="J152" t="n">
-        <v>16.7076</v>
+        <v>16.1746</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3573</v>
+        <v>0.3592</v>
       </c>
       <c r="J153" t="n">
-        <v>9.2898</v>
+        <v>9.3392</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0906</v>
+        <v>-0.1009</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.3556</v>
+        <v>-2.6234</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1257</v>
+        <v>-0.1375</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.2682</v>
+        <v>-3.575</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2518</v>
+        <v>-0.2645</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.5468</v>
+        <v>-6.877</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.31</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8288</v>
+        <v>0.7817</v>
       </c>
       <c r="J157" t="n">
-        <v>21.5488</v>
+        <v>20.3242</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.29</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7821</v>
+        <v>0.7408</v>
       </c>
       <c r="J158" t="n">
-        <v>20.3346</v>
+        <v>19.2608</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3665</v>
+        <v>0.3671</v>
       </c>
       <c r="J159" t="n">
-        <v>9.529</v>
+        <v>9.544600000000001</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1622</v>
+        <v>0.1763</v>
       </c>
       <c r="J160" t="n">
-        <v>4.2172</v>
+        <v>4.5838</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0945</v>
+        <v>0.1111</v>
       </c>
       <c r="J161" t="n">
-        <v>2.457</v>
+        <v>2.8886</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9228</v>
       </c>
       <c r="J162" t="n">
-        <v>27.5352</v>
+        <v>25.8384</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6653</v>
+        <v>0.6373</v>
       </c>
       <c r="J163" t="n">
-        <v>18.6284</v>
+        <v>17.8444</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3942</v>
+        <v>0.3923</v>
       </c>
       <c r="J164" t="n">
-        <v>11.0376</v>
+        <v>10.9844</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1307</v>
+        <v>0.1458</v>
       </c>
       <c r="J165" t="n">
-        <v>3.6596</v>
+        <v>4.0824</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.98</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1329</v>
+        <v>-0.1266</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.7212</v>
+        <v>-3.5448</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.71</v>
+        <v>0.6775</v>
       </c>
       <c r="J167" t="n">
-        <v>19.88</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4949</v>
+        <v>0.482</v>
       </c>
       <c r="J168" t="n">
-        <v>13.8572</v>
+        <v>13.496</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>0.8</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2326</v>
+        <v>-0.2474</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.5128</v>
+        <v>-6.9272</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.73</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3012</v>
+        <v>-0.3148</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.4336</v>
+        <v>-8.814399999999999</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.64</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3864</v>
+        <v>-0.3972</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.8192</v>
+        <v>-11.1216</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.21</v>
       </c>
       <c r="I172" t="n">
-        <v>0.625</v>
+        <v>0.595</v>
       </c>
       <c r="J172" t="n">
-        <v>18.75</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3608</v>
+        <v>0.3567</v>
       </c>
       <c r="J173" t="n">
-        <v>10.824</v>
+        <v>10.701</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.03</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1205</v>
+        <v>0.129</v>
       </c>
       <c r="J174" t="n">
-        <v>3.615</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0437</v>
+        <v>0.0521</v>
       </c>
       <c r="J175" t="n">
-        <v>1.311</v>
+        <v>1.563</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.9</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3638</v>
+        <v>-0.3523</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.914</v>
+        <v>-10.569</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.3</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6048</v>
+        <v>0.5883</v>
       </c>
       <c r="J177" t="n">
-        <v>18.144</v>
+        <v>17.649</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.22</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4645</v>
+        <v>0.4597</v>
       </c>
       <c r="J178" t="n">
-        <v>13.935</v>
+        <v>13.791</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.04</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1108</v>
+        <v>0.1208</v>
       </c>
       <c r="J179" t="n">
-        <v>3.324</v>
+        <v>3.624</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.87</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1707</v>
+        <v>-0.1832</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.121</v>
+        <v>-5.496</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.74</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3018</v>
+        <v>-0.3134</v>
       </c>
       <c r="J181" t="n">
-        <v>-9.054</v>
+        <v>-9.401999999999999</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.67</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3808</v>
+        <v>1.3546</v>
       </c>
       <c r="J182" t="n">
-        <v>38.6624</v>
+        <v>37.9288</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.28</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7705</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="J183" t="n">
-        <v>21.574</v>
+        <v>20.3924</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.05</v>
       </c>
       <c r="I184" t="n">
-        <v>0.171</v>
+        <v>0.1824</v>
       </c>
       <c r="J184" t="n">
-        <v>4.788</v>
+        <v>5.1072</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.87</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4688</v>
+        <v>-0.444</v>
       </c>
       <c r="J185" t="n">
-        <v>-13.1264</v>
+        <v>-12.432</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.75</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7834</v>
+        <v>-0.7245</v>
       </c>
       <c r="J186" t="n">
-        <v>-21.9352</v>
+        <v>-20.286</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4726</v>
+        <v>0.4656</v>
       </c>
       <c r="J187" t="n">
-        <v>13.2328</v>
+        <v>13.0368</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3235</v>
+        <v>0.3264</v>
       </c>
       <c r="J188" t="n">
-        <v>9.058</v>
+        <v>9.139200000000001</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.03</v>
       </c>
       <c r="I189" t="n">
-        <v>0.0905</v>
+        <v>0.099</v>
       </c>
       <c r="J189" t="n">
-        <v>2.534</v>
+        <v>2.772</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.85</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1889</v>
+        <v>-0.2022</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.2892</v>
+        <v>-5.6616</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.8</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2399</v>
+        <v>-0.2531</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.7172</v>
+        <v>-7.0868</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>0.86</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.1052</v>
+        <v>-0.1347</v>
       </c>
       <c r="J192" t="n">
-        <v>-2.2092</v>
+        <v>-2.8287</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>0.65</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3303</v>
+        <v>-0.3519</v>
       </c>
       <c r="J193" t="n">
-        <v>-6.9363</v>
+        <v>-7.3899</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.55</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4201</v>
+        <v>-0.4377</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.822100000000001</v>
+        <v>-9.191700000000001</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.52</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4481</v>
+        <v>-0.464</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.4101</v>
+        <v>-9.744</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.47</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4952</v>
+        <v>-0.508</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.3992</v>
+        <v>-10.668</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>2.23</v>
       </c>
       <c r="I197" t="n">
-        <v>1.8338</v>
+        <v>1.9158</v>
       </c>
       <c r="J197" t="n">
-        <v>38.5098</v>
+        <v>40.2318</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.81</v>
       </c>
       <c r="I198" t="n">
-        <v>1.4396</v>
+        <v>1.4352</v>
       </c>
       <c r="J198" t="n">
-        <v>30.2316</v>
+        <v>30.1392</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.38</v>
       </c>
       <c r="I199" t="n">
-        <v>0.9008</v>
+        <v>0.8605</v>
       </c>
       <c r="J199" t="n">
-        <v>18.9168</v>
+        <v>18.0705</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>1.21</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5112</v>
+        <v>0.5163</v>
       </c>
       <c r="J200" t="n">
-        <v>10.7352</v>
+        <v>10.8423</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>1.19</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4617</v>
+        <v>0.4719</v>
       </c>
       <c r="J201" t="n">
-        <v>9.6957</v>
+        <v>9.9099</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>2.22</v>
       </c>
       <c r="I202" t="n">
-        <v>1.8338</v>
+        <v>1.8717</v>
       </c>
       <c r="J202" t="n">
-        <v>7.3352</v>
+        <v>7.4868</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>2.08</v>
       </c>
       <c r="I203" t="n">
-        <v>1.7043</v>
+        <v>1.7188</v>
       </c>
       <c r="J203" t="n">
-        <v>6.8172</v>
+        <v>6.8752</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.95</v>
       </c>
       <c r="I204" t="n">
-        <v>1.5668</v>
+        <v>1.5743</v>
       </c>
       <c r="J204" t="n">
-        <v>6.2672</v>
+        <v>6.2972</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.53</v>
       </c>
       <c r="I205" t="n">
-        <v>1.1069</v>
+        <v>1.0818</v>
       </c>
       <c r="J205" t="n">
-        <v>4.4276</v>
+        <v>4.3272</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3872</v>
+        <v>-0.3415</v>
       </c>
       <c r="J206" t="n">
-        <v>-1.5488</v>
+        <v>-1.366</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>0.74</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.2383</v>
+        <v>-0.2642</v>
       </c>
       <c r="J207" t="n">
-        <v>-0.9532</v>
+        <v>-1.0568</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.71</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2696</v>
+        <v>-0.2942</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.0784</v>
+        <v>-1.1768</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.58</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3917</v>
+        <v>-0.411</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.5668</v>
+        <v>-1.644</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.5</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4657</v>
+        <v>-0.4807</v>
       </c>
       <c r="J210" t="n">
-        <v>-1.8628</v>
+        <v>-1.9228</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.49</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4751</v>
+        <v>-0.4895</v>
       </c>
       <c r="J211" t="n">
-        <v>-1.9004</v>
+        <v>-1.958</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8716</v>
+        <v>0.8083</v>
       </c>
       <c r="J212" t="n">
-        <v>4.358</v>
+        <v>4.0415</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.07</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2543</v>
+        <v>0.2434</v>
       </c>
       <c r="J213" t="n">
-        <v>1.2715</v>
+        <v>1.217</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2343</v>
+        <v>-0.253</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.1715</v>
+        <v>-1.265</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.64</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3672</v>
+        <v>-0.3821</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.836</v>
+        <v>-1.9105</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.13</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8315</v>
+        <v>-0.8148</v>
       </c>
       <c r="J216" t="n">
-        <v>-4.1575</v>
+        <v>-4.074</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>2.36</v>
       </c>
       <c r="I217" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J217" t="n">
-        <v>9.169</v>
+        <v>9.686</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.73</v>
       </c>
       <c r="I218" t="n">
-        <v>1.3771</v>
+        <v>1.3638</v>
       </c>
       <c r="J218" t="n">
-        <v>6.8855</v>
+        <v>6.819</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.28</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7101</v>
+        <v>0.6868</v>
       </c>
       <c r="J219" t="n">
-        <v>3.5505</v>
+        <v>3.434</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>1.03</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0376</v>
+        <v>0.0713</v>
       </c>
       <c r="J220" t="n">
-        <v>0.188</v>
+        <v>0.3565</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.61</v>
       </c>
       <c r="I221" t="n">
-        <v>-1.1732</v>
+        <v>-1.0549</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.866</v>
+        <v>-5.2745</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.4</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9895</v>
+        <v>0.9353</v>
       </c>
       <c r="J222" t="n">
-        <v>15.832</v>
+        <v>14.9648</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.35</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8895</v>
+        <v>0.8403</v>
       </c>
       <c r="J223" t="n">
-        <v>14.232</v>
+        <v>13.4448</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7115</v>
+        <v>0.6832</v>
       </c>
       <c r="J224" t="n">
-        <v>11.384</v>
+        <v>10.9312</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6442</v>
+        <v>0.6229</v>
       </c>
       <c r="J225" t="n">
-        <v>10.3072</v>
+        <v>9.9664</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>1.06</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1686</v>
+        <v>0.1889</v>
       </c>
       <c r="J226" t="n">
-        <v>2.6976</v>
+        <v>3.0224</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.06</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2106</v>
+        <v>0.2057</v>
       </c>
       <c r="J227" t="n">
-        <v>3.3696</v>
+        <v>3.2912</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.04</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1621</v>
+        <v>0.1581</v>
       </c>
       <c r="J228" t="n">
-        <v>2.5936</v>
+        <v>2.5296</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.82</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2003</v>
+        <v>-0.2181</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.2048</v>
+        <v>-3.4896</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3262</v>
+        <v>-0.3416</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.2192</v>
+        <v>-5.4656</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4015</v>
+        <v>-0.4138</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.424</v>
+        <v>-6.6208</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.06</v>
       </c>
       <c r="I232" t="n">
-        <v>0.1847</v>
+        <v>0.1868</v>
       </c>
       <c r="J232" t="n">
-        <v>4.9869</v>
+        <v>5.0436</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>0.92</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1038</v>
+        <v>-0.1176</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.8026</v>
+        <v>-3.1752</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.88</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1466</v>
+        <v>-0.162</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.9582</v>
+        <v>-4.374</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.86</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1676</v>
+        <v>-0.1832</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.5252</v>
+        <v>-4.9464</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1779</v>
+        <v>-0.1937</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.8033</v>
+        <v>-5.2299</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.71</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4005</v>
+        <v>1.3804</v>
       </c>
       <c r="J237" t="n">
-        <v>37.8135</v>
+        <v>37.2708</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.35</v>
       </c>
       <c r="I238" t="n">
-        <v>0.903</v>
+        <v>0.8498</v>
       </c>
       <c r="J238" t="n">
-        <v>24.381</v>
+        <v>22.9446</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.04</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1158</v>
+        <v>0.1354</v>
       </c>
       <c r="J239" t="n">
-        <v>3.1266</v>
+        <v>3.6558</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>1.02</v>
       </c>
       <c r="I240" t="n">
-        <v>0.0439</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="J240" t="n">
-        <v>1.1853</v>
+        <v>1.7604</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.95</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.254</v>
+        <v>-0.2397</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.858</v>
+        <v>-6.4719</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.08</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3325</v>
+        <v>0.3062</v>
       </c>
       <c r="J242" t="n">
-        <v>6.3175</v>
+        <v>5.8178</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>0.79</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2126</v>
+        <v>-0.2342</v>
       </c>
       <c r="J243" t="n">
-        <v>-4.0394</v>
+        <v>-4.4498</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.76</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2427</v>
+        <v>-0.2637</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.6113</v>
+        <v>-5.0103</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.5</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4844</v>
+        <v>-0.4953</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.2036</v>
+        <v>-9.4107</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.42</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5649</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.621</v>
+        <v>-10.7331</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>2.43</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J247" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2745</v>
+        <v>1.2586</v>
       </c>
       <c r="J248" t="n">
-        <v>24.2155</v>
+        <v>23.9134</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.28</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6835</v>
+        <v>0.6684</v>
       </c>
       <c r="J249" t="n">
-        <v>12.9865</v>
+        <v>12.6996</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.26</v>
       </c>
       <c r="I250" t="n">
-        <v>0.637</v>
+        <v>0.6271</v>
       </c>
       <c r="J250" t="n">
-        <v>12.103</v>
+        <v>11.9149</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>1.04</v>
       </c>
       <c r="I251" t="n">
-        <v>0.046</v>
+        <v>0.0864</v>
       </c>
       <c r="J251" t="n">
-        <v>0.874</v>
+        <v>1.6416</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.67</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3082</v>
+        <v>1.2904</v>
       </c>
       <c r="J252" t="n">
-        <v>31.3968</v>
+        <v>30.9696</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.66</v>
       </c>
       <c r="I253" t="n">
-        <v>1.2964</v>
+        <v>1.2778</v>
       </c>
       <c r="J253" t="n">
-        <v>31.1136</v>
+        <v>30.6672</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>1.38</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9298</v>
+        <v>0.8812</v>
       </c>
       <c r="J254" t="n">
-        <v>22.3152</v>
+        <v>21.1488</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>1.28</v>
       </c>
       <c r="I255" t="n">
-        <v>0.7117</v>
+        <v>0.6879</v>
       </c>
       <c r="J255" t="n">
-        <v>17.0808</v>
+        <v>16.5096</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.98</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1896</v>
+        <v>-0.1664</v>
       </c>
       <c r="J256" t="n">
-        <v>-4.5504</v>
+        <v>-3.9936</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>0.95</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.036</v>
+        <v>-0.0552</v>
       </c>
       <c r="J257" t="n">
-        <v>-0.864</v>
+        <v>-1.3248</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>0.74</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2656</v>
+        <v>-0.2853</v>
       </c>
       <c r="J258" t="n">
-        <v>-6.3744</v>
+        <v>-6.8472</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>0.72</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2838</v>
+        <v>-0.3032</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.8112</v>
+        <v>-7.2768</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.7</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3023</v>
+        <v>-0.3212</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.2552</v>
+        <v>-7.7088</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.6</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.396</v>
+        <v>-0.4111</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.504</v>
+        <v>-9.866400000000001</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.57</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2014</v>
+        <v>1.1738</v>
       </c>
       <c r="J262" t="n">
-        <v>26.4308</v>
+        <v>25.8236</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.46</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0657</v>
+        <v>1.0247</v>
       </c>
       <c r="J263" t="n">
-        <v>23.4454</v>
+        <v>22.5434</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.42</v>
       </c>
       <c r="I264" t="n">
-        <v>1.0101</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="J264" t="n">
-        <v>22.2222</v>
+        <v>21.1244</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.28</v>
       </c>
       <c r="I265" t="n">
-        <v>0.7248</v>
+        <v>0.697</v>
       </c>
       <c r="J265" t="n">
-        <v>15.9456</v>
+        <v>15.334</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.9</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4329</v>
+        <v>-0.4008</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.5238</v>
+        <v>-8.817600000000001</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1</v>
       </c>
       <c r="I267" t="n">
-        <v>0.079</v>
+        <v>0.0576</v>
       </c>
       <c r="J267" t="n">
-        <v>1.738</v>
+        <v>1.2672</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>0.88</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1249</v>
+        <v>-0.1453</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.7478</v>
+        <v>-3.1966</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.76</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2487</v>
+        <v>-0.2683</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.4714</v>
+        <v>-5.9026</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.74</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2667</v>
+        <v>-0.2861</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.8674</v>
+        <v>-6.2942</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.39</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5926</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.0372</v>
+        <v>-13.0966</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.96</v>
       </c>
       <c r="I272" t="n">
-        <v>1.6009</v>
+        <v>1.6061</v>
       </c>
       <c r="J272" t="n">
-        <v>28.8162</v>
+        <v>28.9098</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.85</v>
       </c>
       <c r="I273" t="n">
-        <v>1.48</v>
+        <v>1.4787</v>
       </c>
       <c r="J273" t="n">
-        <v>26.64</v>
+        <v>26.6166</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.8</v>
       </c>
       <c r="I274" t="n">
-        <v>1.4245</v>
+        <v>1.42</v>
       </c>
       <c r="J274" t="n">
-        <v>25.641</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>1.42</v>
       </c>
       <c r="I275" t="n">
-        <v>0.9749</v>
+        <v>0.931</v>
       </c>
       <c r="J275" t="n">
-        <v>17.5482</v>
+        <v>16.758</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.92</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4243</v>
+        <v>-0.3819</v>
       </c>
       <c r="J276" t="n">
-        <v>-7.6374</v>
+        <v>-6.8742</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>0.83</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1574</v>
+        <v>-0.1825</v>
       </c>
       <c r="J277" t="n">
-        <v>-2.8332</v>
+        <v>-3.285</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>0.78</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2117</v>
+        <v>-0.2356</v>
       </c>
       <c r="J278" t="n">
-        <v>-3.8106</v>
+        <v>-4.2408</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>0.63</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3551</v>
+        <v>-0.3744</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.3918</v>
+        <v>-6.7392</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>0.59</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3918</v>
+        <v>-0.4095</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.0524</v>
+        <v>-7.371</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.47</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5042</v>
+        <v>-0.5151</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.0756</v>
+        <v>-9.271800000000001</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>0.9</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.1127</v>
+        <v>-0.1304</v>
       </c>
       <c r="J282" t="n">
-        <v>-2.9302</v>
+        <v>-3.3904</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>0.86</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1567</v>
+        <v>-0.175</v>
       </c>
       <c r="J283" t="n">
-        <v>-4.0742</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>0.84</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1774</v>
+        <v>-0.1958</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.6124</v>
+        <v>-5.0908</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.83</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1875</v>
+        <v>-0.2059</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.875</v>
+        <v>-5.3534</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.61</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3965</v>
+        <v>-0.4099</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.309</v>
+        <v>-10.6574</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.93</v>
       </c>
       <c r="I287" t="n">
-        <v>1.6168</v>
+        <v>1.6147</v>
       </c>
       <c r="J287" t="n">
-        <v>42.0368</v>
+        <v>41.9822</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1086</v>
+        <v>1.0753</v>
       </c>
       <c r="J288" t="n">
-        <v>28.8236</v>
+        <v>27.9578</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1.17</v>
       </c>
       <c r="I289" t="n">
-        <v>0.4516</v>
+        <v>0.4546</v>
       </c>
       <c r="J289" t="n">
-        <v>11.7416</v>
+        <v>11.8196</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>1.13</v>
       </c>
       <c r="I290" t="n">
-        <v>0.3466</v>
+        <v>0.3593</v>
       </c>
       <c r="J290" t="n">
-        <v>9.0116</v>
+        <v>9.341799999999999</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>1.11</v>
       </c>
       <c r="I291" t="n">
-        <v>0.2918</v>
+        <v>0.3091</v>
       </c>
       <c r="J291" t="n">
-        <v>7.5868</v>
+        <v>8.0366</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.5</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1168</v>
+        <v>1.0825</v>
       </c>
       <c r="J292" t="n">
-        <v>24.5696</v>
+        <v>23.815</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.4</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9782</v>
+        <v>0.926</v>
       </c>
       <c r="J293" t="n">
-        <v>21.5204</v>
+        <v>20.372</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.29</v>
       </c>
       <c r="I294" t="n">
-        <v>0.7487</v>
+        <v>0.7178</v>
       </c>
       <c r="J294" t="n">
-        <v>16.4714</v>
+        <v>15.7916</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>1.22</v>
       </c>
       <c r="I295" t="n">
-        <v>0.5864</v>
+        <v>0.5734</v>
       </c>
       <c r="J295" t="n">
-        <v>12.9008</v>
+        <v>12.6148</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>1.18</v>
       </c>
       <c r="I296" t="n">
-        <v>0.4879</v>
+        <v>0.4851</v>
       </c>
       <c r="J296" t="n">
-        <v>10.7338</v>
+        <v>10.6722</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1</v>
       </c>
       <c r="I297" t="n">
-        <v>0.0935</v>
+        <v>0.0683</v>
       </c>
       <c r="J297" t="n">
-        <v>2.057</v>
+        <v>1.5026</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>0.92</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0711</v>
+        <v>-0.0922</v>
       </c>
       <c r="J298" t="n">
-        <v>-1.5642</v>
+        <v>-2.0284</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>0.68</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.319</v>
+        <v>-0.3378</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.018</v>
+        <v>-7.4316</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.54</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4499</v>
+        <v>-0.4624</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.8978</v>
+        <v>-10.1728</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.5</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4872</v>
+        <v>-0.4975</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.7184</v>
+        <v>-10.945</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.08</v>
       </c>
       <c r="I302" t="n">
-        <v>0.226</v>
+        <v>0.2277</v>
       </c>
       <c r="J302" t="n">
-        <v>6.554</v>
+        <v>6.6033</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.01</v>
       </c>
       <c r="I303" t="n">
-        <v>0.0533</v>
+        <v>0.0545</v>
       </c>
       <c r="J303" t="n">
-        <v>1.5457</v>
+        <v>1.5805</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>0.91</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1153</v>
+        <v>-0.1295</v>
       </c>
       <c r="J304" t="n">
-        <v>-3.3437</v>
+        <v>-3.7555</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.84</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1894</v>
+        <v>-0.2049</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.4926</v>
+        <v>-5.9421</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.78</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2497</v>
+        <v>-0.2649</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.2413</v>
+        <v>-7.6821</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.62</v>
       </c>
       <c r="I307" t="n">
-        <v>1.2932</v>
+        <v>1.2662</v>
       </c>
       <c r="J307" t="n">
-        <v>37.5028</v>
+        <v>36.7198</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.19</v>
       </c>
       <c r="I308" t="n">
-        <v>0.5366</v>
+        <v>0.5239</v>
       </c>
       <c r="J308" t="n">
-        <v>15.5614</v>
+        <v>15.1931</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>1.15</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4371</v>
+        <v>0.4336</v>
       </c>
       <c r="J309" t="n">
-        <v>12.6759</v>
+        <v>12.5744</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>1.14</v>
       </c>
       <c r="I310" t="n">
-        <v>0.4111</v>
+        <v>0.4099</v>
       </c>
       <c r="J310" t="n">
-        <v>11.9219</v>
+        <v>11.8871</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.9</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4035</v>
+        <v>-0.3801</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.7015</v>
+        <v>-11.0229</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.42</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0495</v>
+        <v>0.9969</v>
       </c>
       <c r="J312" t="n">
-        <v>30.4355</v>
+        <v>28.9101</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.7149</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J313" t="n">
-        <v>20.7321</v>
+        <v>19.7461</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>1.22</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6187</v>
+        <v>0.5955</v>
       </c>
       <c r="J314" t="n">
-        <v>17.9423</v>
+        <v>17.2695</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.93</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3005</v>
+        <v>-0.2877</v>
       </c>
       <c r="J315" t="n">
-        <v>-8.714499999999999</v>
+        <v>-8.343299999999999</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.91</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3609</v>
+        <v>-0.3438</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.4661</v>
+        <v>-9.9702</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.26</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5805</v>
+        <v>0.5581</v>
       </c>
       <c r="J317" t="n">
-        <v>16.8345</v>
+        <v>16.1849</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.11</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2916</v>
+        <v>0.2901</v>
       </c>
       <c r="J318" t="n">
-        <v>8.4564</v>
+        <v>8.4129</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>0.96</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0563</v>
+        <v>-0.0673</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.6327</v>
+        <v>-1.9517</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.8</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2291</v>
+        <v>-0.2447</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.6439</v>
+        <v>-7.0963</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.46</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5473</v>
+        <v>-0.5504</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.8717</v>
+        <v>-15.9616</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.67</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2986</v>
+        <v>1.2819</v>
       </c>
       <c r="J322" t="n">
-        <v>27.2706</v>
+        <v>26.9199</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.64</v>
       </c>
       <c r="I323" t="n">
-        <v>1.2636</v>
+        <v>1.2445</v>
       </c>
       <c r="J323" t="n">
-        <v>26.5356</v>
+        <v>26.1345</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.58</v>
       </c>
       <c r="I324" t="n">
-        <v>1.1931</v>
+        <v>1.1689</v>
       </c>
       <c r="J324" t="n">
-        <v>25.0551</v>
+        <v>24.5469</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>1.36</v>
       </c>
       <c r="I325" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.8377</v>
       </c>
       <c r="J325" t="n">
-        <v>18.4695</v>
+        <v>17.5917</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.99</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.1596</v>
+        <v>-0.1327</v>
       </c>
       <c r="J326" t="n">
-        <v>-3.3516</v>
+        <v>-2.7867</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.12</v>
       </c>
       <c r="I327" t="n">
-        <v>0.4197</v>
+        <v>0.3891</v>
       </c>
       <c r="J327" t="n">
-        <v>8.813700000000001</v>
+        <v>8.171099999999999</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>0.85</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1499</v>
+        <v>-0.1722</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.1479</v>
+        <v>-3.6162</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.66</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3358</v>
+        <v>-0.3543</v>
       </c>
       <c r="J329" t="n">
-        <v>-7.0518</v>
+        <v>-7.4403</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.48</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.504</v>
+        <v>-0.5135</v>
       </c>
       <c r="J330" t="n">
-        <v>-10.584</v>
+        <v>-10.7835</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.47</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5133</v>
+        <v>-0.5222</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.7793</v>
+        <v>-10.9662</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.0455</v>
+        <v>-0.066</v>
       </c>
       <c r="J332" t="n">
-        <v>-1.0465</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>0.8</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2058</v>
+        <v>-0.2268</v>
       </c>
       <c r="J333" t="n">
-        <v>-4.7334</v>
+        <v>-5.2164</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.73</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2735</v>
+        <v>-0.2933</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.2905</v>
+        <v>-6.7459</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.73</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2735</v>
+        <v>-0.2933</v>
       </c>
       <c r="J335" t="n">
-        <v>-6.2905</v>
+        <v>-6.7459</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.44</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5429</v>
+        <v>-0.5496</v>
       </c>
       <c r="J336" t="n">
-        <v>-12.4867</v>
+        <v>-12.6408</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.77</v>
       </c>
       <c r="I337" t="n">
-        <v>1.443</v>
+        <v>1.4302</v>
       </c>
       <c r="J337" t="n">
-        <v>33.189</v>
+        <v>32.8946</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.51</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1288</v>
+        <v>1.0956</v>
       </c>
       <c r="J338" t="n">
-        <v>25.9624</v>
+        <v>25.1988</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.3</v>
       </c>
       <c r="I339" t="n">
-        <v>0.7705</v>
+        <v>0.7372</v>
       </c>
       <c r="J339" t="n">
-        <v>17.7215</v>
+        <v>16.9556</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.08</v>
       </c>
       <c r="I340" t="n">
-        <v>0.2165</v>
+        <v>0.2369</v>
       </c>
       <c r="J340" t="n">
-        <v>4.9795</v>
+        <v>5.4487</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3112</v>
+        <v>-0.2878</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.1576</v>
+        <v>-6.6194</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.33</v>
       </c>
       <c r="I342" t="n">
-        <v>0.6651</v>
+        <v>0.6415</v>
       </c>
       <c r="J342" t="n">
-        <v>23.2785</v>
+        <v>22.4525</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.22</v>
       </c>
       <c r="I343" t="n">
-        <v>0.4719</v>
+        <v>0.4651</v>
       </c>
       <c r="J343" t="n">
-        <v>16.5165</v>
+        <v>16.2785</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>0.96</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0733</v>
       </c>
       <c r="J344" t="n">
-        <v>-2.247</v>
+        <v>-2.5655</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2301</v>
+        <v>-0.2434</v>
       </c>
       <c r="J345" t="n">
-        <v>-8.0535</v>
+        <v>-8.519</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.73</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3087</v>
+        <v>-0.3207</v>
       </c>
       <c r="J346" t="n">
-        <v>-10.8045</v>
+        <v>-11.2245</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.35</v>
       </c>
       <c r="I347" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.8754</v>
       </c>
       <c r="J347" t="n">
-        <v>32.83</v>
+        <v>30.639</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.16</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4783</v>
+        <v>0.4674</v>
       </c>
       <c r="J348" t="n">
-        <v>16.7405</v>
+        <v>16.359</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>1.15</v>
       </c>
       <c r="I349" t="n">
-        <v>0.4526</v>
+        <v>0.4441</v>
       </c>
       <c r="J349" t="n">
-        <v>15.841</v>
+        <v>15.5435</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>1.04</v>
       </c>
       <c r="I350" t="n">
-        <v>0.141</v>
+        <v>0.1529</v>
       </c>
       <c r="J350" t="n">
-        <v>4.935</v>
+        <v>5.3515</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.86</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4932</v>
+        <v>-0.4667</v>
       </c>
       <c r="J351" t="n">
-        <v>-17.262</v>
+        <v>-16.3345</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.26</v>
       </c>
       <c r="I352" t="n">
-        <v>0.7267</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="J352" t="n">
-        <v>24.7078</v>
+        <v>23.426</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.18</v>
       </c>
       <c r="I353" t="n">
-        <v>0.5292</v>
+        <v>0.5134</v>
       </c>
       <c r="J353" t="n">
-        <v>17.9928</v>
+        <v>17.4556</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.14</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4267</v>
+        <v>0.4204</v>
       </c>
       <c r="J354" t="n">
-        <v>14.5078</v>
+        <v>14.2936</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.12</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3744</v>
+        <v>0.3724</v>
       </c>
       <c r="J355" t="n">
-        <v>12.7296</v>
+        <v>12.6616</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.86</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.4932</v>
+        <v>-0.4667</v>
       </c>
       <c r="J356" t="n">
-        <v>-16.7688</v>
+        <v>-15.8678</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.38</v>
       </c>
       <c r="I357" t="n">
-        <v>0.7491</v>
+        <v>0.7173</v>
       </c>
       <c r="J357" t="n">
-        <v>25.4694</v>
+        <v>24.3882</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2435</v>
+        <v>0.2504</v>
       </c>
       <c r="J358" t="n">
-        <v>8.279</v>
+        <v>8.5136</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.07</v>
       </c>
       <c r="I359" t="n">
-        <v>0.181</v>
+        <v>0.1897</v>
       </c>
       <c r="J359" t="n">
-        <v>6.154</v>
+        <v>6.4498</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.8</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2404</v>
+        <v>-0.2535</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.1736</v>
+        <v>-8.619</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.71</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3281</v>
+        <v>-0.3395</v>
       </c>
       <c r="J361" t="n">
-        <v>-11.1554</v>
+        <v>-11.543</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.16</v>
       </c>
       <c r="I362" t="n">
-        <v>0.3874</v>
+        <v>0.3812</v>
       </c>
       <c r="J362" t="n">
-        <v>13.9464</v>
+        <v>13.7232</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.15</v>
       </c>
       <c r="I363" t="n">
-        <v>0.3679</v>
+        <v>0.3629</v>
       </c>
       <c r="J363" t="n">
-        <v>13.2444</v>
+        <v>13.0644</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.83</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.2003</v>
+        <v>-0.2157</v>
       </c>
       <c r="J364" t="n">
-        <v>-7.2108</v>
+        <v>-7.7652</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.78</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.2505</v>
+        <v>-0.2655</v>
       </c>
       <c r="J365" t="n">
-        <v>-9.018000000000001</v>
+        <v>-9.558</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.73</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.2992</v>
+        <v>-0.3133</v>
       </c>
       <c r="J366" t="n">
-        <v>-10.7712</v>
+        <v>-11.2788</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.45</v>
       </c>
       <c r="I367" t="n">
-        <v>1.0827</v>
+        <v>1.0381</v>
       </c>
       <c r="J367" t="n">
-        <v>38.9772</v>
+        <v>37.3716</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.31</v>
       </c>
       <c r="I368" t="n">
-        <v>0.8237</v>
+        <v>0.7781</v>
       </c>
       <c r="J368" t="n">
-        <v>29.6532</v>
+        <v>28.0116</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.24</v>
       </c>
       <c r="I369" t="n">
-        <v>0.6596</v>
+        <v>0.6333</v>
       </c>
       <c r="J369" t="n">
-        <v>23.7456</v>
+        <v>22.7988</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.95</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.2443</v>
+        <v>-0.233</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.7948</v>
+        <v>-8.388</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.93</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3078</v>
+        <v>-0.2928</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.0808</v>
+        <v>-10.5408</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.02</v>
       </c>
       <c r="I372" t="n">
-        <v>0.1949</v>
+        <v>0.1679</v>
       </c>
       <c r="J372" t="n">
-        <v>3.898</v>
+        <v>3.358</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>0.75</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.2479</v>
+        <v>-0.2697</v>
       </c>
       <c r="J373" t="n">
-        <v>-4.958</v>
+        <v>-5.394</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>0.66</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.3312</v>
+        <v>-0.3508</v>
       </c>
       <c r="J374" t="n">
-        <v>-6.624</v>
+        <v>-7.016</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.5</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.4801</v>
+        <v>-0.492</v>
       </c>
       <c r="J375" t="n">
-        <v>-9.602</v>
+        <v>-9.84</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.49</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.4895</v>
+        <v>-0.5007</v>
       </c>
       <c r="J376" t="n">
-        <v>-9.789999999999999</v>
+        <v>-10.014</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.79</v>
       </c>
       <c r="I377" t="n">
-        <v>1.451</v>
+        <v>1.4412</v>
       </c>
       <c r="J377" t="n">
-        <v>29.02</v>
+        <v>28.824</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.44</v>
       </c>
       <c r="I378" t="n">
-        <v>1.0309</v>
+        <v>0.9856</v>
       </c>
       <c r="J378" t="n">
-        <v>20.618</v>
+        <v>19.712</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.41</v>
       </c>
       <c r="I379" t="n">
-        <v>0.9849</v>
+        <v>0.9352</v>
       </c>
       <c r="J379" t="n">
-        <v>19.698</v>
+        <v>18.704</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>1.16</v>
       </c>
       <c r="I380" t="n">
-        <v>0.4223</v>
+        <v>0.4289</v>
       </c>
       <c r="J380" t="n">
-        <v>8.446</v>
+        <v>8.577999999999999</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>1.12</v>
       </c>
       <c r="I381" t="n">
-        <v>0.3159</v>
+        <v>0.332</v>
       </c>
       <c r="J381" t="n">
-        <v>6.318</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.67</v>
       </c>
       <c r="I382" t="n">
-        <v>1.3461</v>
+        <v>1.3238</v>
       </c>
       <c r="J382" t="n">
-        <v>36.3447</v>
+        <v>35.7426</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.26</v>
       </c>
       <c r="I383" t="n">
-        <v>0.694</v>
+        <v>0.6665</v>
       </c>
       <c r="J383" t="n">
-        <v>18.738</v>
+        <v>17.9955</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.22</v>
       </c>
       <c r="I384" t="n">
-        <v>0.6028</v>
+        <v>0.5847</v>
       </c>
       <c r="J384" t="n">
-        <v>16.2756</v>
+        <v>15.7869</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.11</v>
       </c>
       <c r="I385" t="n">
-        <v>0.323</v>
+        <v>0.3308</v>
       </c>
       <c r="J385" t="n">
-        <v>8.721</v>
+        <v>8.9316</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.9</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4113</v>
+        <v>-0.3856</v>
       </c>
       <c r="J386" t="n">
-        <v>-11.1051</v>
+        <v>-10.4112</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.22</v>
       </c>
       <c r="I387" t="n">
-        <v>0.511</v>
+        <v>0.4938</v>
       </c>
       <c r="J387" t="n">
-        <v>13.797</v>
+        <v>13.3326</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1</v>
       </c>
       <c r="I388" t="n">
-        <v>0.0185</v>
+        <v>0.0133</v>
       </c>
       <c r="J388" t="n">
-        <v>0.4995</v>
+        <v>0.3591</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.93</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.0919</v>
+        <v>-0.1054</v>
       </c>
       <c r="J389" t="n">
-        <v>-2.4813</v>
+        <v>-2.8458</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.9</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.1248</v>
+        <v>-0.1397</v>
       </c>
       <c r="J390" t="n">
-        <v>-3.3696</v>
+        <v>-3.7719</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.49</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.5193</v>
+        <v>-0.5243</v>
       </c>
       <c r="J391" t="n">
-        <v>-14.0211</v>
+        <v>-14.1561</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>0.63</v>
       </c>
       <c r="I392" t="n">
-        <v>-0.3326</v>
+        <v>-0.3571</v>
       </c>
       <c r="J392" t="n">
-        <v>-6.3194</v>
+        <v>-6.7849</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>0.61</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.3526</v>
+        <v>-0.376</v>
       </c>
       <c r="J393" t="n">
-        <v>-6.6994</v>
+        <v>-7.144</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>0.57</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.3911</v>
+        <v>-0.4122</v>
       </c>
       <c r="J394" t="n">
-        <v>-7.4309</v>
+        <v>-7.8318</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.51</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.4439</v>
+        <v>-0.4623</v>
       </c>
       <c r="J395" t="n">
-        <v>-8.434100000000001</v>
+        <v>-8.7837</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.38</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.5676</v>
+        <v>-0.5768</v>
       </c>
       <c r="J396" t="n">
-        <v>-10.7844</v>
+        <v>-10.9592</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>2.06</v>
       </c>
       <c r="I397" t="n">
-        <v>1.7261</v>
+        <v>1.7346</v>
       </c>
       <c r="J397" t="n">
-        <v>32.7959</v>
+        <v>32.9574</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.6</v>
       </c>
       <c r="I398" t="n">
-        <v>1.208</v>
+        <v>1.1867</v>
       </c>
       <c r="J398" t="n">
-        <v>22.952</v>
+        <v>22.5473</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.53</v>
       </c>
       <c r="I399" t="n">
-        <v>1.1274</v>
+        <v>1.0995</v>
       </c>
       <c r="J399" t="n">
-        <v>21.4206</v>
+        <v>20.8905</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>1.27</v>
       </c>
       <c r="I400" t="n">
-        <v>0.6643</v>
+        <v>0.6506</v>
       </c>
       <c r="J400" t="n">
-        <v>12.6217</v>
+        <v>12.3614</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>1.11</v>
       </c>
       <c r="I401" t="n">
-        <v>0.2613</v>
+        <v>0.2877</v>
       </c>
       <c r="J401" t="n">
-        <v>4.9647</v>
+        <v>5.4663</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.55</v>
       </c>
       <c r="I402" t="n">
-        <v>1.201</v>
+        <v>1.1688</v>
       </c>
       <c r="J402" t="n">
-        <v>30.025</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.28</v>
       </c>
       <c r="I403" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7096</v>
       </c>
       <c r="J403" t="n">
-        <v>18.585</v>
+        <v>17.74</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.17</v>
       </c>
       <c r="I404" t="n">
-        <v>0.4846</v>
+        <v>0.4775</v>
       </c>
       <c r="J404" t="n">
-        <v>12.115</v>
+        <v>11.9375</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>1.13</v>
       </c>
       <c r="I405" t="n">
-        <v>0.3811</v>
+        <v>0.3833</v>
       </c>
       <c r="J405" t="n">
-        <v>9.5275</v>
+        <v>9.5825</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.95</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.2545</v>
+        <v>-0.2401</v>
       </c>
       <c r="J406" t="n">
-        <v>-6.3625</v>
+        <v>-6.0025</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.22</v>
       </c>
       <c r="I407" t="n">
-        <v>0.5023</v>
+        <v>0.4874</v>
       </c>
       <c r="J407" t="n">
-        <v>12.5575</v>
+        <v>12.185</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.05</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1572</v>
+        <v>0.1608</v>
       </c>
       <c r="J408" t="n">
-        <v>3.93</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.01</v>
       </c>
       <c r="I409" t="n">
-        <v>0.0523</v>
+        <v>0.0538</v>
       </c>
       <c r="J409" t="n">
-        <v>1.3075</v>
+        <v>1.345</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.79</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2403</v>
+        <v>-0.2555</v>
       </c>
       <c r="J410" t="n">
-        <v>-6.0075</v>
+        <v>-6.3875</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.57</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.4489</v>
+        <v>-0.4572</v>
       </c>
       <c r="J411" t="n">
-        <v>-11.2225</v>
+        <v>-11.43</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.8</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4599</v>
+        <v>1.4511</v>
       </c>
       <c r="J412" t="n">
-        <v>30.6579</v>
+        <v>30.4731</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.77</v>
       </c>
       <c r="I413" t="n">
-        <v>1.425</v>
+        <v>1.4143</v>
       </c>
       <c r="J413" t="n">
-        <v>29.925</v>
+        <v>29.7003</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>1.28</v>
       </c>
       <c r="I414" t="n">
-        <v>0.7113</v>
+        <v>0.6877</v>
       </c>
       <c r="J414" t="n">
-        <v>14.9373</v>
+        <v>14.4417</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>1.21</v>
       </c>
       <c r="I415" t="n">
-        <v>0.5455</v>
+        <v>0.5402</v>
       </c>
       <c r="J415" t="n">
-        <v>11.4555</v>
+        <v>11.3442</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.92</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.3888</v>
+        <v>-0.3568</v>
       </c>
       <c r="J416" t="n">
-        <v>-8.1648</v>
+        <v>-7.4928</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.12</v>
       </c>
       <c r="I417" t="n">
-        <v>0.4025</v>
+        <v>0.3763</v>
       </c>
       <c r="J417" t="n">
-        <v>8.452500000000001</v>
+        <v>7.9023</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>0.88</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.1218</v>
+        <v>-0.1428</v>
       </c>
       <c r="J418" t="n">
-        <v>-2.5578</v>
+        <v>-2.9988</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>0.66</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.3395</v>
+        <v>-0.3571</v>
       </c>
       <c r="J419" t="n">
-        <v>-7.1295</v>
+        <v>-7.4991</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.65</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.3488</v>
+        <v>-0.3661</v>
       </c>
       <c r="J420" t="n">
-        <v>-7.3248</v>
+        <v>-7.6881</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.39</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.5908</v>
+        <v>-0.5939</v>
       </c>
       <c r="J421" t="n">
-        <v>-12.4068</v>
+        <v>-12.4719</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.64</v>
       </c>
       <c r="I422" t="n">
-        <v>1.2841</v>
+        <v>1.2626</v>
       </c>
       <c r="J422" t="n">
-        <v>32.1025</v>
+        <v>31.565</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.44</v>
       </c>
       <c r="I423" t="n">
-        <v>1.0378</v>
+        <v>0.992</v>
       </c>
       <c r="J423" t="n">
-        <v>25.945</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.36</v>
       </c>
       <c r="I424" t="n">
-        <v>0.8963</v>
+        <v>0.8492</v>
       </c>
       <c r="J424" t="n">
-        <v>22.4075</v>
+        <v>21.23</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.31</v>
       </c>
       <c r="I425" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="J425" t="n">
-        <v>19.75</v>
+        <v>18.875</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.93</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.3458</v>
+        <v>-0.3195</v>
       </c>
       <c r="J426" t="n">
-        <v>-8.645</v>
+        <v>-7.9875</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.08</v>
       </c>
       <c r="I427" t="n">
-        <v>0.2816</v>
+        <v>0.2685</v>
       </c>
       <c r="J427" t="n">
-        <v>7.04</v>
+        <v>6.7125</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>0.89</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.1212</v>
+        <v>-0.1397</v>
       </c>
       <c r="J428" t="n">
-        <v>-3.03</v>
+        <v>-3.4925</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.72</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.2904</v>
+        <v>-0.3082</v>
       </c>
       <c r="J429" t="n">
-        <v>-7.26</v>
+        <v>-7.705</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.67</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.3378</v>
+        <v>-0.3541</v>
       </c>
       <c r="J430" t="n">
-        <v>-8.445</v>
+        <v>-8.852499999999999</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.6</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.4036</v>
+        <v>-0.417</v>
       </c>
       <c r="J431" t="n">
-        <v>-10.09</v>
+        <v>-10.425</v>
       </c>
     </row>
     <row r="432">
@@ -20549,10 +20549,10 @@
         <v>0.77</v>
       </c>
       <c r="I432" t="n">
-        <v>-0.1998</v>
+        <v>-0.2282</v>
       </c>
       <c r="J432" t="n">
-        <v>-3.996</v>
+        <v>-4.564</v>
       </c>
     </row>
     <row r="433">
@@ -20589,10 +20589,10 @@
         <v>0.75</v>
       </c>
       <c r="I433" t="n">
-        <v>-0.2218</v>
+        <v>-0.2493</v>
       </c>
       <c r="J433" t="n">
-        <v>-4.436</v>
+        <v>-4.986</v>
       </c>
     </row>
     <row r="434">
@@ -20629,10 +20629,10 @@
         <v>0.64</v>
       </c>
       <c r="I434" t="n">
-        <v>-0.3348</v>
+        <v>-0.3572</v>
       </c>
       <c r="J434" t="n">
-        <v>-6.696</v>
+        <v>-7.144</v>
       </c>
     </row>
     <row r="435">
@@ -20669,10 +20669,10 @@
         <v>0.42</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.5382</v>
+        <v>-0.5485</v>
       </c>
       <c r="J435" t="n">
-        <v>-10.764</v>
+        <v>-10.97</v>
       </c>
     </row>
     <row r="436">
@@ -20709,10 +20709,10 @@
         <v>0.35</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.6055</v>
+        <v>-0.6105</v>
       </c>
       <c r="J436" t="n">
-        <v>-12.11</v>
+        <v>-12.21</v>
       </c>
     </row>
     <row r="437">
@@ -20749,10 +20749,10 @@
         <v>1.69</v>
       </c>
       <c r="I437" t="n">
-        <v>1.316</v>
+        <v>1.3015</v>
       </c>
       <c r="J437" t="n">
-        <v>26.32</v>
+        <v>26.03</v>
       </c>
     </row>
     <row r="438">
@@ -20789,10 +20789,10 @@
         <v>1.64</v>
       </c>
       <c r="I438" t="n">
-        <v>1.2582</v>
+        <v>1.2398</v>
       </c>
       <c r="J438" t="n">
-        <v>25.164</v>
+        <v>24.796</v>
       </c>
     </row>
     <row r="439">
@@ -20829,10 +20829,10 @@
         <v>1.5</v>
       </c>
       <c r="I439" t="n">
-        <v>1.0951</v>
+        <v>1.0633</v>
       </c>
       <c r="J439" t="n">
-        <v>21.902</v>
+        <v>21.266</v>
       </c>
     </row>
     <row r="440">
@@ -20869,10 +20869,10 @@
         <v>1.32</v>
       </c>
       <c r="I440" t="n">
-        <v>0.7844</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="J440" t="n">
-        <v>15.688</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="441">
@@ -20909,10 +20909,10 @@
         <v>1.27</v>
       </c>
       <c r="I441" t="n">
-        <v>0.6703</v>
+        <v>0.6548</v>
       </c>
       <c r="J441" t="n">
-        <v>13.406</v>
+        <v>13.096</v>
       </c>
     </row>
     <row r="442">
@@ -20949,10 +20949,10 @@
         <v>1.21</v>
       </c>
       <c r="I442" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.5869</v>
       </c>
       <c r="J442" t="n">
-        <v>18.402</v>
+        <v>17.607</v>
       </c>
     </row>
     <row r="443">
@@ -20989,10 +20989,10 @@
         <v>1.15</v>
       </c>
       <c r="I443" t="n">
-        <v>0.4597</v>
+        <v>0.4489</v>
       </c>
       <c r="J443" t="n">
-        <v>13.791</v>
+        <v>13.467</v>
       </c>
     </row>
     <row r="444">
@@ -21029,10 +21029,10 @@
         <v>1.12</v>
       </c>
       <c r="I444" t="n">
-        <v>0.38</v>
+        <v>0.3762</v>
       </c>
       <c r="J444" t="n">
-        <v>11.4</v>
+        <v>11.286</v>
       </c>
     </row>
     <row r="445">
@@ -21069,10 +21069,10 @@
         <v>1.11</v>
       </c>
       <c r="I445" t="n">
-        <v>0.3529</v>
+        <v>0.3512</v>
       </c>
       <c r="J445" t="n">
-        <v>10.587</v>
+        <v>10.536</v>
       </c>
     </row>
     <row r="446">
@@ -21109,10 +21109,10 @@
         <v>0.83</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.5666</v>
+        <v>-0.5342</v>
       </c>
       <c r="J446" t="n">
-        <v>-16.998</v>
+        <v>-16.026</v>
       </c>
     </row>
     <row r="447">
@@ -21149,10 +21149,10 @@
         <v>1.22</v>
       </c>
       <c r="I447" t="n">
-        <v>0.4739</v>
+        <v>0.4665</v>
       </c>
       <c r="J447" t="n">
-        <v>14.217</v>
+        <v>13.995</v>
       </c>
     </row>
     <row r="448">
@@ -21189,10 +21189,10 @@
         <v>1.09</v>
       </c>
       <c r="I448" t="n">
-        <v>0.2249</v>
+        <v>0.232</v>
       </c>
       <c r="J448" t="n">
-        <v>6.747</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="449">
@@ -21229,10 +21229,10 @@
         <v>0.98</v>
       </c>
       <c r="I449" t="n">
-        <v>-0.0363</v>
+        <v>-0.043</v>
       </c>
       <c r="J449" t="n">
-        <v>-1.089</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="450">
@@ -21269,10 +21269,10 @@
         <v>0.88</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.1566</v>
+        <v>-0.1697</v>
       </c>
       <c r="J450" t="n">
-        <v>-4.698</v>
+        <v>-5.091</v>
       </c>
     </row>
     <row r="451">
@@ -21309,10 +21309,10 @@
         <v>0.85</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.1884</v>
+        <v>-0.2018</v>
       </c>
       <c r="J451" t="n">
-        <v>-5.652</v>
+        <v>-6.054</v>
       </c>
     </row>
     <row r="452">
@@ -21349,10 +21349,10 @@
         <v>1.96</v>
       </c>
       <c r="I452" t="n">
-        <v>1.654</v>
+        <v>1.6532</v>
       </c>
       <c r="J452" t="n">
-        <v>38.042</v>
+        <v>38.0236</v>
       </c>
     </row>
     <row r="453">
@@ -21389,10 +21389,10 @@
         <v>1.49</v>
       </c>
       <c r="I453" t="n">
-        <v>1.0979</v>
+        <v>1.0631</v>
       </c>
       <c r="J453" t="n">
-        <v>25.2517</v>
+        <v>24.4513</v>
       </c>
     </row>
     <row r="454">
@@ -21429,10 +21429,10 @@
         <v>1.18</v>
       </c>
       <c r="I454" t="n">
-        <v>0.4791</v>
+        <v>0.479</v>
       </c>
       <c r="J454" t="n">
-        <v>11.0193</v>
+        <v>11.017</v>
       </c>
     </row>
     <row r="455">
@@ -21469,10 +21469,10 @@
         <v>1.08</v>
       </c>
       <c r="I455" t="n">
-        <v>0.2079</v>
+        <v>0.2309</v>
       </c>
       <c r="J455" t="n">
-        <v>4.7817</v>
+        <v>5.3107</v>
       </c>
     </row>
     <row r="456">
@@ -21509,10 +21509,10 @@
         <v>1.08</v>
       </c>
       <c r="I456" t="n">
-        <v>0.2079</v>
+        <v>0.2309</v>
       </c>
       <c r="J456" t="n">
-        <v>4.7817</v>
+        <v>5.3107</v>
       </c>
     </row>
     <row r="457">
@@ -21549,10 +21549,10 @@
         <v>1.14</v>
       </c>
       <c r="I457" t="n">
-        <v>0.4067</v>
+        <v>0.3875</v>
       </c>
       <c r="J457" t="n">
-        <v>9.354100000000001</v>
+        <v>8.9125</v>
       </c>
     </row>
     <row r="458">
@@ -21589,10 +21589,10 @@
         <v>0.86</v>
       </c>
       <c r="I458" t="n">
-        <v>-0.1558</v>
+        <v>-0.1743</v>
       </c>
       <c r="J458" t="n">
-        <v>-3.5834</v>
+        <v>-4.0089</v>
       </c>
     </row>
     <row r="459">
@@ -21629,10 +21629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I459" t="n">
-        <v>-0.2064</v>
+        <v>-0.225</v>
       </c>
       <c r="J459" t="n">
-        <v>-4.7472</v>
+        <v>-5.175</v>
       </c>
     </row>
     <row r="460">
@@ -21669,10 +21669,10 @@
         <v>0.7</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.3108</v>
+        <v>-0.3278</v>
       </c>
       <c r="J460" t="n">
-        <v>-7.1484</v>
+        <v>-7.5394</v>
       </c>
     </row>
     <row r="461">
@@ -21709,10 +21709,10 @@
         <v>0.5</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.4977</v>
+        <v>-0.5058</v>
       </c>
       <c r="J461" t="n">
-        <v>-11.4471</v>
+        <v>-11.6334</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2557/event_2557_evp_summary.xlsx
+++ b/database/event/2557/event_2557_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.3737</v>
+        <v>6.4727</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2025</v>
+        <v>2.2367</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2772</v>
+        <v>2.3428</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3737</v>
+        <v>6.4727</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6979</v>
+        <v>2.7452</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6758</v>
+        <v>3.7275</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0071</v>
+        <v>3.864</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1638</v>
+        <v>2.1695</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6758</v>
+        <v>3.7275</v>
       </c>
       <c r="K2" t="n">
         <v>125</v>
@@ -529,7 +529,7 @@
         <v>155</v>
       </c>
       <c r="M2" t="n">
-        <v>5.839600000000001</v>
+        <v>5.897</v>
       </c>
       <c r="N2" t="n">
         <v>280</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7124</v>
+        <v>5.5881</v>
       </c>
       <c r="C3" t="n">
-        <v>1.974</v>
+        <v>1.931</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9762</v>
+        <v>1.9399</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7124</v>
+        <v>5.5881</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5397</v>
+        <v>2.4504</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1727</v>
+        <v>3.1377</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5397</v>
+        <v>2.7572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8314</v>
+        <v>1.5481</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1727</v>
+        <v>3.1377</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0041</v>
+        <v>4.6858</v>
       </c>
       <c r="N3" t="n">
         <v>280</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4724</v>
+        <v>5.5295</v>
       </c>
       <c r="C4" t="n">
-        <v>1.891</v>
+        <v>1.9108</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8669</v>
+        <v>1.9132</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4724</v>
+        <v>5.5295</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3754</v>
+        <v>1.391</v>
       </c>
       <c r="G4" t="n">
-        <v>3.097</v>
+        <v>4.1385</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9432</v>
+        <v>1.391</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5893</v>
+        <v>0.781</v>
       </c>
       <c r="J4" t="n">
-        <v>3.097</v>
+        <v>4.1385</v>
       </c>
       <c r="K4" t="n">
         <v>125</v>
@@ -621,7 +621,7 @@
         <v>155</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6863</v>
+        <v>4.919499999999999</v>
       </c>
       <c r="N4" t="n">
         <v>280</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4195</v>
+        <v>5.253</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8728</v>
+        <v>1.8152</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8429</v>
+        <v>1.7872</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4195</v>
+        <v>5.253</v>
       </c>
       <c r="F5" t="n">
-        <v>3.943</v>
+        <v>3.3668</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4765</v>
+        <v>1.8862</v>
       </c>
       <c r="H5" t="n">
-        <v>8.1153</v>
+        <v>4.7656</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3822</v>
+        <v>4.8929</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4765</v>
+        <v>1.8862</v>
       </c>
       <c r="K5" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="L5" t="n">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8587</v>
+        <v>6.7791</v>
       </c>
       <c r="N5" t="n">
-        <v>300</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3034</v>
+        <v>5.2004</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8326</v>
+        <v>1.7971</v>
       </c>
       <c r="D6" t="n">
-        <v>1.79</v>
+        <v>1.7632</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3034</v>
+        <v>5.2004</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3527</v>
+        <v>3.76</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9507</v>
+        <v>1.4404</v>
       </c>
       <c r="H6" t="n">
-        <v>4.613</v>
+        <v>7.6742</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7319</v>
+        <v>4.3088</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9507</v>
+        <v>1.4404</v>
       </c>
       <c r="K6" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="L6" t="n">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="M6" t="n">
-        <v>6.682600000000001</v>
+        <v>5.7492</v>
       </c>
       <c r="N6" t="n">
-        <v>216</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8775</v>
+        <v>4.8569</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6855</v>
+        <v>1.6784</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5961</v>
+        <v>1.6068</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8775</v>
+        <v>4.8569</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1919</v>
+        <v>2.1991</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6856</v>
+        <v>2.6578</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1919</v>
+        <v>2.1991</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1919</v>
+        <v>2.1991</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6856</v>
+        <v>2.6578</v>
       </c>
       <c r="K7" t="n">
         <v>124</v>
@@ -759,7 +759,7 @@
         <v>133</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8775</v>
+        <v>4.8569</v>
       </c>
       <c r="N7" t="n">
         <v>257</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.8731</v>
+        <v>4.7662</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6839</v>
+        <v>1.647</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5941</v>
+        <v>1.5654</v>
       </c>
       <c r="E8" t="n">
-        <v>4.8731</v>
+        <v>4.7662</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1533</v>
+        <v>3.1081</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7198</v>
+        <v>1.6581</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1767</v>
+        <v>4.1726</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2843</v>
+        <v>4.2842</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7198</v>
+        <v>1.6581</v>
       </c>
       <c r="K8" t="n">
         <v>113</v>
@@ -805,7 +805,7 @@
         <v>103</v>
       </c>
       <c r="M8" t="n">
-        <v>6.0041</v>
+        <v>5.9423</v>
       </c>
       <c r="N8" t="n">
         <v>216</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3816</v>
+        <v>4.3241</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5141</v>
+        <v>1.4942</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3704</v>
+        <v>1.364</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3816</v>
+        <v>4.3241</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9612</v>
+        <v>2.9535</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4204</v>
+        <v>1.3706</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7561</v>
+        <v>3.8184</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8529</v>
+        <v>3.9204</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4204</v>
+        <v>1.3706</v>
       </c>
       <c r="K9" t="n">
         <v>113</v>
@@ -851,7 +851,7 @@
         <v>103</v>
       </c>
       <c r="M9" t="n">
-        <v>5.2733</v>
+        <v>5.291</v>
       </c>
       <c r="N9" t="n">
         <v>216</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9225</v>
+        <v>3.8296</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3555</v>
+        <v>1.3234</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1614</v>
+        <v>1.1388</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9225</v>
+        <v>3.8296</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3028</v>
+        <v>2.2688</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6197</v>
+        <v>1.5608</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3152</v>
+        <v>2.2688</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3152</v>
+        <v>2.2688</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6197</v>
+        <v>1.5608</v>
       </c>
       <c r="K10" t="n">
         <v>124</v>
@@ -897,7 +897,7 @@
         <v>133</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9349</v>
+        <v>3.8296</v>
       </c>
       <c r="N10" t="n">
         <v>257</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8003</v>
+        <v>3.7767</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3132</v>
+        <v>1.3051</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1058</v>
+        <v>1.1147</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8003</v>
+        <v>3.7767</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6028</v>
+        <v>2.5695</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1975</v>
+        <v>1.2072</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9718</v>
+        <v>2.9385</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0484</v>
+        <v>3.017</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1975</v>
+        <v>1.2072</v>
       </c>
       <c r="K11" t="n">
         <v>113</v>
@@ -943,7 +943,7 @@
         <v>103</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2459</v>
+        <v>4.2242</v>
       </c>
       <c r="N11" t="n">
         <v>216</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5211</v>
+        <v>3.3994</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2168</v>
+        <v>1.1747</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9787</v>
+        <v>0.9428</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5211</v>
+        <v>3.3994</v>
       </c>
       <c r="F12" t="n">
-        <v>4.0005</v>
+        <v>3.8625</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4794</v>
+        <v>-0.4631</v>
       </c>
       <c r="H12" t="n">
-        <v>6.0308</v>
+        <v>5.9017</v>
       </c>
       <c r="I12" t="n">
-        <v>6.3456</v>
+        <v>6.2213</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4794</v>
+        <v>-0.4631</v>
       </c>
       <c r="K12" t="n">
         <v>140</v>
@@ -989,7 +989,7 @@
         <v>76</v>
       </c>
       <c r="M12" t="n">
-        <v>5.8662</v>
+        <v>5.7582</v>
       </c>
       <c r="N12" t="n">
         <v>216</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.4654</v>
+        <v>3.3662</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1975</v>
+        <v>1.1632</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9533</v>
+        <v>0.9277</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4654</v>
+        <v>3.3662</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3011</v>
+        <v>3.3214</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1643</v>
+        <v>0.0448</v>
       </c>
       <c r="H13" t="n">
-        <v>5.9975</v>
+        <v>4.6616</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2386</v>
+        <v>4.914</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1643</v>
+        <v>0.0448</v>
       </c>
       <c r="K13" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L13" t="n">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4029</v>
+        <v>4.9588</v>
       </c>
       <c r="N13" t="n">
-        <v>300</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.4474</v>
+        <v>3.2996</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1913</v>
+        <v>1.1402</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8973</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4474</v>
+        <v>3.2996</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3668</v>
+        <v>3.1879</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0806</v>
+        <v>0.1117</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6439</v>
+        <v>5.5262</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8863</v>
+        <v>3.1028</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0806</v>
+        <v>0.1117</v>
       </c>
       <c r="K14" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L14" t="n">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="M14" t="n">
-        <v>4.966900000000001</v>
+        <v>3.2145</v>
       </c>
       <c r="N14" t="n">
-        <v>216</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9908</v>
+        <v>2.9201</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0335</v>
+        <v>1.0091</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7373</v>
+        <v>0.7245</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9908</v>
+        <v>2.9201</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7952</v>
+        <v>0.8092</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1956</v>
+        <v>2.1109</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7952</v>
+        <v>0.8092</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7952</v>
+        <v>0.8092</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1956</v>
+        <v>2.1109</v>
       </c>
       <c r="K15" t="n">
         <v>124</v>
@@ -1127,7 +1127,7 @@
         <v>133</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9908</v>
+        <v>2.9201</v>
       </c>
       <c r="N15" t="n">
         <v>257</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8131</v>
+        <v>2.7347</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9721</v>
+        <v>0.945</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6564</v>
+        <v>0.64</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8131</v>
+        <v>2.7347</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8131</v>
+        <v>2.7347</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4321</v>
+        <v>3.3169</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4321</v>
+        <v>3.3169</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4321</v>
+        <v>3.3169</v>
       </c>
       <c r="N16" t="n">
         <v>128</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.7334</v>
+        <v>2.6209</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9446</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6201</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7334</v>
+        <v>2.6209</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4016</v>
+        <v>2.3507</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3318</v>
+        <v>0.2702</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5314</v>
+        <v>2.437</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5966</v>
+        <v>2.5021</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3318</v>
+        <v>0.2702</v>
       </c>
       <c r="K17" t="n">
         <v>152</v>
@@ -1219,7 +1219,7 @@
         <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9284</v>
+        <v>2.7723</v>
       </c>
       <c r="N17" t="n">
         <v>199</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4762</v>
+        <v>2.5601</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8557</v>
+        <v>0.8847</v>
       </c>
       <c r="D18" t="n">
-        <v>0.503</v>
+        <v>0.5605</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4762</v>
+        <v>2.5601</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4762</v>
+        <v>-0.1234</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2.6835</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6947</v>
+        <v>-0.1234</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6947</v>
+        <v>-0.0693</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.6835</v>
       </c>
       <c r="K18" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6947</v>
+        <v>2.6142</v>
       </c>
       <c r="N18" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4252</v>
+        <v>2.4769</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8381</v>
+        <v>0.8559</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4798</v>
+        <v>0.5226</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4252</v>
+        <v>2.4769</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3394</v>
+        <v>2.4769</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7646</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3394</v>
+        <v>2.7262</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1833</v>
+        <v>2.7262</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7646</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L19" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.5813</v>
+        <v>2.7262</v>
       </c>
       <c r="N19" t="n">
-        <v>280</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1179</v>
+        <v>2.0983</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7319</v>
+        <v>0.7251</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3399</v>
+        <v>0.3501</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1179</v>
+        <v>2.0983</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9615</v>
+        <v>2.0983</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1564</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9615</v>
+        <v>2.0983</v>
       </c>
       <c r="I20" t="n">
-        <v>2.012</v>
+        <v>2.0983</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1564</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L20" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1684</v>
+        <v>2.0983</v>
       </c>
       <c r="N20" t="n">
-        <v>199</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9988</v>
+        <v>1.9008</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6907</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2857</v>
+        <v>0.2601</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9988</v>
+        <v>1.9008</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9988</v>
+        <v>1.7746</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.1262</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9988</v>
+        <v>1.7746</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9988</v>
+        <v>1.822</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.1262</v>
       </c>
       <c r="K21" t="n">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9988</v>
+        <v>1.9482</v>
       </c>
       <c r="N21" t="n">
-        <v>114</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8711</v>
+        <v>1.7634</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6466</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2276</v>
+        <v>0.1975</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8711</v>
+        <v>1.7634</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8711</v>
+        <v>1.7634</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8711</v>
+        <v>1.7634</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8711</v>
+        <v>1.7634</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8711</v>
+        <v>1.7634</v>
       </c>
       <c r="N22" t="n">
         <v>138</v>
@@ -1458,81 +1458,81 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7024</v>
+        <v>1.6988</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5883</v>
+        <v>0.587</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1508</v>
+        <v>0.1681</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7024</v>
+        <v>1.6988</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2393</v>
+        <v>1.6988</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5369</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2393</v>
+        <v>1.6988</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3562</v>
+        <v>1.6988</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5369</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L23" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8193</v>
+        <v>1.6988</v>
       </c>
       <c r="N23" t="n">
-        <v>216</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6821</v>
+        <v>1.6981</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5813</v>
+        <v>0.5868</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1415</v>
+        <v>0.1678</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6821</v>
+        <v>1.6981</v>
       </c>
       <c r="F24" t="n">
-        <v>2.6821</v>
+        <v>2.2301</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>-0.532</v>
       </c>
       <c r="H24" t="n">
-        <v>3.1454</v>
+        <v>2.2301</v>
       </c>
       <c r="I24" t="n">
-        <v>3.3096</v>
+        <v>2.3509</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>-0.532</v>
       </c>
       <c r="K24" t="n">
         <v>140</v>
@@ -1541,7 +1541,7 @@
         <v>76</v>
       </c>
       <c r="M24" t="n">
-        <v>2.3096</v>
+        <v>1.8189</v>
       </c>
       <c r="N24" t="n">
         <v>216</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6721</v>
+        <v>1.6584</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5778</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.137</v>
+        <v>0.1497</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6721</v>
+        <v>1.6584</v>
       </c>
       <c r="F25" t="n">
-        <v>1.712</v>
+        <v>1.7325</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0399</v>
+        <v>-0.0741</v>
       </c>
       <c r="H25" t="n">
-        <v>1.712</v>
+        <v>1.7325</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8014</v>
+        <v>1.8263</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0399</v>
+        <v>-0.0741</v>
       </c>
       <c r="K25" t="n">
         <v>140</v>
@@ -1587,7 +1587,7 @@
         <v>76</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7615</v>
+        <v>1.7522</v>
       </c>
       <c r="N25" t="n">
         <v>216</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6517</v>
+        <v>1.6234</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5708</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1277</v>
+        <v>0.1337</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6517</v>
+        <v>1.6234</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6517</v>
+        <v>2.6234</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6517</v>
+        <v>3.0619</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6517</v>
+        <v>3.2277</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K26" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6517</v>
+        <v>2.2277</v>
       </c>
       <c r="N26" t="n">
-        <v>138</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6339</v>
+        <v>1.6183</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5646</v>
+        <v>0.5592</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1196</v>
+        <v>0.1314</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6339</v>
+        <v>1.6183</v>
       </c>
       <c r="F27" t="n">
-        <v>2.184</v>
+        <v>2.1504</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5501</v>
+        <v>-0.5321</v>
       </c>
       <c r="H27" t="n">
-        <v>2.3117</v>
+        <v>2.1504</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2483</v>
+        <v>1.2074</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5501</v>
+        <v>-0.5321</v>
       </c>
       <c r="K27" t="n">
         <v>144</v>
@@ -1679,7 +1679,7 @@
         <v>156</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6981999999999999</v>
+        <v>0.6753</v>
       </c>
       <c r="N27" t="n">
         <v>300</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6309</v>
+        <v>1.6033</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5636</v>
+        <v>0.554</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1182</v>
+        <v>0.1246</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6309</v>
+        <v>1.6033</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6309</v>
+        <v>1.6033</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6309</v>
+        <v>1.6033</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6309</v>
+        <v>1.6033</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6309</v>
+        <v>1.6033</v>
       </c>
       <c r="N28" t="n">
         <v>128</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.6076</v>
+        <v>1.5974</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5555</v>
+        <v>0.552</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1076</v>
+        <v>0.1219</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6076</v>
+        <v>1.5974</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6076</v>
+        <v>1.5974</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6076</v>
+        <v>1.5974</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6076</v>
+        <v>1.5974</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.6076</v>
+        <v>1.5974</v>
       </c>
       <c r="N29" t="n">
         <v>138</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4597</v>
+        <v>1.3635</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5044</v>
+        <v>0.4712</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0403</v>
+        <v>0.0154</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4597</v>
+        <v>1.3635</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9296</v>
+        <v>0.8751</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5301</v>
+        <v>0.4884</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9296</v>
+        <v>0.8751</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9296</v>
+        <v>0.8751</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5301</v>
+        <v>0.4884</v>
       </c>
       <c r="K30" t="n">
         <v>124</v>
@@ -1817,7 +1817,7 @@
         <v>133</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4597</v>
+        <v>1.3635</v>
       </c>
       <c r="N30" t="n">
         <v>257</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4012</v>
+        <v>1.3232</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4842</v>
+        <v>0.4572</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0137</v>
+        <v>-0.003</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4012</v>
+        <v>1.3232</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4012</v>
+        <v>1.3232</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4012</v>
+        <v>1.3232</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4012</v>
+        <v>1.3232</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4012</v>
+        <v>1.3232</v>
       </c>
       <c r="N31" t="n">
         <v>138</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2608</v>
+        <v>1.1765</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4357</v>
+        <v>0.4066</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0503</v>
+        <v>-0.0698</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2608</v>
+        <v>1.1765</v>
       </c>
       <c r="F32" t="n">
-        <v>1.2608</v>
+        <v>1.1765</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2608</v>
+        <v>1.1765</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2608</v>
+        <v>1.1765</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2608</v>
+        <v>1.1765</v>
       </c>
       <c r="N32" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1178</v>
+        <v>1.1025</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3863</v>
+        <v>0.381</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1154</v>
+        <v>-0.1035</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1178</v>
+        <v>1.1025</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1178</v>
+        <v>1.1025</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1178</v>
+        <v>1.1025</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1178</v>
+        <v>1.1025</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1178</v>
+        <v>1.1025</v>
       </c>
       <c r="N33" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0728</v>
+        <v>1.1018</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3707</v>
+        <v>0.3807</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1358</v>
+        <v>-0.1039</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0728</v>
+        <v>1.1018</v>
       </c>
       <c r="F34" t="n">
-        <v>0.456</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6168</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0.456</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>0.456</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6168</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="K34" t="n">
         <v>124</v>
@@ -2001,7 +2001,7 @@
         <v>133</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0728</v>
+        <v>1.1018</v>
       </c>
       <c r="N34" t="n">
         <v>257</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9939</v>
+        <v>0.9837</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3435</v>
+        <v>0.3399</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1718</v>
+        <v>-0.1577</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9939</v>
+        <v>0.9837</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9939</v>
+        <v>0.9837</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9939</v>
+        <v>0.9837</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9939</v>
+        <v>0.9837</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9939</v>
+        <v>0.9837</v>
       </c>
       <c r="N35" t="n">
         <v>138</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2621</v>
+        <v>0.26</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2789</v>
+        <v>-0.263</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>116</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7048</v>
+        <v>0.6361</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2436</v>
+        <v>0.2198</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3034</v>
+        <v>-0.316</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7048</v>
+        <v>0.6361</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7048</v>
+        <v>0.6361</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7048</v>
+        <v>0.6361</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7048</v>
+        <v>0.6361</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7048</v>
+        <v>0.6361</v>
       </c>
       <c r="N37" t="n">
         <v>128</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6552</v>
+        <v>0.577</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2264</v>
+        <v>0.1994</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3259</v>
+        <v>-0.3429</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6552</v>
+        <v>0.577</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6552</v>
+        <v>0.577</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6552</v>
+        <v>0.577</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6552</v>
+        <v>0.577</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6552</v>
+        <v>0.577</v>
       </c>
       <c r="N38" t="n">
         <v>114</v>
@@ -2194,170 +2194,170 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6301</v>
+        <v>0.5698</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2177</v>
+        <v>0.1969</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3374</v>
+        <v>-0.3462</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6301</v>
+        <v>0.5698</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6301</v>
+        <v>0.5698</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6301</v>
+        <v>0.5698</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6301</v>
+        <v>0.5698</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6301</v>
+        <v>0.5698</v>
       </c>
       <c r="N39" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6223</v>
+        <v>0.5683</v>
       </c>
       <c r="C40" t="n">
-        <v>0.215</v>
+        <v>0.1964</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3409</v>
+        <v>-0.3469</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6223</v>
+        <v>0.5683</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6223</v>
+        <v>1.5683</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6223</v>
+        <v>1.5683</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6223</v>
+        <v>1.6102</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6223</v>
+        <v>0.6102000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>138</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5641</v>
+        <v>0.5554</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1949</v>
+        <v>0.1919</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3674</v>
+        <v>-0.3528</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5641</v>
+        <v>0.5554</v>
       </c>
       <c r="F41" t="n">
-        <v>1.5641</v>
+        <v>0.5554</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.5641</v>
+        <v>0.5554</v>
       </c>
       <c r="I41" t="n">
-        <v>1.6044</v>
+        <v>0.5554</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="L41" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6044</v>
+        <v>0.5554</v>
       </c>
       <c r="N41" t="n">
-        <v>199</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4823</v>
+        <v>0.5284</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1667</v>
+        <v>0.1826</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4047</v>
+        <v>-0.3651</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4823</v>
+        <v>0.5284</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4823</v>
+        <v>0.5284</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4823</v>
+        <v>0.5284</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4823</v>
+        <v>0.5284</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4823</v>
+        <v>0.5284</v>
       </c>
       <c r="N42" t="n">
         <v>138</v>
@@ -2378,93 +2378,93 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4782</v>
+        <v>0.5211</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1652</v>
+        <v>0.1801</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4065</v>
+        <v>-0.3684</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4782</v>
+        <v>0.5211</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2724</v>
+        <v>0.5211</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7506</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2724</v>
+        <v>0.5211</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1471</v>
+        <v>0.5211</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7506</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="L43" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6035</v>
+        <v>0.5211</v>
       </c>
       <c r="N43" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4694</v>
+        <v>0.4437</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1622</v>
+        <v>0.1533</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4105</v>
+        <v>-0.4037</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4694</v>
+        <v>0.4437</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4694</v>
+        <v>-0.1858</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4694</v>
+        <v>-0.1858</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4694</v>
+        <v>-0.1043</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4694</v>
+        <v>0.5251999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>116</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3949</v>
+        <v>0.3928</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1365</v>
+        <v>0.1357</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4444</v>
+        <v>-0.4268</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3949</v>
+        <v>0.3928</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3949</v>
+        <v>0.3928</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3949</v>
+        <v>0.3928</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3949</v>
+        <v>0.3928</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3949</v>
+        <v>0.3928</v>
       </c>
       <c r="N45" t="n">
         <v>114</v>
@@ -2520,31 +2520,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3531</v>
+        <v>0.3546</v>
       </c>
       <c r="C46" t="n">
-        <v>0.122</v>
+        <v>0.1225</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4635</v>
+        <v>-0.4443</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3531</v>
+        <v>0.3546</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.8165</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.4962</v>
+        <v>-0.4619</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.8165</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8712</v>
+        <v>0.8384</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.4962</v>
+        <v>-0.4619</v>
       </c>
       <c r="K46" t="n">
         <v>152</v>
@@ -2553,7 +2553,7 @@
         <v>47</v>
       </c>
       <c r="M46" t="n">
-        <v>0.375</v>
+        <v>0.3765000000000001</v>
       </c>
       <c r="N46" t="n">
         <v>199</v>
@@ -2562,93 +2562,93 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ptr</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2646</v>
+        <v>0.2732</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0914</v>
+        <v>0.0944</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5038</v>
+        <v>-0.4813</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2646</v>
+        <v>0.2732</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2646</v>
+        <v>-1.1657</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1.4389</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2646</v>
+        <v>-1.1657</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2646</v>
+        <v>-0.6545</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1.4389</v>
       </c>
       <c r="K47" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2646</v>
+        <v>0.7844000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>134</v>
+        <v>280</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2412</v>
+        <v>0.2545</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0833</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5144</v>
+        <v>-0.4899</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2412</v>
+        <v>0.2545</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2412</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1.0998</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2412</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2412</v>
+        <v>-0.4746</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1.0998</v>
       </c>
       <c r="K48" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2412</v>
+        <v>0.6252000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>116</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2311</v>
+        <v>0.2111</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0799</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.519</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2311</v>
+        <v>0.2111</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2311</v>
+        <v>0.2111</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2311</v>
+        <v>0.2111</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2311</v>
+        <v>0.2111</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2311</v>
+        <v>0.2111</v>
       </c>
       <c r="N49" t="n">
         <v>138</v>
@@ -2700,93 +2700,93 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.2017</v>
+        <v>0.2028</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0697</v>
+        <v>0.0701</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5324</v>
+        <v>-0.5134</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2017</v>
+        <v>0.2028</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.1795</v>
+        <v>0.2028</v>
       </c>
       <c r="G50" t="n">
-        <v>1.3812</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.1795</v>
+        <v>0.2028</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6369</v>
+        <v>0.2028</v>
       </c>
       <c r="J50" t="n">
-        <v>1.3812</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="L50" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7443</v>
+        <v>0.2028</v>
       </c>
       <c r="N50" t="n">
-        <v>280</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>ptr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0125</v>
+        <v>0.1945</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0043</v>
+        <v>0.0672</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6299</v>
+        <v>-0.5172</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0125</v>
+        <v>0.1945</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.0961</v>
+        <v>0.1945</v>
       </c>
       <c r="G51" t="n">
-        <v>1.0836</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.0961</v>
+        <v>0.1945</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5919</v>
+        <v>0.1945</v>
       </c>
       <c r="J51" t="n">
-        <v>1.0836</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="L51" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4916999999999999</v>
+        <v>0.1945</v>
       </c>
       <c r="N51" t="n">
-        <v>300</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52">
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0527</v>
+        <v>-0.0315</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0182</v>
+        <v>-0.0109</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6482</v>
+        <v>-0.6201</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0527</v>
+        <v>-0.0315</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0527</v>
+        <v>-0.0315</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0527</v>
+        <v>-0.0315</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0527</v>
+        <v>-0.0315</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0527</v>
+        <v>-0.0315</v>
       </c>
       <c r="N52" t="n">
         <v>116</v>
@@ -2838,47 +2838,47 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1249</v>
+        <v>-0.1471</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0432</v>
+        <v>-0.0508</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6811</v>
+        <v>-0.6728</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1249</v>
+        <v>-0.1471</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1249</v>
+        <v>-0.1471</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1249</v>
+        <v>-0.1471</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1249</v>
+        <v>-0.1471</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1249</v>
+        <v>-0.1471</v>
       </c>
       <c r="N53" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.134</v>
+        <v>-0.1706</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0463</v>
+        <v>-0.059</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6852</v>
+        <v>-0.6835</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.134</v>
+        <v>-0.1706</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.134</v>
+        <v>-0.1706</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.134</v>
+        <v>-0.1706</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.134</v>
+        <v>-0.1706</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.134</v>
+        <v>-0.1706</v>
       </c>
       <c r="N54" t="n">
         <v>114</v>
@@ -2930,47 +2930,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2069</v>
+        <v>-0.208</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7184</v>
+        <v>-0.7005</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2069</v>
+        <v>-0.208</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2069</v>
+        <v>-0.208</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2069</v>
+        <v>-0.208</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2069</v>
+        <v>-0.208</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2069</v>
+        <v>-0.208</v>
       </c>
       <c r="N55" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3241</v>
+        <v>-0.3646</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.112</v>
+        <v>-0.126</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7719</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3241</v>
+        <v>-0.3646</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3241</v>
+        <v>-0.3646</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3241</v>
+        <v>-0.3646</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3241</v>
+        <v>-0.3646</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3241</v>
+        <v>-0.3646</v>
       </c>
       <c r="N56" t="n">
         <v>134</v>
@@ -3026,31 +3026,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.6169</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1991</v>
+        <v>-0.2132</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.8865</v>
+        <v>-0.8868</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.6169</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.5335</v>
+        <v>-0.5794</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.0426</v>
+        <v>-0.0375</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.5335</v>
+        <v>-0.5794</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.5472</v>
+        <v>-0.5949</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.0426</v>
+        <v>-0.0375</v>
       </c>
       <c r="K57" t="n">
         <v>113</v>
@@ -3059,7 +3059,7 @@
         <v>103</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.5898</v>
+        <v>-0.6324</v>
       </c>
       <c r="N57" t="n">
         <v>216</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.7821</v>
+        <v>-0.7342</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2703</v>
+        <v>-0.2537</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.9802</v>
+        <v>-0.9403</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.7821</v>
+        <v>-0.7342</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.7821</v>
+        <v>-0.7342</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.7821</v>
+        <v>-0.7342</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.7821</v>
+        <v>-0.7342</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.7821</v>
+        <v>-0.7342</v>
       </c>
       <c r="N58" t="n">
         <v>138</v>
@@ -3118,31 +3118,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.0598</v>
+        <v>-1.0761</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3662</v>
+        <v>-0.3719</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.1066</v>
+        <v>-1.096</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.0598</v>
+        <v>-1.0761</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3516</v>
+        <v>-0.3851</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3516</v>
+        <v>-0.3851</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3607</v>
+        <v>-0.3954</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="K59" t="n">
         <v>152</v>
@@ -3151,7 +3151,7 @@
         <v>47</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.0689</v>
+        <v>-1.0864</v>
       </c>
       <c r="N59" t="n">
         <v>199</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.2329</v>
+        <v>-1.1549</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.426</v>
+        <v>-0.3991</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.1854</v>
+        <v>-1.1319</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.2329</v>
+        <v>-1.1549</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.2329</v>
+        <v>-1.1549</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.2329</v>
+        <v>-1.1549</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.2329</v>
+        <v>-1.1549</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.2329</v>
+        <v>-1.1549</v>
       </c>
       <c r="N60" t="n">
         <v>134</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.2775</v>
+        <v>-1.2071</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4415</v>
+        <v>-0.4171</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.2057</v>
+        <v>-1.1557</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.2775</v>
+        <v>-1.2071</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.2775</v>
+        <v>-1.2071</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.2775</v>
+        <v>-1.2071</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.2775</v>
+        <v>-1.2071</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-1.2775</v>
+        <v>-1.2071</v>
       </c>
       <c r="N61" t="n">
         <v>134</v>
@@ -3349,10 +3349,10 @@
         <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4367</v>
+        <v>1.4746</v>
       </c>
       <c r="J2" t="n">
-        <v>41.6643</v>
+        <v>42.7634</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4596</v>
+        <v>0.4238</v>
       </c>
       <c r="J3" t="n">
-        <v>13.3284</v>
+        <v>12.2902</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2874</v>
+        <v>0.2549</v>
       </c>
       <c r="J4" t="n">
-        <v>8.3346</v>
+        <v>7.3921</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0241</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8613</v>
+        <v>-0.6989</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.98</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.131</v>
+        <v>-0.1037</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.799</v>
+        <v>-3.0073</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.11</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2896</v>
+        <v>0.24</v>
       </c>
       <c r="J7" t="n">
-        <v>8.398400000000001</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.053</v>
+        <v>-0.0426</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.537</v>
+        <v>-1.2354</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.92</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1179</v>
+        <v>-0.1012</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.4191</v>
+        <v>-2.9348</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1624</v>
+        <v>-0.1433</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.7096</v>
+        <v>-4.1557</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3216</v>
+        <v>-0.3047</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.3264</v>
+        <v>-8.8363</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.53</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1492</v>
+        <v>1.1618</v>
       </c>
       <c r="J12" t="n">
-        <v>24.1332</v>
+        <v>24.3978</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.45</v>
       </c>
       <c r="I13" t="n">
-        <v>1.007</v>
+        <v>1.0064</v>
       </c>
       <c r="J13" t="n">
-        <v>21.147</v>
+        <v>21.1344</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.39</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8993</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>18.8853</v>
+        <v>18.7026</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>1.37</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8628</v>
+        <v>0.8516</v>
       </c>
       <c r="J15" t="n">
-        <v>18.1188</v>
+        <v>17.8836</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>1.23</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5838</v>
+        <v>0.5576</v>
       </c>
       <c r="J16" t="n">
-        <v>12.2598</v>
+        <v>11.7096</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0521</v>
+        <v>-0.0387</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0941</v>
+        <v>-0.8127</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>0.79</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2368</v>
+        <v>-0.2216</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.9728</v>
+        <v>-4.6536</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>0.71</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3109</v>
+        <v>-0.296</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.5289</v>
+        <v>-6.216</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>0.63</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3826</v>
+        <v>-0.3703</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.034599999999999</v>
+        <v>-7.7763</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4448</v>
+        <v>-0.4372</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.3408</v>
+        <v>-9.1812</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.41</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6129</v>
+        <v>0.6443</v>
       </c>
       <c r="J22" t="n">
-        <v>18.387</v>
+        <v>19.329</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.13</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2503</v>
+        <v>0.2353</v>
       </c>
       <c r="J23" t="n">
-        <v>7.509</v>
+        <v>7.059</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0386</v>
+        <v>0.029</v>
       </c>
       <c r="J24" t="n">
-        <v>1.158</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.68</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3618</v>
+        <v>-0.3478</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.854</v>
+        <v>-10.434</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.54</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4854</v>
+        <v>-0.4845</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.562</v>
+        <v>-14.535</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6271</v>
+        <v>0.5555</v>
       </c>
       <c r="J27" t="n">
-        <v>18.813</v>
+        <v>16.665</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.34</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4585</v>
+        <v>0.3925</v>
       </c>
       <c r="J28" t="n">
-        <v>13.755</v>
+        <v>11.775</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2388</v>
+        <v>0.1931</v>
       </c>
       <c r="J29" t="n">
-        <v>7.164</v>
+        <v>5.793</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1854</v>
+        <v>0.1468</v>
       </c>
       <c r="J30" t="n">
-        <v>5.562</v>
+        <v>4.404</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2275</v>
+        <v>-0.2082</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.825</v>
+        <v>-6.246</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.58</v>
       </c>
       <c r="I32" t="n">
-        <v>1.216</v>
+        <v>1.2415</v>
       </c>
       <c r="J32" t="n">
-        <v>23.104</v>
+        <v>23.5885</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.57</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1992</v>
+        <v>1.223</v>
       </c>
       <c r="J33" t="n">
-        <v>22.7848</v>
+        <v>23.237</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1322</v>
+        <v>1.1494</v>
       </c>
       <c r="J34" t="n">
-        <v>21.5118</v>
+        <v>21.8386</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>1.53</v>
       </c>
       <c r="I35" t="n">
-        <v>1.1322</v>
+        <v>1.1494</v>
       </c>
       <c r="J35" t="n">
-        <v>21.5118</v>
+        <v>21.8386</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>1.42</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9397</v>
+        <v>0.9399</v>
       </c>
       <c r="J36" t="n">
-        <v>17.8543</v>
+        <v>17.8581</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>0.85</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1489</v>
+        <v>-0.1298</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.8291</v>
+        <v>-2.4662</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2156</v>
+        <v>-0.1999</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.0964</v>
+        <v>-3.7981</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>0.63</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3706</v>
+        <v>-0.3612</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.0414</v>
+        <v>-6.8628</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.5</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4828</v>
+        <v>-0.4792</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.1732</v>
+        <v>-9.104799999999999</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.32</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6411</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.1809</v>
+        <v>-12.5362</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.82</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3286</v>
+        <v>1.3328</v>
       </c>
       <c r="J42" t="n">
-        <v>27.9006</v>
+        <v>27.9888</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.35</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7245</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>15.2145</v>
+        <v>15.0402</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>13.7067</v>
+        <v>13.5807</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.623</v>
+        <v>0.618</v>
       </c>
       <c r="J45" t="n">
-        <v>13.083</v>
+        <v>12.978</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>1.22</v>
       </c>
       <c r="I46" t="n">
-        <v>0.53</v>
+        <v>0.5274</v>
       </c>
       <c r="J46" t="n">
-        <v>11.13</v>
+        <v>11.0754</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>0.97</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0236</v>
+        <v>-0.0125</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.4956</v>
+        <v>-0.2625</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>0.92</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0935</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.9635</v>
+        <v>-1.6527</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.66</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3564</v>
+        <v>-0.3427</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.4844</v>
+        <v>-7.1967</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.57</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4367</v>
+        <v>-0.4284</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.1707</v>
+        <v>-8.9964</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4544</v>
+        <v>-0.4477</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.542400000000001</v>
+        <v>-9.4017</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7287</v>
+        <v>0.713</v>
       </c>
       <c r="J52" t="n">
-        <v>26.2332</v>
+        <v>25.668</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.27</v>
       </c>
       <c r="I53" t="n">
-        <v>0.637</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>22.932</v>
+        <v>22.446</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.14</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4178</v>
+        <v>0.3805</v>
       </c>
       <c r="J54" t="n">
-        <v>15.0408</v>
+        <v>13.698</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0801</v>
+        <v>-0.0595</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.8836</v>
+        <v>-2.142</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.9</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3667</v>
+        <v>-0.3244</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.2012</v>
+        <v>-11.6784</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.32</v>
       </c>
       <c r="I57" t="n">
-        <v>0.57</v>
+        <v>0.5434</v>
       </c>
       <c r="J57" t="n">
-        <v>20.52</v>
+        <v>19.5624</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.14</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3195</v>
+        <v>0.2683</v>
       </c>
       <c r="J58" t="n">
-        <v>11.502</v>
+        <v>9.658799999999999</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.09</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2256</v>
+        <v>0.183</v>
       </c>
       <c r="J59" t="n">
-        <v>8.121600000000001</v>
+        <v>6.588</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1426</v>
+        <v>0.1108</v>
       </c>
       <c r="J60" t="n">
-        <v>5.1336</v>
+        <v>3.9888</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4145</v>
+        <v>-0.4063</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.922</v>
+        <v>-14.6268</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.37</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7886</v>
+        <v>0.7725</v>
       </c>
       <c r="J62" t="n">
-        <v>22.0808</v>
+        <v>21.63</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.15</v>
       </c>
       <c r="I63" t="n">
-        <v>0.439</v>
+        <v>0.4038</v>
       </c>
       <c r="J63" t="n">
-        <v>12.292</v>
+        <v>11.3064</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.439</v>
+        <v>0.4038</v>
       </c>
       <c r="J64" t="n">
-        <v>12.292</v>
+        <v>11.3064</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1212</v>
+        <v>-0.0941</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.3936</v>
+        <v>-2.6348</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.97</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1578</v>
+        <v>-0.1263</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.4184</v>
+        <v>-3.5364</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.2</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4271</v>
+        <v>0.3714</v>
       </c>
       <c r="J67" t="n">
-        <v>11.9588</v>
+        <v>10.3992</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.19</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4113</v>
+        <v>0.355</v>
       </c>
       <c r="J68" t="n">
-        <v>11.5164</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.08</v>
       </c>
       <c r="I69" t="n">
-        <v>0.209</v>
+        <v>0.1675</v>
       </c>
       <c r="J69" t="n">
-        <v>5.852</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.91</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1373</v>
+        <v>-0.1179</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.8444</v>
+        <v>-3.3012</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3218</v>
+        <v>-0.3053</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.010400000000001</v>
+        <v>-8.548400000000001</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.53</v>
       </c>
       <c r="I72" t="n">
-        <v>1.01</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>28.28</v>
+        <v>27.958</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.522</v>
+        <v>0.5108</v>
       </c>
       <c r="J73" t="n">
-        <v>14.616</v>
+        <v>14.3024</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.12</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3685</v>
+        <v>0.3326</v>
       </c>
       <c r="J74" t="n">
-        <v>10.318</v>
+        <v>9.312799999999999</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0247</v>
+        <v>-0.0193</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.6916</v>
+        <v>-0.5404</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.9</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3711</v>
+        <v>-0.3292</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.3908</v>
+        <v>-9.217599999999999</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.31</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5729</v>
+        <v>0.5474</v>
       </c>
       <c r="J77" t="n">
-        <v>16.0412</v>
+        <v>15.3272</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3146</v>
+        <v>0.2629</v>
       </c>
       <c r="J78" t="n">
-        <v>8.8088</v>
+        <v>7.3612</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1672</v>
+        <v>-0.1471</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.6816</v>
+        <v>-4.1188</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.82</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2302</v>
+        <v>-0.2098</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.4456</v>
+        <v>-5.8744</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3082</v>
+        <v>-0.2907</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.6296</v>
+        <v>-8.1396</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.34</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4665</v>
+        <v>0.4092</v>
       </c>
       <c r="J82" t="n">
-        <v>13.995</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.32</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4488</v>
+        <v>0.3876</v>
       </c>
       <c r="J83" t="n">
-        <v>13.464</v>
+        <v>11.628</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.04</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0877</v>
+        <v>0.0639</v>
       </c>
       <c r="J84" t="n">
-        <v>2.631</v>
+        <v>1.917</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0497</v>
+        <v>0.0345</v>
       </c>
       <c r="J85" t="n">
-        <v>1.491</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.62</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.425</v>
+        <v>-0.4182</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.75</v>
+        <v>-12.546</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.25</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3884</v>
+        <v>0.3843</v>
       </c>
       <c r="J87" t="n">
-        <v>11.652</v>
+        <v>11.529</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>1.23</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3633</v>
+        <v>0.357</v>
       </c>
       <c r="J88" t="n">
-        <v>10.899</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2022</v>
+        <v>0.1879</v>
       </c>
       <c r="J89" t="n">
-        <v>6.066</v>
+        <v>5.637</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1419</v>
+        <v>0.128</v>
       </c>
       <c r="J90" t="n">
-        <v>4.257</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2407</v>
+        <v>-0.2209</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.221</v>
+        <v>-6.627</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0876</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>-2.2776</v>
+        <v>-1.9344</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>0.93</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1003</v>
+        <v>-0.0862</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.6078</v>
+        <v>-2.2412</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>0.89</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1473</v>
+        <v>-0.1306</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.8298</v>
+        <v>-3.3956</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>0.79</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2485</v>
+        <v>-0.2295</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.461</v>
+        <v>-5.967</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.73</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3057</v>
+        <v>-0.2882</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.9482</v>
+        <v>-7.4932</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.54</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0.9875</v>
       </c>
       <c r="J97" t="n">
-        <v>26</v>
+        <v>25.675</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7369</v>
+        <v>0.7235</v>
       </c>
       <c r="J98" t="n">
-        <v>19.1594</v>
+        <v>18.811</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>1.2</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5129</v>
+        <v>0.5047</v>
       </c>
       <c r="J99" t="n">
-        <v>13.3354</v>
+        <v>13.1222</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3773</v>
+        <v>0.3446</v>
       </c>
       <c r="J100" t="n">
-        <v>9.809799999999999</v>
+        <v>8.9596</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>1.05</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1603</v>
+        <v>0.1344</v>
       </c>
       <c r="J101" t="n">
-        <v>4.1678</v>
+        <v>3.4944</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>0.73</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2806</v>
+        <v>-0.2681</v>
       </c>
       <c r="J102" t="n">
-        <v>-5.612</v>
+        <v>-5.362</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>0.73</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2806</v>
+        <v>-0.2681</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.612</v>
+        <v>-5.362</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3189</v>
+        <v>-0.3077</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.378</v>
+        <v>-6.154</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.59</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4061</v>
+        <v>-0.3971</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.122</v>
+        <v>-7.942</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.43</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5466</v>
+        <v>-0.5504</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.932</v>
+        <v>-11.008</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.83</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3202</v>
+        <v>1.3244</v>
       </c>
       <c r="J107" t="n">
-        <v>26.404</v>
+        <v>26.488</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.61</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0527</v>
+        <v>1.0462</v>
       </c>
       <c r="J108" t="n">
-        <v>21.054</v>
+        <v>20.924</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>1.46</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8641</v>
+        <v>0.8569</v>
       </c>
       <c r="J109" t="n">
-        <v>17.282</v>
+        <v>17.138</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>1.44</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8378</v>
+        <v>0.8307</v>
       </c>
       <c r="J110" t="n">
-        <v>16.756</v>
+        <v>16.614</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>1.19</v>
       </c>
       <c r="I111" t="n">
-        <v>0.469</v>
+        <v>0.45</v>
       </c>
       <c r="J111" t="n">
-        <v>9.380000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.57</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0337</v>
+        <v>1.0224</v>
       </c>
       <c r="J112" t="n">
-        <v>23.7751</v>
+        <v>23.5152</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.43</v>
       </c>
       <c r="I113" t="n">
-        <v>0.845</v>
+        <v>0.8309</v>
       </c>
       <c r="J113" t="n">
-        <v>19.435</v>
+        <v>19.1107</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.38</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7754</v>
+        <v>0.7621</v>
       </c>
       <c r="J114" t="n">
-        <v>17.8342</v>
+        <v>17.5283</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>1.21</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.5205</v>
       </c>
       <c r="J115" t="n">
-        <v>12.0911</v>
+        <v>11.9715</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5455</v>
+        <v>-0.51</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.5465</v>
+        <v>-11.73</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.01</v>
       </c>
       <c r="I117" t="n">
-        <v>0.097</v>
+        <v>0.0789</v>
       </c>
       <c r="J117" t="n">
-        <v>2.231</v>
+        <v>1.8147</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>0.92</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1003</v>
+        <v>-0.0862</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.3069</v>
+        <v>-1.9826</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2221</v>
+        <v>-0.2058</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.1083</v>
+        <v>-4.7334</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.62</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3966</v>
+        <v>-0.3849</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.1218</v>
+        <v>-8.8527</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.49</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.511</v>
+        <v>-0.5113</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.753</v>
+        <v>-11.7599</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.49</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9246</v>
+        <v>0.9111</v>
       </c>
       <c r="J122" t="n">
-        <v>22.1904</v>
+        <v>21.8664</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.48</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9111</v>
+        <v>0.8975</v>
       </c>
       <c r="J123" t="n">
-        <v>21.8664</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.34</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7174</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="J124" t="n">
-        <v>17.2176</v>
+        <v>16.9464</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>1.26</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6021</v>
+        <v>0.5957</v>
       </c>
       <c r="J125" t="n">
-        <v>14.4504</v>
+        <v>14.2968</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3139</v>
+        <v>-0.2767</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.5336</v>
+        <v>-6.6408</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2567</v>
+        <v>0.2133</v>
       </c>
       <c r="J127" t="n">
-        <v>6.1608</v>
+        <v>5.1192</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2348</v>
+        <v>0.1932</v>
       </c>
       <c r="J128" t="n">
-        <v>5.6352</v>
+        <v>4.6368</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.84</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1972</v>
+        <v>-0.1797</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.7328</v>
+        <v>-4.3128</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2741</v>
+        <v>-0.2561</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.5784</v>
+        <v>-6.1464</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.37</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6364</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.8416</v>
+        <v>-15.2736</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.5</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1225</v>
+        <v>1.1355</v>
       </c>
       <c r="J132" t="n">
-        <v>29.185</v>
+        <v>29.523</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8517</v>
+        <v>0.8294</v>
       </c>
       <c r="J133" t="n">
-        <v>22.1442</v>
+        <v>21.5644</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6862</v>
+        <v>0.6529</v>
       </c>
       <c r="J134" t="n">
-        <v>17.8412</v>
+        <v>16.9754</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.87</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.444</v>
+        <v>-0.4017</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.544</v>
+        <v>-10.4442</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.65</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.9371</v>
+        <v>-0.929</v>
       </c>
       <c r="J136" t="n">
-        <v>-24.3646</v>
+        <v>-24.154</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.37</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6998</v>
+        <v>0.6428</v>
       </c>
       <c r="J137" t="n">
-        <v>18.1948</v>
+        <v>16.7128</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.28</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5603</v>
+        <v>0.5008</v>
       </c>
       <c r="J138" t="n">
-        <v>14.5678</v>
+        <v>13.0208</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.96</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.074</v>
+        <v>-0.0593</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.924</v>
+        <v>-1.5418</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2739</v>
+        <v>-0.2548</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.1214</v>
+        <v>-6.6248</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3402</v>
+        <v>-0.325</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.8452</v>
+        <v>-8.449999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>2.06</v>
       </c>
       <c r="I142" t="n">
-        <v>1.7703</v>
+        <v>1.8282</v>
       </c>
       <c r="J142" t="n">
-        <v>42.4872</v>
+        <v>43.8768</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.47</v>
       </c>
       <c r="I143" t="n">
-        <v>1.034</v>
+        <v>1.0408</v>
       </c>
       <c r="J143" t="n">
-        <v>24.816</v>
+        <v>24.9792</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.36</v>
       </c>
       <c r="I144" t="n">
-        <v>0.8469</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J144" t="n">
-        <v>20.3256</v>
+        <v>19.9968</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0406</v>
+        <v>0.0227</v>
       </c>
       <c r="J145" t="n">
-        <v>0.9744</v>
+        <v>0.5448</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3796</v>
+        <v>-0.3434</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.1104</v>
+        <v>-8.2416</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.12</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3547</v>
+        <v>0.3093</v>
       </c>
       <c r="J147" t="n">
-        <v>8.5128</v>
+        <v>7.4232</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.123</v>
+        <v>0.0982</v>
       </c>
       <c r="J148" t="n">
-        <v>2.952</v>
+        <v>2.3568</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.6</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4163</v>
+        <v>-0.4062</v>
       </c>
       <c r="J149" t="n">
-        <v>-9.991199999999999</v>
+        <v>-9.748799999999999</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.6</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4163</v>
+        <v>-0.4062</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.991199999999999</v>
+        <v>-9.748799999999999</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.59</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4252</v>
+        <v>-0.4159</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.2048</v>
+        <v>-9.9816</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6221</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J152" t="n">
-        <v>16.1746</v>
+        <v>14.638</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3592</v>
+        <v>0.305</v>
       </c>
       <c r="J153" t="n">
-        <v>9.3392</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1009</v>
+        <v>-0.0837</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.6234</v>
+        <v>-2.1762</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1375</v>
+        <v>-0.1181</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.575</v>
+        <v>-3.0706</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2645</v>
+        <v>-0.245</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.877</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.31</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7817</v>
+        <v>0.7549</v>
       </c>
       <c r="J157" t="n">
-        <v>20.3242</v>
+        <v>19.6274</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.29</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7408</v>
+        <v>0.7114</v>
       </c>
       <c r="J158" t="n">
-        <v>19.2608</v>
+        <v>18.4964</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3671</v>
+        <v>0.3317</v>
       </c>
       <c r="J159" t="n">
-        <v>9.544600000000001</v>
+        <v>8.6242</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1763</v>
+        <v>0.1495</v>
       </c>
       <c r="J160" t="n">
-        <v>4.5838</v>
+        <v>3.887</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1111</v>
+        <v>0.0902</v>
       </c>
       <c r="J161" t="n">
-        <v>2.8886</v>
+        <v>2.3452</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9228</v>
+        <v>0.9074</v>
       </c>
       <c r="J162" t="n">
-        <v>25.8384</v>
+        <v>25.4072</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6373</v>
+        <v>0.603</v>
       </c>
       <c r="J163" t="n">
-        <v>17.8444</v>
+        <v>16.884</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3923</v>
+        <v>0.356</v>
       </c>
       <c r="J164" t="n">
-        <v>10.9844</v>
+        <v>9.968</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1458</v>
+        <v>0.1214</v>
       </c>
       <c r="J165" t="n">
-        <v>4.0824</v>
+        <v>3.3992</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.98</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1266</v>
+        <v>-0.0994</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.5448</v>
+        <v>-2.7832</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6775</v>
+        <v>0.6229</v>
       </c>
       <c r="J167" t="n">
-        <v>18.97</v>
+        <v>17.4412</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.482</v>
+        <v>0.4243</v>
       </c>
       <c r="J168" t="n">
-        <v>13.496</v>
+        <v>11.8804</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>0.8</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2474</v>
+        <v>-0.2274</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.9272</v>
+        <v>-6.3672</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.73</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3148</v>
+        <v>-0.2975</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.814399999999999</v>
+        <v>-8.33</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.64</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3972</v>
+        <v>-0.3861</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.1216</v>
+        <v>-10.8108</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.21</v>
       </c>
       <c r="I172" t="n">
-        <v>0.595</v>
+        <v>0.5562</v>
       </c>
       <c r="J172" t="n">
-        <v>17.85</v>
+        <v>16.686</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3567</v>
+        <v>0.3161</v>
       </c>
       <c r="J173" t="n">
-        <v>10.701</v>
+        <v>9.483000000000001</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.03</v>
       </c>
       <c r="I174" t="n">
-        <v>0.129</v>
+        <v>0.1043</v>
       </c>
       <c r="J174" t="n">
-        <v>3.87</v>
+        <v>3.129</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0521</v>
+        <v>0.0392</v>
       </c>
       <c r="J175" t="n">
-        <v>1.563</v>
+        <v>1.176</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.9</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3523</v>
+        <v>-0.3097</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.569</v>
+        <v>-9.291</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.3</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5883</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J177" t="n">
-        <v>17.649</v>
+        <v>15.861</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.22</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4597</v>
+        <v>0.4013</v>
       </c>
       <c r="J178" t="n">
-        <v>13.791</v>
+        <v>12.039</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.04</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1208</v>
+        <v>0.0921</v>
       </c>
       <c r="J179" t="n">
-        <v>3.624</v>
+        <v>2.763</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.87</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1832</v>
+        <v>-0.1626</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.496</v>
+        <v>-4.878</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.74</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3134</v>
+        <v>-0.2965</v>
       </c>
       <c r="J181" t="n">
-        <v>-9.401999999999999</v>
+        <v>-8.895</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.67</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3546</v>
+        <v>1.3816</v>
       </c>
       <c r="J182" t="n">
-        <v>37.9288</v>
+        <v>38.6848</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.28</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.6973</v>
       </c>
       <c r="J183" t="n">
-        <v>20.3924</v>
+        <v>19.5244</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.05</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1824</v>
+        <v>0.1546</v>
       </c>
       <c r="J184" t="n">
-        <v>5.1072</v>
+        <v>4.3288</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.87</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.444</v>
+        <v>-0.4017</v>
       </c>
       <c r="J185" t="n">
-        <v>-12.432</v>
+        <v>-11.2476</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.75</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7245</v>
+        <v>-0.6955</v>
       </c>
       <c r="J186" t="n">
-        <v>-20.286</v>
+        <v>-19.474</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4656</v>
+        <v>0.4071</v>
       </c>
       <c r="J187" t="n">
-        <v>13.0368</v>
+        <v>11.3988</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3264</v>
+        <v>0.2741</v>
       </c>
       <c r="J188" t="n">
-        <v>9.139200000000001</v>
+        <v>7.6748</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.03</v>
       </c>
       <c r="I189" t="n">
-        <v>0.099</v>
+        <v>0.0733</v>
       </c>
       <c r="J189" t="n">
-        <v>2.772</v>
+        <v>2.0524</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.85</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2022</v>
+        <v>-0.1815</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.6616</v>
+        <v>-5.082</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.8</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2531</v>
+        <v>-0.2333</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.0868</v>
+        <v>-6.5324</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>0.86</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.1347</v>
+        <v>-0.1145</v>
       </c>
       <c r="J192" t="n">
-        <v>-2.8287</v>
+        <v>-2.4045</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>0.65</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3519</v>
+        <v>-0.3425</v>
       </c>
       <c r="J193" t="n">
-        <v>-7.3899</v>
+        <v>-7.1925</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.55</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4377</v>
+        <v>-0.431</v>
       </c>
       <c r="J194" t="n">
-        <v>-9.191700000000001</v>
+        <v>-9.051</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.52</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.464</v>
+        <v>-0.459</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.744</v>
+        <v>-9.638999999999999</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.47</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.508</v>
+        <v>-0.507</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.668</v>
+        <v>-10.647</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>2.23</v>
       </c>
       <c r="I197" t="n">
-        <v>1.9158</v>
+        <v>1.9818</v>
       </c>
       <c r="J197" t="n">
-        <v>40.2318</v>
+        <v>41.6178</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.81</v>
       </c>
       <c r="I198" t="n">
-        <v>1.4352</v>
+        <v>1.464</v>
       </c>
       <c r="J198" t="n">
-        <v>30.1392</v>
+        <v>30.744</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.38</v>
       </c>
       <c r="I199" t="n">
-        <v>0.8605</v>
+        <v>0.8551</v>
       </c>
       <c r="J199" t="n">
-        <v>18.0705</v>
+        <v>17.9571</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>1.21</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5163</v>
+        <v>0.4877</v>
       </c>
       <c r="J200" t="n">
-        <v>10.8423</v>
+        <v>10.2417</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>1.19</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4719</v>
+        <v>0.4413</v>
       </c>
       <c r="J201" t="n">
-        <v>9.9099</v>
+        <v>9.267300000000001</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>2.22</v>
       </c>
       <c r="I202" t="n">
-        <v>1.8717</v>
+        <v>1.9359</v>
       </c>
       <c r="J202" t="n">
-        <v>7.4868</v>
+        <v>7.7436</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>2.08</v>
       </c>
       <c r="I203" t="n">
-        <v>1.7188</v>
+        <v>1.7694</v>
       </c>
       <c r="J203" t="n">
-        <v>6.8752</v>
+        <v>7.0776</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.95</v>
       </c>
       <c r="I204" t="n">
-        <v>1.5743</v>
+        <v>1.6148</v>
       </c>
       <c r="J204" t="n">
-        <v>6.2972</v>
+        <v>6.4592</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.53</v>
       </c>
       <c r="I205" t="n">
-        <v>1.0818</v>
+        <v>1.105</v>
       </c>
       <c r="J205" t="n">
-        <v>4.3272</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3415</v>
+        <v>-0.3196</v>
       </c>
       <c r="J206" t="n">
-        <v>-1.366</v>
+        <v>-1.2784</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>0.74</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.2642</v>
+        <v>-0.251</v>
       </c>
       <c r="J207" t="n">
-        <v>-1.0568</v>
+        <v>-1.004</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.71</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2942</v>
+        <v>-0.2825</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.1768</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.58</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.411</v>
+        <v>-0.4032</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.644</v>
+        <v>-1.6128</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.5</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4807</v>
+        <v>-0.4771</v>
       </c>
       <c r="J210" t="n">
-        <v>-1.9228</v>
+        <v>-1.9084</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.49</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4895</v>
+        <v>-0.4867</v>
       </c>
       <c r="J211" t="n">
-        <v>-1.958</v>
+        <v>-1.9468</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8083</v>
+        <v>0.7784</v>
       </c>
       <c r="J212" t="n">
-        <v>4.0415</v>
+        <v>3.892</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.07</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2434</v>
+        <v>0.2028</v>
       </c>
       <c r="J213" t="n">
-        <v>1.217</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.253</v>
+        <v>-0.2354</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.265</v>
+        <v>-1.177</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.64</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3821</v>
+        <v>-0.3692</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.9105</v>
+        <v>-1.846</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.13</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8148</v>
+        <v>-0.8751</v>
       </c>
       <c r="J216" t="n">
-        <v>-4.074</v>
+        <v>-4.3755</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>2.36</v>
       </c>
       <c r="I217" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J217" t="n">
-        <v>9.686</v>
+        <v>9.909000000000001</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.73</v>
       </c>
       <c r="I218" t="n">
-        <v>1.3638</v>
+        <v>1.3867</v>
       </c>
       <c r="J218" t="n">
-        <v>6.819</v>
+        <v>6.9335</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.28</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6868</v>
+        <v>0.6657</v>
       </c>
       <c r="J219" t="n">
-        <v>3.434</v>
+        <v>3.3285</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>1.03</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0713</v>
+        <v>0.0487</v>
       </c>
       <c r="J220" t="n">
-        <v>0.3565</v>
+        <v>0.2435</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.61</v>
       </c>
       <c r="I221" t="n">
-        <v>-1.0549</v>
+        <v>-1.0702</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.2745</v>
+        <v>-5.351</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.4</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9353</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="J222" t="n">
-        <v>14.9648</v>
+        <v>14.7824</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.35</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8403</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>13.4448</v>
+        <v>13.1376</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6832</v>
+        <v>0.6561</v>
       </c>
       <c r="J224" t="n">
-        <v>10.9312</v>
+        <v>10.4976</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6229</v>
+        <v>0.5938</v>
       </c>
       <c r="J225" t="n">
-        <v>9.9664</v>
+        <v>9.5008</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>1.06</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1889</v>
+        <v>0.1612</v>
       </c>
       <c r="J226" t="n">
-        <v>3.0224</v>
+        <v>2.5792</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.06</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2057</v>
+        <v>0.1658</v>
       </c>
       <c r="J227" t="n">
-        <v>3.2912</v>
+        <v>2.6528</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.04</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1581</v>
+        <v>0.1238</v>
       </c>
       <c r="J228" t="n">
-        <v>2.5296</v>
+        <v>1.9808</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.82</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2181</v>
+        <v>-0.1995</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.4896</v>
+        <v>-3.192</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3416</v>
+        <v>-0.3258</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.4656</v>
+        <v>-5.2128</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4138</v>
+        <v>-0.4037</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.6208</v>
+        <v>-6.4592</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.06</v>
       </c>
       <c r="I232" t="n">
-        <v>0.1868</v>
+        <v>0.1469</v>
       </c>
       <c r="J232" t="n">
-        <v>5.0436</v>
+        <v>3.9663</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>0.92</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1176</v>
+        <v>-0.1011</v>
       </c>
       <c r="J233" t="n">
-        <v>-3.1752</v>
+        <v>-2.7297</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.88</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.162</v>
+        <v>-0.143</v>
       </c>
       <c r="J234" t="n">
-        <v>-4.374</v>
+        <v>-3.861</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.86</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1832</v>
+        <v>-0.1636</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.9464</v>
+        <v>-4.4172</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1937</v>
+        <v>-0.1739</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.2299</v>
+        <v>-4.6953</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.71</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3804</v>
+        <v>1.4059</v>
       </c>
       <c r="J237" t="n">
-        <v>37.2708</v>
+        <v>37.9593</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.35</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8498</v>
+        <v>0.8293</v>
       </c>
       <c r="J238" t="n">
-        <v>22.9446</v>
+        <v>22.3911</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.04</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1354</v>
+        <v>0.1118</v>
       </c>
       <c r="J239" t="n">
-        <v>3.6558</v>
+        <v>3.0186</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>1.02</v>
       </c>
       <c r="I240" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0491</v>
       </c>
       <c r="J240" t="n">
-        <v>1.7604</v>
+        <v>1.3257</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.95</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2397</v>
+        <v>-0.2034</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.4719</v>
+        <v>-5.4918</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.08</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3062</v>
+        <v>0.2727</v>
       </c>
       <c r="J242" t="n">
-        <v>5.8178</v>
+        <v>5.1813</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>0.79</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2342</v>
+        <v>-0.2193</v>
       </c>
       <c r="J243" t="n">
-        <v>-4.4498</v>
+        <v>-4.1667</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.76</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2637</v>
+        <v>-0.2492</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.0103</v>
+        <v>-4.7348</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.5</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4953</v>
+        <v>-0.493</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.4107</v>
+        <v>-9.367000000000001</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.42</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5649</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.7331</v>
+        <v>-10.8699</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>2.43</v>
       </c>
       <c r="I247" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J247" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2586</v>
+        <v>1.2797</v>
       </c>
       <c r="J248" t="n">
-        <v>23.9134</v>
+        <v>24.3143</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.28</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6684</v>
+        <v>0.6484</v>
       </c>
       <c r="J249" t="n">
-        <v>12.6996</v>
+        <v>12.3196</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.26</v>
       </c>
       <c r="I250" t="n">
-        <v>0.6271</v>
+        <v>0.6046</v>
       </c>
       <c r="J250" t="n">
-        <v>11.9149</v>
+        <v>11.4874</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>1.04</v>
       </c>
       <c r="I251" t="n">
-        <v>0.0864</v>
+        <v>0.0577</v>
       </c>
       <c r="J251" t="n">
-        <v>1.6416</v>
+        <v>1.0963</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.67</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2904</v>
+        <v>1.3097</v>
       </c>
       <c r="J252" t="n">
-        <v>30.9696</v>
+        <v>31.4328</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.66</v>
       </c>
       <c r="I253" t="n">
-        <v>1.2778</v>
+        <v>1.2966</v>
       </c>
       <c r="J253" t="n">
-        <v>30.6672</v>
+        <v>31.1184</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>1.38</v>
       </c>
       <c r="I254" t="n">
-        <v>0.8812</v>
+        <v>0.8712</v>
       </c>
       <c r="J254" t="n">
-        <v>21.1488</v>
+        <v>20.9088</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>1.28</v>
       </c>
       <c r="I255" t="n">
-        <v>0.6879</v>
+        <v>0.6667</v>
       </c>
       <c r="J255" t="n">
-        <v>16.5096</v>
+        <v>16.0008</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.98</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1664</v>
+        <v>-0.1428</v>
       </c>
       <c r="J256" t="n">
-        <v>-3.9936</v>
+        <v>-3.4272</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>0.95</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0552</v>
+        <v>-0.0423</v>
       </c>
       <c r="J257" t="n">
-        <v>-1.3248</v>
+        <v>-1.0152</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>0.74</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2853</v>
+        <v>-0.2698</v>
       </c>
       <c r="J258" t="n">
-        <v>-6.8472</v>
+        <v>-6.4752</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>0.72</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3032</v>
+        <v>-0.2877</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.2768</v>
+        <v>-6.9048</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.7</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3212</v>
+        <v>-0.3061</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.7088</v>
+        <v>-7.3464</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.6</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4111</v>
+        <v>-0.4006</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.866400000000001</v>
+        <v>-9.6144</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.57</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1738</v>
+        <v>1.1882</v>
       </c>
       <c r="J262" t="n">
-        <v>25.8236</v>
+        <v>26.1404</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.46</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0247</v>
+        <v>1.0287</v>
       </c>
       <c r="J263" t="n">
-        <v>22.5434</v>
+        <v>22.6314</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.42</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9545</v>
       </c>
       <c r="J264" t="n">
-        <v>21.1244</v>
+        <v>20.999</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.28</v>
       </c>
       <c r="I265" t="n">
-        <v>0.697</v>
+        <v>0.6736</v>
       </c>
       <c r="J265" t="n">
-        <v>15.334</v>
+        <v>14.8192</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.9</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4008</v>
+        <v>-0.3632</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.817600000000001</v>
+        <v>-7.9904</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1</v>
       </c>
       <c r="I267" t="n">
-        <v>0.0576</v>
+        <v>0.0534</v>
       </c>
       <c r="J267" t="n">
-        <v>1.2672</v>
+        <v>1.1748</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>0.88</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1453</v>
+        <v>-0.1299</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.1966</v>
+        <v>-2.8578</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.76</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2683</v>
+        <v>-0.2522</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.9026</v>
+        <v>-5.5484</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.74</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2861</v>
+        <v>-0.2701</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.2942</v>
+        <v>-5.9422</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.39</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.6081</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.0966</v>
+        <v>-13.3782</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.96</v>
       </c>
       <c r="I272" t="n">
-        <v>1.6061</v>
+        <v>1.6461</v>
       </c>
       <c r="J272" t="n">
-        <v>28.9098</v>
+        <v>29.6298</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.85</v>
       </c>
       <c r="I273" t="n">
-        <v>1.4787</v>
+        <v>1.5103</v>
       </c>
       <c r="J273" t="n">
-        <v>26.6166</v>
+        <v>27.1854</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.8</v>
       </c>
       <c r="I274" t="n">
-        <v>1.42</v>
+        <v>1.4485</v>
       </c>
       <c r="J274" t="n">
-        <v>25.56</v>
+        <v>26.073</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>1.42</v>
       </c>
       <c r="I275" t="n">
-        <v>0.931</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="J275" t="n">
-        <v>16.758</v>
+        <v>16.794</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.92</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3819</v>
+        <v>-0.3535</v>
       </c>
       <c r="J276" t="n">
-        <v>-6.8742</v>
+        <v>-6.363</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>0.83</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1825</v>
+        <v>-0.1664</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.285</v>
+        <v>-2.9952</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>0.78</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2356</v>
+        <v>-0.2212</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.2408</v>
+        <v>-3.9816</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>0.63</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3744</v>
+        <v>-0.3633</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.7392</v>
+        <v>-6.5394</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>0.59</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4095</v>
+        <v>-0.3999</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.371</v>
+        <v>-7.1982</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.47</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5151</v>
+        <v>-0.515</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.271800000000001</v>
+        <v>-9.27</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>0.9</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.1304</v>
+        <v>-0.1152</v>
       </c>
       <c r="J282" t="n">
-        <v>-3.3904</v>
+        <v>-2.9952</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>0.86</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.175</v>
+        <v>-0.1584</v>
       </c>
       <c r="J283" t="n">
-        <v>-4.55</v>
+        <v>-4.1184</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>0.84</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1958</v>
+        <v>-0.1788</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.0908</v>
+        <v>-4.6488</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.83</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2059</v>
+        <v>-0.1887</v>
       </c>
       <c r="J285" t="n">
-        <v>-5.3534</v>
+        <v>-4.9062</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.61</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4099</v>
+        <v>-0.3992</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.6574</v>
+        <v>-10.3792</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.93</v>
       </c>
       <c r="I287" t="n">
-        <v>1.6147</v>
+        <v>1.6562</v>
       </c>
       <c r="J287" t="n">
-        <v>41.9822</v>
+        <v>43.0612</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0753</v>
+        <v>1.087</v>
       </c>
       <c r="J288" t="n">
-        <v>27.9578</v>
+        <v>28.262</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1.17</v>
       </c>
       <c r="I289" t="n">
-        <v>0.4546</v>
+        <v>0.4239</v>
       </c>
       <c r="J289" t="n">
-        <v>11.8196</v>
+        <v>11.0214</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>1.13</v>
       </c>
       <c r="I290" t="n">
-        <v>0.3593</v>
+        <v>0.3273</v>
       </c>
       <c r="J290" t="n">
-        <v>9.341799999999999</v>
+        <v>8.5098</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>1.11</v>
       </c>
       <c r="I291" t="n">
-        <v>0.3091</v>
+        <v>0.2771</v>
       </c>
       <c r="J291" t="n">
-        <v>8.0366</v>
+        <v>7.2046</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.5</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0825</v>
+        <v>1.0936</v>
       </c>
       <c r="J292" t="n">
-        <v>23.815</v>
+        <v>24.0592</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.4</v>
       </c>
       <c r="I293" t="n">
-        <v>0.926</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="J293" t="n">
-        <v>20.372</v>
+        <v>20.1476</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.29</v>
       </c>
       <c r="I294" t="n">
-        <v>0.7178</v>
+        <v>0.6949</v>
       </c>
       <c r="J294" t="n">
-        <v>15.7916</v>
+        <v>15.2878</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>1.22</v>
       </c>
       <c r="I295" t="n">
-        <v>0.5734</v>
+        <v>0.5451</v>
       </c>
       <c r="J295" t="n">
-        <v>12.6148</v>
+        <v>11.9922</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>1.18</v>
       </c>
       <c r="I296" t="n">
-        <v>0.4851</v>
+        <v>0.4544</v>
       </c>
       <c r="J296" t="n">
-        <v>10.6722</v>
+        <v>9.9968</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1</v>
       </c>
       <c r="I297" t="n">
-        <v>0.0683</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>1.5026</v>
+        <v>1.4454</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>0.92</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0922</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.0284</v>
+        <v>-1.7006</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>0.68</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3378</v>
+        <v>-0.3235</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.4316</v>
+        <v>-7.117</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.54</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4624</v>
+        <v>-0.4566</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.1728</v>
+        <v>-10.0452</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.5</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4975</v>
+        <v>-0.4956</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.945</v>
+        <v>-10.9032</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.08</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2277</v>
+        <v>0.1833</v>
       </c>
       <c r="J302" t="n">
-        <v>6.6033</v>
+        <v>5.3157</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.01</v>
       </c>
       <c r="I303" t="n">
-        <v>0.0545</v>
+        <v>0.037</v>
       </c>
       <c r="J303" t="n">
-        <v>1.5805</v>
+        <v>1.073</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>0.91</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1295</v>
+        <v>-0.1119</v>
       </c>
       <c r="J304" t="n">
-        <v>-3.7555</v>
+        <v>-3.2451</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.84</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2049</v>
+        <v>-0.1849</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.9421</v>
+        <v>-5.3621</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.78</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2649</v>
+        <v>-0.2455</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.6821</v>
+        <v>-7.1195</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.62</v>
       </c>
       <c r="I307" t="n">
-        <v>1.2662</v>
+        <v>1.2846</v>
       </c>
       <c r="J307" t="n">
-        <v>36.7198</v>
+        <v>37.2534</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.19</v>
       </c>
       <c r="I308" t="n">
-        <v>0.5239</v>
+        <v>0.4895</v>
       </c>
       <c r="J308" t="n">
-        <v>15.1931</v>
+        <v>14.1955</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>1.15</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4336</v>
+        <v>0.399</v>
       </c>
       <c r="J309" t="n">
-        <v>12.5744</v>
+        <v>11.571</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>1.14</v>
       </c>
       <c r="I310" t="n">
-        <v>0.4099</v>
+        <v>0.3755</v>
       </c>
       <c r="J310" t="n">
-        <v>11.8871</v>
+        <v>10.8895</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.9</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3801</v>
+        <v>-0.3391</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.0229</v>
+        <v>-9.8339</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.42</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9969</v>
+        <v>0.993</v>
       </c>
       <c r="J312" t="n">
-        <v>28.9101</v>
+        <v>28.797</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6481</v>
       </c>
       <c r="J313" t="n">
-        <v>19.7461</v>
+        <v>18.7949</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>1.22</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5955</v>
+        <v>0.5596</v>
       </c>
       <c r="J314" t="n">
-        <v>17.2695</v>
+        <v>16.2284</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.93</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2877</v>
+        <v>-0.2476</v>
       </c>
       <c r="J315" t="n">
-        <v>-8.343299999999999</v>
+        <v>-7.1804</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.91</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3438</v>
+        <v>-0.3021</v>
       </c>
       <c r="J316" t="n">
-        <v>-9.9702</v>
+        <v>-8.760899999999999</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.26</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5581</v>
+        <v>0.5017</v>
       </c>
       <c r="J317" t="n">
-        <v>16.1849</v>
+        <v>14.5493</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.11</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2901</v>
+        <v>0.2405</v>
       </c>
       <c r="J318" t="n">
-        <v>8.4129</v>
+        <v>6.9745</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>0.96</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0673</v>
+        <v>-0.0552</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.9517</v>
+        <v>-1.6008</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.8</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2447</v>
+        <v>-0.2249</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.0963</v>
+        <v>-6.5221</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.46</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5504</v>
+        <v>-0.5584</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.9616</v>
+        <v>-16.1936</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.67</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2819</v>
+        <v>1.3017</v>
       </c>
       <c r="J322" t="n">
-        <v>26.9199</v>
+        <v>27.3357</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.64</v>
       </c>
       <c r="I323" t="n">
-        <v>1.2445</v>
+        <v>1.2631</v>
       </c>
       <c r="J323" t="n">
-        <v>26.1345</v>
+        <v>26.5251</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.58</v>
       </c>
       <c r="I324" t="n">
-        <v>1.1689</v>
+        <v>1.1857</v>
       </c>
       <c r="J324" t="n">
-        <v>24.5469</v>
+        <v>24.8997</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>1.36</v>
       </c>
       <c r="I325" t="n">
-        <v>0.8377</v>
+        <v>0.8272</v>
       </c>
       <c r="J325" t="n">
-        <v>17.5917</v>
+        <v>17.3712</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.99</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.1327</v>
+        <v>-0.1166</v>
       </c>
       <c r="J326" t="n">
-        <v>-2.7867</v>
+        <v>-2.4486</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.12</v>
       </c>
       <c r="I327" t="n">
-        <v>0.3891</v>
+        <v>0.3524</v>
       </c>
       <c r="J327" t="n">
-        <v>8.171099999999999</v>
+        <v>7.4004</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>0.85</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1722</v>
+        <v>-0.1566</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.6162</v>
+        <v>-3.2886</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.66</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3543</v>
+        <v>-0.3409</v>
       </c>
       <c r="J329" t="n">
-        <v>-7.4403</v>
+        <v>-7.1589</v>
       </c>
     </row>
     <row r="330">
@@ -16509,10 +16509,10 @@
         <v>0.47</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5222</v>
+        <v>-0.5234</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.9662</v>
+        <v>-10.9914</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.066</v>
+        <v>-0.0519</v>
       </c>
       <c r="J332" t="n">
-        <v>-1.518</v>
+        <v>-1.1937</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>0.8</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2268</v>
+        <v>-0.2115</v>
       </c>
       <c r="J333" t="n">
-        <v>-5.2164</v>
+        <v>-4.8645</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.73</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2933</v>
+        <v>-0.2783</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.7459</v>
+        <v>-6.4009</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.73</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2933</v>
+        <v>-0.2783</v>
       </c>
       <c r="J335" t="n">
-        <v>-6.7459</v>
+        <v>-6.4009</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.44</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5496</v>
+        <v>-0.5548</v>
       </c>
       <c r="J336" t="n">
-        <v>-12.6408</v>
+        <v>-12.7604</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.77</v>
       </c>
       <c r="I337" t="n">
-        <v>1.4302</v>
+        <v>1.4573</v>
       </c>
       <c r="J337" t="n">
-        <v>32.8946</v>
+        <v>33.5179</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.51</v>
       </c>
       <c r="I338" t="n">
-        <v>1.0956</v>
+        <v>1.1077</v>
       </c>
       <c r="J338" t="n">
-        <v>25.1988</v>
+        <v>25.4771</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.3</v>
       </c>
       <c r="I339" t="n">
-        <v>0.7372</v>
+        <v>0.7153</v>
       </c>
       <c r="J339" t="n">
-        <v>16.9556</v>
+        <v>16.4519</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.08</v>
       </c>
       <c r="I340" t="n">
-        <v>0.2369</v>
+        <v>0.2066</v>
       </c>
       <c r="J340" t="n">
-        <v>5.4487</v>
+        <v>4.7518</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2878</v>
+        <v>-0.2521</v>
       </c>
       <c r="J341" t="n">
-        <v>-6.6194</v>
+        <v>-5.7983</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.33</v>
       </c>
       <c r="I342" t="n">
-        <v>0.6415</v>
+        <v>0.5831</v>
       </c>
       <c r="J342" t="n">
-        <v>22.4525</v>
+        <v>20.4085</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.22</v>
       </c>
       <c r="I343" t="n">
-        <v>0.4651</v>
+        <v>0.4067</v>
       </c>
       <c r="J343" t="n">
-        <v>16.2785</v>
+        <v>14.2345</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>0.96</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0733</v>
+        <v>-0.0587</v>
       </c>
       <c r="J344" t="n">
-        <v>-2.5655</v>
+        <v>-2.0545</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2434</v>
+        <v>-0.2232</v>
       </c>
       <c r="J345" t="n">
-        <v>-8.519</v>
+        <v>-7.812</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.73</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3207</v>
+        <v>-0.3041</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.2245</v>
+        <v>-10.6435</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.35</v>
       </c>
       <c r="I347" t="n">
-        <v>0.8754</v>
+        <v>0.8549</v>
       </c>
       <c r="J347" t="n">
-        <v>30.639</v>
+        <v>29.9215</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.16</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4674</v>
+        <v>0.4281</v>
       </c>
       <c r="J348" t="n">
-        <v>16.359</v>
+        <v>14.9835</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>1.15</v>
       </c>
       <c r="I349" t="n">
-        <v>0.4441</v>
+        <v>0.4049</v>
       </c>
       <c r="J349" t="n">
-        <v>15.5435</v>
+        <v>14.1715</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>1.04</v>
       </c>
       <c r="I350" t="n">
-        <v>0.1529</v>
+        <v>0.1274</v>
       </c>
       <c r="J350" t="n">
-        <v>5.3515</v>
+        <v>4.459</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.86</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4667</v>
+        <v>-0.4246</v>
       </c>
       <c r="J351" t="n">
-        <v>-16.3345</v>
+        <v>-14.861</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.26</v>
       </c>
       <c r="I352" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6556</v>
       </c>
       <c r="J352" t="n">
-        <v>23.426</v>
+        <v>22.2904</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.18</v>
       </c>
       <c r="I353" t="n">
-        <v>0.5134</v>
+        <v>0.4743</v>
       </c>
       <c r="J353" t="n">
-        <v>17.4556</v>
+        <v>16.1262</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.14</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4204</v>
+        <v>0.3815</v>
       </c>
       <c r="J354" t="n">
-        <v>14.2936</v>
+        <v>12.971</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.12</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3724</v>
+        <v>0.3345</v>
       </c>
       <c r="J355" t="n">
-        <v>12.6616</v>
+        <v>11.373</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.86</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.4667</v>
+        <v>-0.4246</v>
       </c>
       <c r="J356" t="n">
-        <v>-15.8678</v>
+        <v>-14.4364</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.38</v>
       </c>
       <c r="I357" t="n">
-        <v>0.7173</v>
+        <v>0.6613</v>
       </c>
       <c r="J357" t="n">
-        <v>24.3882</v>
+        <v>22.4842</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2504</v>
+        <v>0.2043</v>
       </c>
       <c r="J358" t="n">
-        <v>8.5136</v>
+        <v>6.9462</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.07</v>
       </c>
       <c r="I359" t="n">
-        <v>0.1897</v>
+        <v>0.1503</v>
       </c>
       <c r="J359" t="n">
-        <v>6.4498</v>
+        <v>5.1102</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.8</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2535</v>
+        <v>-0.2337</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.619</v>
+        <v>-7.9458</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.71</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3395</v>
+        <v>-0.3242</v>
       </c>
       <c r="J361" t="n">
-        <v>-11.543</v>
+        <v>-11.0228</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.16</v>
       </c>
       <c r="I362" t="n">
-        <v>0.3812</v>
+        <v>0.3264</v>
       </c>
       <c r="J362" t="n">
-        <v>13.7232</v>
+        <v>11.7504</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.15</v>
       </c>
       <c r="I363" t="n">
-        <v>0.3629</v>
+        <v>0.3089</v>
       </c>
       <c r="J363" t="n">
-        <v>13.0644</v>
+        <v>11.1204</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.83</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.2157</v>
+        <v>-0.1955</v>
       </c>
       <c r="J364" t="n">
-        <v>-7.7652</v>
+        <v>-7.038</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.78</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.2655</v>
+        <v>-0.246</v>
       </c>
       <c r="J365" t="n">
-        <v>-9.558</v>
+        <v>-8.856</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.73</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.3133</v>
+        <v>-0.2958</v>
       </c>
       <c r="J366" t="n">
-        <v>-11.2788</v>
+        <v>-10.6488</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.45</v>
       </c>
       <c r="I367" t="n">
-        <v>1.0381</v>
+        <v>1.0416</v>
       </c>
       <c r="J367" t="n">
-        <v>37.3716</v>
+        <v>37.4976</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.31</v>
       </c>
       <c r="I368" t="n">
-        <v>0.7781</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="J368" t="n">
-        <v>28.0116</v>
+        <v>27.054</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.24</v>
       </c>
       <c r="I369" t="n">
-        <v>0.6333</v>
+        <v>0.5999</v>
       </c>
       <c r="J369" t="n">
-        <v>22.7988</v>
+        <v>21.5964</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.95</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.233</v>
+        <v>-0.1962</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.388</v>
+        <v>-7.0632</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.93</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.2928</v>
+        <v>-0.2531</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.5408</v>
+        <v>-9.111599999999999</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.02</v>
       </c>
       <c r="I372" t="n">
-        <v>0.1679</v>
+        <v>0.1513</v>
       </c>
       <c r="J372" t="n">
-        <v>3.358</v>
+        <v>3.026</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>0.75</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.2697</v>
+        <v>-0.2559</v>
       </c>
       <c r="J373" t="n">
-        <v>-5.394</v>
+        <v>-5.118</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>0.66</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.3508</v>
+        <v>-0.3382</v>
       </c>
       <c r="J374" t="n">
-        <v>-7.016</v>
+        <v>-6.764</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.5</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.492</v>
+        <v>-0.4892</v>
       </c>
       <c r="J375" t="n">
-        <v>-9.84</v>
+        <v>-9.784000000000001</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.49</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.5007</v>
+        <v>-0.499</v>
       </c>
       <c r="J376" t="n">
-        <v>-10.014</v>
+        <v>-9.98</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.79</v>
       </c>
       <c r="I377" t="n">
-        <v>1.4412</v>
+        <v>1.4687</v>
       </c>
       <c r="J377" t="n">
-        <v>28.824</v>
+        <v>29.374</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.44</v>
       </c>
       <c r="I378" t="n">
-        <v>0.9856</v>
+        <v>0.9863</v>
       </c>
       <c r="J378" t="n">
-        <v>19.712</v>
+        <v>19.726</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.41</v>
       </c>
       <c r="I379" t="n">
-        <v>0.9352</v>
+        <v>0.9294</v>
       </c>
       <c r="J379" t="n">
-        <v>18.704</v>
+        <v>18.588</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>1.16</v>
       </c>
       <c r="I380" t="n">
-        <v>0.4289</v>
+        <v>0.3978</v>
       </c>
       <c r="J380" t="n">
-        <v>8.577999999999999</v>
+        <v>7.956</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>1.12</v>
       </c>
       <c r="I381" t="n">
-        <v>0.332</v>
+        <v>0.2998</v>
       </c>
       <c r="J381" t="n">
-        <v>6.64</v>
+        <v>5.996</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.67</v>
       </c>
       <c r="I382" t="n">
-        <v>1.3238</v>
+        <v>1.3451</v>
       </c>
       <c r="J382" t="n">
-        <v>35.7426</v>
+        <v>36.3177</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.26</v>
       </c>
       <c r="I383" t="n">
-        <v>0.6665</v>
+        <v>0.6371</v>
       </c>
       <c r="J383" t="n">
-        <v>17.9955</v>
+        <v>17.2017</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.22</v>
       </c>
       <c r="I384" t="n">
-        <v>0.5847</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="J384" t="n">
-        <v>15.7869</v>
+        <v>14.9283</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.11</v>
       </c>
       <c r="I385" t="n">
-        <v>0.3308</v>
+        <v>0.2982</v>
       </c>
       <c r="J385" t="n">
-        <v>8.9316</v>
+        <v>8.051399999999999</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.9</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.3856</v>
+        <v>-0.3454</v>
       </c>
       <c r="J386" t="n">
-        <v>-10.4112</v>
+        <v>-9.325799999999999</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.22</v>
       </c>
       <c r="I387" t="n">
-        <v>0.4938</v>
+        <v>0.4376</v>
       </c>
       <c r="J387" t="n">
-        <v>13.3326</v>
+        <v>11.8152</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1</v>
       </c>
       <c r="I388" t="n">
-        <v>0.0133</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J388" t="n">
-        <v>0.3591</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.93</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.1054</v>
+        <v>-0.09</v>
       </c>
       <c r="J389" t="n">
-        <v>-2.8458</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.9</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.1397</v>
+        <v>-0.122</v>
       </c>
       <c r="J390" t="n">
-        <v>-3.7719</v>
+        <v>-3.294</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.49</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.5243</v>
+        <v>-0.5281</v>
       </c>
       <c r="J391" t="n">
-        <v>-14.1561</v>
+        <v>-14.2587</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>0.63</v>
       </c>
       <c r="I392" t="n">
-        <v>-0.3571</v>
+        <v>-0.3498</v>
       </c>
       <c r="J392" t="n">
-        <v>-6.7849</v>
+        <v>-6.6462</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>0.61</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.376</v>
+        <v>-0.3698</v>
       </c>
       <c r="J393" t="n">
-        <v>-7.144</v>
+        <v>-7.0262</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>0.57</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.4122</v>
+        <v>-0.4076</v>
       </c>
       <c r="J394" t="n">
-        <v>-7.8318</v>
+        <v>-7.7444</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.51</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.4623</v>
+        <v>-0.4591</v>
       </c>
       <c r="J395" t="n">
-        <v>-8.7837</v>
+        <v>-8.722899999999999</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.38</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.5768</v>
+        <v>-0.5841</v>
       </c>
       <c r="J396" t="n">
-        <v>-10.9592</v>
+        <v>-11.0979</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>2.06</v>
       </c>
       <c r="I397" t="n">
-        <v>1.7346</v>
+        <v>1.7855</v>
       </c>
       <c r="J397" t="n">
-        <v>32.9574</v>
+        <v>33.9245</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.6</v>
       </c>
       <c r="I398" t="n">
-        <v>1.1867</v>
+        <v>1.2058</v>
       </c>
       <c r="J398" t="n">
-        <v>22.5473</v>
+        <v>22.9102</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.53</v>
       </c>
       <c r="I399" t="n">
-        <v>1.0995</v>
+        <v>1.1177</v>
       </c>
       <c r="J399" t="n">
-        <v>20.8905</v>
+        <v>21.2363</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>1.27</v>
       </c>
       <c r="I400" t="n">
-        <v>0.6506</v>
+        <v>0.6294</v>
       </c>
       <c r="J400" t="n">
-        <v>12.3614</v>
+        <v>11.9586</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>1.11</v>
       </c>
       <c r="I401" t="n">
-        <v>0.2877</v>
+        <v>0.2536</v>
       </c>
       <c r="J401" t="n">
-        <v>5.4663</v>
+        <v>4.8184</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.55</v>
       </c>
       <c r="I402" t="n">
-        <v>1.1688</v>
+        <v>1.1825</v>
       </c>
       <c r="J402" t="n">
-        <v>29.22</v>
+        <v>29.5625</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.28</v>
       </c>
       <c r="I403" t="n">
-        <v>0.7096</v>
+        <v>0.681</v>
       </c>
       <c r="J403" t="n">
-        <v>17.74</v>
+        <v>17.025</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.17</v>
       </c>
       <c r="I404" t="n">
-        <v>0.4775</v>
+        <v>0.4436</v>
       </c>
       <c r="J404" t="n">
-        <v>11.9375</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>1.13</v>
       </c>
       <c r="I405" t="n">
-        <v>0.3833</v>
+        <v>0.3496</v>
       </c>
       <c r="J405" t="n">
-        <v>9.5825</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.95</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.2401</v>
+        <v>-0.2037</v>
       </c>
       <c r="J406" t="n">
-        <v>-6.0025</v>
+        <v>-5.0925</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.22</v>
       </c>
       <c r="I407" t="n">
-        <v>0.4874</v>
+        <v>0.4303</v>
       </c>
       <c r="J407" t="n">
-        <v>12.185</v>
+        <v>10.7575</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.05</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1608</v>
+        <v>0.1242</v>
       </c>
       <c r="J408" t="n">
-        <v>4.02</v>
+        <v>3.105</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.01</v>
       </c>
       <c r="I409" t="n">
-        <v>0.0538</v>
+        <v>0.0364</v>
       </c>
       <c r="J409" t="n">
-        <v>1.345</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.79</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2555</v>
+        <v>-0.2358</v>
       </c>
       <c r="J410" t="n">
-        <v>-6.3875</v>
+        <v>-5.895</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.57</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.4572</v>
+        <v>-0.4525</v>
       </c>
       <c r="J411" t="n">
-        <v>-11.43</v>
+        <v>-11.3125</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.8</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4511</v>
+        <v>1.4791</v>
       </c>
       <c r="J412" t="n">
-        <v>30.4731</v>
+        <v>31.0611</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.77</v>
       </c>
       <c r="I413" t="n">
-        <v>1.4143</v>
+        <v>1.44</v>
       </c>
       <c r="J413" t="n">
-        <v>29.7003</v>
+        <v>30.24</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>1.28</v>
       </c>
       <c r="I414" t="n">
-        <v>0.6877</v>
+        <v>0.6664</v>
       </c>
       <c r="J414" t="n">
-        <v>14.4417</v>
+        <v>13.9944</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>1.21</v>
       </c>
       <c r="I415" t="n">
-        <v>0.5402</v>
+        <v>0.5124</v>
       </c>
       <c r="J415" t="n">
-        <v>11.3442</v>
+        <v>10.7604</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.92</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.3568</v>
+        <v>-0.3218</v>
       </c>
       <c r="J416" t="n">
-        <v>-7.4928</v>
+        <v>-6.7578</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.12</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3763</v>
+        <v>0.336</v>
       </c>
       <c r="J417" t="n">
-        <v>7.9023</v>
+        <v>7.056</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>0.88</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.1428</v>
+        <v>-0.1274</v>
       </c>
       <c r="J418" t="n">
-        <v>-2.9988</v>
+        <v>-2.6754</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>0.66</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.3571</v>
+        <v>-0.3433</v>
       </c>
       <c r="J419" t="n">
-        <v>-7.4991</v>
+        <v>-7.2093</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.65</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.3661</v>
+        <v>-0.3527</v>
       </c>
       <c r="J420" t="n">
-        <v>-7.6881</v>
+        <v>-7.4067</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.39</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.5939</v>
+        <v>-0.6063</v>
       </c>
       <c r="J421" t="n">
-        <v>-12.4719</v>
+        <v>-12.7323</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.64</v>
       </c>
       <c r="I422" t="n">
-        <v>1.2626</v>
+        <v>1.2801</v>
       </c>
       <c r="J422" t="n">
-        <v>31.565</v>
+        <v>32.0025</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.44</v>
       </c>
       <c r="I423" t="n">
-        <v>0.992</v>
+        <v>0.9915</v>
       </c>
       <c r="J423" t="n">
-        <v>24.8</v>
+        <v>24.7875</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.36</v>
       </c>
       <c r="I424" t="n">
-        <v>0.8492</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="J424" t="n">
-        <v>21.23</v>
+        <v>20.855</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.31</v>
       </c>
       <c r="I425" t="n">
-        <v>0.755</v>
+        <v>0.7348</v>
       </c>
       <c r="J425" t="n">
-        <v>18.875</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.93</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.3195</v>
+        <v>-0.2834</v>
       </c>
       <c r="J426" t="n">
-        <v>-7.9875</v>
+        <v>-7.085</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.08</v>
       </c>
       <c r="I427" t="n">
-        <v>0.2685</v>
+        <v>0.2268</v>
       </c>
       <c r="J427" t="n">
-        <v>6.7125</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>0.89</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.1397</v>
+        <v>-0.1244</v>
       </c>
       <c r="J428" t="n">
-        <v>-3.4925</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.72</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.3082</v>
+        <v>-0.2916</v>
       </c>
       <c r="J429" t="n">
-        <v>-7.705</v>
+        <v>-7.29</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.67</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.3541</v>
+        <v>-0.3394</v>
       </c>
       <c r="J430" t="n">
-        <v>-8.852499999999999</v>
+        <v>-8.484999999999999</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.6</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.417</v>
+        <v>-0.4069</v>
       </c>
       <c r="J431" t="n">
-        <v>-10.425</v>
+        <v>-10.1725</v>
       </c>
     </row>
     <row r="432">
@@ -20549,10 +20549,10 @@
         <v>0.77</v>
       </c>
       <c r="I432" t="n">
-        <v>-0.2282</v>
+        <v>-0.2124</v>
       </c>
       <c r="J432" t="n">
-        <v>-4.564</v>
+        <v>-4.248</v>
       </c>
     </row>
     <row r="433">
@@ -20589,10 +20589,10 @@
         <v>0.75</v>
       </c>
       <c r="I433" t="n">
-        <v>-0.2493</v>
+        <v>-0.2349</v>
       </c>
       <c r="J433" t="n">
-        <v>-4.986</v>
+        <v>-4.698</v>
       </c>
     </row>
     <row r="434">
@@ -20629,10 +20629,10 @@
         <v>0.64</v>
       </c>
       <c r="I434" t="n">
-        <v>-0.3572</v>
+        <v>-0.3487</v>
       </c>
       <c r="J434" t="n">
-        <v>-7.144</v>
+        <v>-6.974</v>
       </c>
     </row>
     <row r="435">
@@ -20669,10 +20669,10 @@
         <v>0.42</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.5485</v>
+        <v>-0.5523</v>
       </c>
       <c r="J435" t="n">
-        <v>-10.97</v>
+        <v>-11.046</v>
       </c>
     </row>
     <row r="436">
@@ -20709,10 +20709,10 @@
         <v>0.35</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.6105</v>
+        <v>-0.6234</v>
       </c>
       <c r="J436" t="n">
-        <v>-12.21</v>
+        <v>-12.468</v>
       </c>
     </row>
     <row r="437">
@@ -20749,10 +20749,10 @@
         <v>1.69</v>
       </c>
       <c r="I437" t="n">
-        <v>1.3015</v>
+        <v>1.3228</v>
       </c>
       <c r="J437" t="n">
-        <v>26.03</v>
+        <v>26.456</v>
       </c>
     </row>
     <row r="438">
@@ -20789,10 +20789,10 @@
         <v>1.64</v>
       </c>
       <c r="I438" t="n">
-        <v>1.2398</v>
+        <v>1.2591</v>
       </c>
       <c r="J438" t="n">
-        <v>24.796</v>
+        <v>25.182</v>
       </c>
     </row>
     <row r="439">
@@ -20829,10 +20829,10 @@
         <v>1.5</v>
       </c>
       <c r="I439" t="n">
-        <v>1.0633</v>
+        <v>1.0782</v>
       </c>
       <c r="J439" t="n">
-        <v>21.266</v>
+        <v>21.564</v>
       </c>
     </row>
     <row r="440">
@@ -20869,10 +20869,10 @@
         <v>1.32</v>
       </c>
       <c r="I440" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7406</v>
       </c>
       <c r="J440" t="n">
-        <v>15.11</v>
+        <v>14.812</v>
       </c>
     </row>
     <row r="441">
@@ -20909,10 +20909,10 @@
         <v>1.27</v>
       </c>
       <c r="I441" t="n">
-        <v>0.6548</v>
+        <v>0.6335</v>
       </c>
       <c r="J441" t="n">
-        <v>13.096</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="442">
@@ -20949,10 +20949,10 @@
         <v>1.21</v>
       </c>
       <c r="I442" t="n">
-        <v>0.5869</v>
+        <v>0.5484</v>
       </c>
       <c r="J442" t="n">
-        <v>17.607</v>
+        <v>16.452</v>
       </c>
     </row>
     <row r="443">
@@ -20989,10 +20989,10 @@
         <v>1.15</v>
       </c>
       <c r="I443" t="n">
-        <v>0.4489</v>
+        <v>0.4084</v>
       </c>
       <c r="J443" t="n">
-        <v>13.467</v>
+        <v>12.252</v>
       </c>
     </row>
     <row r="444">
@@ -21029,10 +21029,10 @@
         <v>1.12</v>
       </c>
       <c r="I444" t="n">
-        <v>0.3762</v>
+        <v>0.3366</v>
       </c>
       <c r="J444" t="n">
-        <v>11.286</v>
+        <v>10.098</v>
       </c>
     </row>
     <row r="445">
@@ -21069,10 +21069,10 @@
         <v>1.11</v>
       </c>
       <c r="I445" t="n">
-        <v>0.3512</v>
+        <v>0.3124</v>
       </c>
       <c r="J445" t="n">
-        <v>10.536</v>
+        <v>9.372</v>
       </c>
     </row>
     <row r="446">
@@ -21109,10 +21109,10 @@
         <v>0.83</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.5342</v>
+        <v>-0.4935</v>
       </c>
       <c r="J446" t="n">
-        <v>-16.026</v>
+        <v>-14.805</v>
       </c>
     </row>
     <row r="447">
@@ -21149,10 +21149,10 @@
         <v>1.22</v>
       </c>
       <c r="I447" t="n">
-        <v>0.4665</v>
+        <v>0.4081</v>
       </c>
       <c r="J447" t="n">
-        <v>13.995</v>
+        <v>12.243</v>
       </c>
     </row>
     <row r="448">
@@ -21189,10 +21189,10 @@
         <v>1.09</v>
       </c>
       <c r="I448" t="n">
-        <v>0.232</v>
+        <v>0.1876</v>
       </c>
       <c r="J448" t="n">
-        <v>6.96</v>
+        <v>5.628</v>
       </c>
     </row>
     <row r="449">
@@ -21229,10 +21229,10 @@
         <v>0.98</v>
       </c>
       <c r="I449" t="n">
-        <v>-0.043</v>
+        <v>-0.0326</v>
       </c>
       <c r="J449" t="n">
-        <v>-1.29</v>
+        <v>-0.978</v>
       </c>
     </row>
     <row r="450">
@@ -21269,10 +21269,10 @@
         <v>0.88</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.1697</v>
+        <v>-0.1493</v>
       </c>
       <c r="J450" t="n">
-        <v>-5.091</v>
+        <v>-4.479</v>
       </c>
     </row>
     <row r="451">
@@ -21309,10 +21309,10 @@
         <v>0.85</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.2018</v>
+        <v>-0.1812</v>
       </c>
       <c r="J451" t="n">
-        <v>-6.054</v>
+        <v>-5.436</v>
       </c>
     </row>
     <row r="452">
@@ -21349,10 +21349,10 @@
         <v>1.96</v>
       </c>
       <c r="I452" t="n">
-        <v>1.6532</v>
+        <v>1.6986</v>
       </c>
       <c r="J452" t="n">
-        <v>38.0236</v>
+        <v>39.0678</v>
       </c>
     </row>
     <row r="453">
@@ -21389,10 +21389,10 @@
         <v>1.49</v>
       </c>
       <c r="I453" t="n">
-        <v>1.0631</v>
+        <v>1.0733</v>
       </c>
       <c r="J453" t="n">
-        <v>24.4513</v>
+        <v>24.6859</v>
       </c>
     </row>
     <row r="454">
@@ -21429,10 +21429,10 @@
         <v>1.18</v>
       </c>
       <c r="I454" t="n">
-        <v>0.479</v>
+        <v>0.4488</v>
       </c>
       <c r="J454" t="n">
-        <v>11.017</v>
+        <v>10.3224</v>
       </c>
     </row>
     <row r="455">
@@ -21469,10 +21469,10 @@
         <v>1.08</v>
       </c>
       <c r="I455" t="n">
-        <v>0.2309</v>
+        <v>0.2003</v>
       </c>
       <c r="J455" t="n">
-        <v>5.3107</v>
+        <v>4.6069</v>
       </c>
     </row>
     <row r="456">
@@ -21509,10 +21509,10 @@
         <v>1.08</v>
       </c>
       <c r="I456" t="n">
-        <v>0.2309</v>
+        <v>0.2003</v>
       </c>
       <c r="J456" t="n">
-        <v>5.3107</v>
+        <v>4.6069</v>
       </c>
     </row>
     <row r="457">
@@ -21549,10 +21549,10 @@
         <v>1.14</v>
       </c>
       <c r="I457" t="n">
-        <v>0.3875</v>
+        <v>0.3397</v>
       </c>
       <c r="J457" t="n">
-        <v>8.9125</v>
+        <v>7.8131</v>
       </c>
     </row>
     <row r="458">
@@ -21589,10 +21589,10 @@
         <v>0.86</v>
       </c>
       <c r="I458" t="n">
-        <v>-0.1743</v>
+        <v>-0.1579</v>
       </c>
       <c r="J458" t="n">
-        <v>-4.0089</v>
+        <v>-3.6317</v>
       </c>
     </row>
     <row r="459">
@@ -21629,10 +21629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I459" t="n">
-        <v>-0.225</v>
+        <v>-0.2076</v>
       </c>
       <c r="J459" t="n">
-        <v>-5.175</v>
+        <v>-4.7748</v>
       </c>
     </row>
     <row r="460">
@@ -21669,10 +21669,10 @@
         <v>0.7</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.3278</v>
+        <v>-0.3117</v>
       </c>
       <c r="J460" t="n">
-        <v>-7.5394</v>
+        <v>-7.1691</v>
       </c>
     </row>
     <row r="461">
@@ -21709,10 +21709,10 @@
         <v>0.5</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.5058</v>
+        <v>-0.5057</v>
       </c>
       <c r="J461" t="n">
-        <v>-11.6334</v>
+        <v>-11.6311</v>
       </c>
     </row>
   </sheetData>
